--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y813"/>
+  <dimension ref="A1:Y814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,12 +719,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>505fatty</t>
+          <t>4nnabel5.2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@505fatty</t>
+          <t>https://www.tiktok.com/@4nnabel5.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -742,22 +742,22 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P5" s="1" t="n">
-        <v>46216.47454861111</v>
+        <v>46251.56591435185</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46216.47454861111</v>
+        <v>46251.56591435185</v>
       </c>
       <c r="R5" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -774,12 +774,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>76rene</t>
+          <t>505fatty</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@76rene</t>
+          <t>https://www.tiktok.com/@505fatty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -788,11 +788,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -801,22 +797,22 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P6" s="1" t="n">
-        <v>45915.69722222222</v>
+        <v>46216.47454861111</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>45915.69722222222</v>
+        <v>46216.47454861111</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -833,12 +829,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>__olabisi1__</t>
+          <t>76rene</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@__olabisi1__</t>
+          <t>https://www.tiktok.com/@76rene</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -849,7 +845,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -860,7 +856,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -869,13 +865,13 @@
         </is>
       </c>
       <c r="P7" s="1" t="n">
-        <v>46248.64019675926</v>
+        <v>45915.69722222222</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46248.64019675926</v>
+        <v>45915.69722222222</v>
       </c>
       <c r="R7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -892,12 +888,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>_clarahayes</t>
+          <t>__olabisi1__</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_clarahayes</t>
+          <t>https://www.tiktok.com/@__olabisi1__</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -906,7 +902,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="P8" s="1" t="n">
-        <v>46244.81741898148</v>
+        <v>46248.64019675926</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46244.81741898148</v>
+        <v>46248.64019675926</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -947,12 +947,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>_paula.ox</t>
+          <t>_clarahayes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_paula.ox</t>
+          <t>https://www.tiktok.com/@_clarahayes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -970,22 +970,22 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P9" s="1" t="n">
-        <v>46212.71496527778</v>
+        <v>46244.81741898148</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46212.71496527778</v>
+        <v>46244.81741898148</v>
       </c>
       <c r="R9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1002,12 +1002,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>_princessdee.43_</t>
+          <t>_paula.ox</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_princessdee.43_</t>
+          <t>https://www.tiktok.com/@_paula.ox</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1016,11 +1016,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1029,7 +1025,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1038,13 +1034,13 @@
         </is>
       </c>
       <c r="P10" s="1" t="n">
-        <v>46189.62420138889</v>
+        <v>46212.71496527778</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46189.62420138889</v>
+        <v>46212.71496527778</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1061,12 +1057,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>abarialabi.abiodu</t>
+          <t>_princessdee.43_</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abarialabi.abiodu</t>
+          <t>https://www.tiktok.com/@_princessdee.43_</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1075,7 +1071,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="P11" s="1" t="n">
-        <v>46211.7615625</v>
+        <v>46189.62420138889</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46211.7615625</v>
+        <v>46189.62420138889</v>
       </c>
       <c r="R11" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1116,12 +1116,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>abena.akwabeax</t>
+          <t>abarialabi.abiodu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abena.akwabeax</t>
+          <t>https://www.tiktok.com/@abarialabi.abiodu</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1139,22 +1139,22 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46189.54383101852</v>
+        <v>46211.7615625</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46189.54383101852</v>
+        <v>46211.7615625</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1171,12 +1171,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>abenafosuapabi</t>
+          <t>abena.akwabeax</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenafosuapabi</t>
+          <t>https://www.tiktok.com/@abena.akwabeax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1185,11 +1185,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1198,22 +1194,22 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P13" s="1" t="n">
-        <v>46210.21534722222</v>
+        <v>46189.54383101852</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46210.21534722222</v>
+        <v>46189.54383101852</v>
       </c>
       <c r="R13" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1230,12 +1226,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>abenamango</t>
+          <t>abenafosuapabi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenamango</t>
+          <t>https://www.tiktok.com/@abenafosuapabi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1244,7 +1240,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="P14" s="1" t="n">
-        <v>46219.56912037037</v>
+        <v>46210.21534722222</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46219.56912037037</v>
+        <v>46210.21534722222</v>
       </c>
       <c r="R14" t="n">
         <v>4.8</v>
@@ -1285,12 +1285,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>abi83231</t>
+          <t>abenamango</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abi83231</t>
+          <t>https://www.tiktok.com/@abenamango</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46221.47987268519</v>
+        <v>46219.56912037037</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46221.47987268519</v>
+        <v>46219.56912037037</v>
       </c>
       <c r="R15" t="n">
         <v>4.8</v>
@@ -1340,12 +1340,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>abiadebiyi</t>
+          <t>abi83231</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abiadebiyi</t>
+          <t>https://www.tiktok.com/@abi83231</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46229.1405787037</v>
+        <v>46221.47987268519</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46229.1405787037</v>
+        <v>46221.47987268519</v>
       </c>
       <c r="R16" t="n">
         <v>4.8</v>
@@ -1395,12 +1395,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>abimbolalongr</t>
+          <t>abiadebiyi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abimbolalongr</t>
+          <t>https://www.tiktok.com/@abiadebiyi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46228.95553240741</v>
+        <v>46229.1405787037</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46228.95553240741</v>
+        <v>46229.1405787037</v>
       </c>
       <c r="R17" t="n">
         <v>4.8</v>
@@ -1450,12 +1450,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>abiola.nofisat86</t>
+          <t>abimbolalongr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abiola.nofisat86</t>
+          <t>https://www.tiktok.com/@abimbolalongr</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46230.60199074074</v>
+        <v>46228.95553240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46230.60199074074</v>
+        <v>46228.95553240741</v>
       </c>
       <c r="R18" t="n">
         <v>4.8</v>
@@ -1505,12 +1505,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>actuallyworthittts</t>
+          <t>abiola.nofisat86</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@actuallyworthittts</t>
+          <t>https://www.tiktok.com/@abiola.nofisat86</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46250.90700231482</v>
+        <v>46230.60199074074</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46250.90700231482</v>
+        <v>46230.60199074074</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -1560,12 +1560,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ade55309</t>
+          <t>actuallyworthittts</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ade55309</t>
+          <t>https://www.tiktok.com/@actuallyworthittts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P20" s="1" t="n">
-        <v>46242.51421296296</v>
+        <v>46250.90700231482</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46242.51421296296</v>
+        <v>46250.90700231482</v>
       </c>
       <c r="R20" t="n">
         <v>6</v>
@@ -13766,11 +13766,11 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Other</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -13782,10 +13782,10 @@
         <v>46231.40361111111</v>
       </c>
       <c r="Q233" s="1" t="n">
-        <v>46247.87644675926</v>
+        <v>46251.67158564815</v>
       </c>
       <c r="R233" t="n">
-        <v>12</v>
+        <v>17.9</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -32662,26 +32662,26 @@
       <c r="K565" t="inlineStr"/>
       <c r="L565" t="inlineStr"/>
       <c r="M565" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee, Green Burner</t>
         </is>
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P565" s="1" t="n">
         <v>46248.94241898148</v>
       </c>
       <c r="Q565" s="1" t="n">
-        <v>46248.94241898148</v>
+        <v>46251.90353009259</v>
       </c>
       <c r="R565" t="n">
-        <v>5.9</v>
+        <v>11.9</v>
       </c>
       <c r="S565" t="inlineStr">
         <is>
@@ -35846,12 +35846,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>sheluvslivx</t>
+          <t>sheenyajohnston</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sheluvslivx</t>
+          <t>https://www.tiktok.com/@sheenyajohnston</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
@@ -35869,7 +35869,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O622" t="inlineStr">
@@ -35878,13 +35878,13 @@
         </is>
       </c>
       <c r="P622" s="1" t="n">
-        <v>46191.82362268519</v>
+        <v>46251.48388888889</v>
       </c>
       <c r="Q622" s="1" t="n">
-        <v>46191.82362268519</v>
+        <v>46251.48388888889</v>
       </c>
       <c r="R622" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="S622" t="inlineStr">
         <is>
@@ -35901,12 +35901,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>sher_4l</t>
+          <t>sheluvslivx</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sher_4l</t>
+          <t>https://www.tiktok.com/@sheluvslivx</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
@@ -35924,22 +35924,22 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P623" s="1" t="n">
-        <v>46213.27768518519</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="Q623" s="1" t="n">
-        <v>46213.27768518519</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="R623" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S623" t="inlineStr">
         <is>
@@ -35956,12 +35956,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>sherrydailyfinds</t>
+          <t>sher_4l</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sherrydailyfinds</t>
+          <t>https://www.tiktok.com/@sher_4l</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
@@ -35975,60 +35975,48 @@
       <c r="K624" t="inlineStr"/>
       <c r="L624" t="inlineStr"/>
       <c r="M624" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P624" s="1" t="n">
-        <v>46216.23868055556</v>
+        <v>46213.27768518519</v>
       </c>
       <c r="Q624" s="1" t="n">
-        <v>46245.41950231481</v>
+        <v>46213.27768518519</v>
       </c>
       <c r="R624" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S624" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T624" t="n">
-        <v>2</v>
-      </c>
-      <c r="U624" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="V624" t="n">
-        <v>1</v>
-      </c>
-      <c r="W624" t="n">
-        <v>112</v>
-      </c>
-      <c r="X624" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="Y624" t="n">
-        <v>15</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T624" t="inlineStr"/>
+      <c r="U624" t="inlineStr"/>
+      <c r="V624" t="inlineStr"/>
+      <c r="W624" t="inlineStr"/>
+      <c r="X624" t="inlineStr"/>
+      <c r="Y624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>shileazeezat</t>
+          <t>sherrydailyfinds</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shileazeezat</t>
+          <t>https://www.tiktok.com/@sherrydailyfinds</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -36042,48 +36030,60 @@
       <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr"/>
       <c r="M625" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee, Other</t>
         </is>
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P625" s="1" t="n">
-        <v>46209.98465277778</v>
+        <v>46216.23868055556</v>
       </c>
       <c r="Q625" s="1" t="n">
-        <v>46209.98465277778</v>
+        <v>46245.41950231481</v>
       </c>
       <c r="R625" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S625" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T625" t="inlineStr"/>
-      <c r="U625" t="inlineStr"/>
-      <c r="V625" t="inlineStr"/>
-      <c r="W625" t="inlineStr"/>
-      <c r="X625" t="inlineStr"/>
-      <c r="Y625" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T625" t="n">
+        <v>2</v>
+      </c>
+      <c r="U625" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="V625" t="n">
+        <v>1</v>
+      </c>
+      <c r="W625" t="n">
+        <v>112</v>
+      </c>
+      <c r="X625" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="Y625" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>shingara.s.natt</t>
+          <t>shileazeezat</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shingara.s.natt</t>
+          <t>https://www.tiktok.com/@shileazeezat</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -36110,10 +36110,10 @@
         </is>
       </c>
       <c r="P626" s="1" t="n">
-        <v>46231.84402777778</v>
+        <v>46209.98465277778</v>
       </c>
       <c r="Q626" s="1" t="n">
-        <v>46231.84402777778</v>
+        <v>46209.98465277778</v>
       </c>
       <c r="R626" t="n">
         <v>4.8</v>
@@ -36133,12 +36133,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>sholasho2</t>
+          <t>shingara.s.natt</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sholasho2</t>
+          <t>https://www.tiktok.com/@shingara.s.natt</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -36147,11 +36147,7 @@
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="inlineStr"/>
       <c r="H627" t="inlineStr"/>
-      <c r="I627" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I627" t="inlineStr"/>
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr"/>
       <c r="L627" t="inlineStr"/>
@@ -36169,10 +36165,10 @@
         </is>
       </c>
       <c r="P627" s="1" t="n">
-        <v>46216.41796296297</v>
+        <v>46231.84402777778</v>
       </c>
       <c r="Q627" s="1" t="n">
-        <v>46216.41796296297</v>
+        <v>46231.84402777778</v>
       </c>
       <c r="R627" t="n">
         <v>4.8</v>
@@ -36192,12 +36188,12 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>shollyodesky</t>
+          <t>sholasho2</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shollyodesky</t>
+          <t>https://www.tiktok.com/@sholasho2</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -36228,10 +36224,10 @@
         </is>
       </c>
       <c r="P628" s="1" t="n">
-        <v>46222.30527777778</v>
+        <v>46216.41796296297</v>
       </c>
       <c r="Q628" s="1" t="n">
-        <v>46222.30527777778</v>
+        <v>46216.41796296297</v>
       </c>
       <c r="R628" t="n">
         <v>4.8</v>
@@ -36251,12 +36247,12 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>shop_with_mia_</t>
+          <t>shollyodesky</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shop_with_mia_</t>
+          <t>https://www.tiktok.com/@shollyodesky</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -36265,7 +36261,11 @@
       <c r="F629" t="inlineStr"/>
       <c r="G629" t="inlineStr"/>
       <c r="H629" t="inlineStr"/>
-      <c r="I629" t="inlineStr"/>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr"/>
       <c r="L629" t="inlineStr"/>
@@ -36274,56 +36274,44 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P629" s="1" t="n">
-        <v>46231.40219907407</v>
+        <v>46222.30527777778</v>
       </c>
       <c r="Q629" s="1" t="n">
-        <v>46231.40219907407</v>
+        <v>46222.30527777778</v>
       </c>
       <c r="R629" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S629" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T629" t="n">
-        <v>6</v>
-      </c>
-      <c r="U629" t="n">
-        <v>0</v>
-      </c>
-      <c r="V629" t="n">
-        <v>0</v>
-      </c>
-      <c r="W629" t="n">
-        <v>165</v>
-      </c>
-      <c r="X629" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="Y629" t="n">
-        <v>2</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T629" t="inlineStr"/>
+      <c r="U629" t="inlineStr"/>
+      <c r="V629" t="inlineStr"/>
+      <c r="W629" t="inlineStr"/>
+      <c r="X629" t="inlineStr"/>
+      <c r="Y629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>shukri.sharaf793</t>
+          <t>shop_with_mia_</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukri.sharaf793</t>
+          <t>https://www.tiktok.com/@shop_with_mia_</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -36341,44 +36329,56 @@
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P630" s="1" t="n">
-        <v>46207.54836805556</v>
+        <v>46231.40219907407</v>
       </c>
       <c r="Q630" s="1" t="n">
-        <v>46207.54836805556</v>
+        <v>46231.40219907407</v>
       </c>
       <c r="R630" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S630" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T630" t="inlineStr"/>
-      <c r="U630" t="inlineStr"/>
-      <c r="V630" t="inlineStr"/>
-      <c r="W630" t="inlineStr"/>
-      <c r="X630" t="inlineStr"/>
-      <c r="Y630" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T630" t="n">
+        <v>6</v>
+      </c>
+      <c r="U630" t="n">
+        <v>0</v>
+      </c>
+      <c r="V630" t="n">
+        <v>0</v>
+      </c>
+      <c r="W630" t="n">
+        <v>165</v>
+      </c>
+      <c r="X630" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="Y630" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>shukridaud1</t>
+          <t>shukri.sharaf793</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukridaud1</t>
+          <t>https://www.tiktok.com/@shukri.sharaf793</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -36396,7 +36396,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
@@ -36405,13 +36405,13 @@
         </is>
       </c>
       <c r="P631" s="1" t="n">
-        <v>46197.41108796297</v>
+        <v>46207.54836805556</v>
       </c>
       <c r="Q631" s="1" t="n">
-        <v>46197.41108796297</v>
+        <v>46207.54836805556</v>
       </c>
       <c r="R631" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S631" t="inlineStr">
         <is>
@@ -36428,12 +36428,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>sicino.dube</t>
+          <t>shukridaud1</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sicino.dube</t>
+          <t>https://www.tiktok.com/@shukridaud1</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -36451,7 +36451,7 @@
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O632" t="inlineStr">
@@ -36460,13 +36460,13 @@
         </is>
       </c>
       <c r="P632" s="1" t="n">
-        <v>46213.78520833333</v>
+        <v>46197.41108796297</v>
       </c>
       <c r="Q632" s="1" t="n">
-        <v>46213.78520833333</v>
+        <v>46197.41108796297</v>
       </c>
       <c r="R632" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S632" t="inlineStr">
         <is>
@@ -36483,12 +36483,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>sikabaaagudie</t>
+          <t>sicino.dube</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sikabaaagudie</t>
+          <t>https://www.tiktok.com/@sicino.dube</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -36515,10 +36515,10 @@
         </is>
       </c>
       <c r="P633" s="1" t="n">
-        <v>46212.42873842592</v>
+        <v>46213.78520833333</v>
       </c>
       <c r="Q633" s="1" t="n">
-        <v>46212.42873842592</v>
+        <v>46213.78520833333</v>
       </c>
       <c r="R633" t="n">
         <v>4.8</v>
@@ -36538,12 +36538,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>simonlikestiktok</t>
+          <t>sikabaaagudie</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@simonlikestiktok</t>
+          <t>https://www.tiktok.com/@sikabaaagudie</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -36561,7 +36561,7 @@
       </c>
       <c r="N634" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O634" t="inlineStr">
@@ -36570,13 +36570,13 @@
         </is>
       </c>
       <c r="P634" s="1" t="n">
-        <v>46153.56069444444</v>
+        <v>46212.42873842592</v>
       </c>
       <c r="Q634" s="1" t="n">
-        <v>46153.56069444444</v>
+        <v>46212.42873842592</v>
       </c>
       <c r="R634" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S634" t="inlineStr">
         <is>
@@ -36593,12 +36593,12 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>simple.lady065</t>
+          <t>simonlikestiktok</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@simple.lady065</t>
+          <t>https://www.tiktok.com/@simonlikestiktok</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -36616,7 +36616,7 @@
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O635" t="inlineStr">
@@ -36625,13 +36625,13 @@
         </is>
       </c>
       <c r="P635" s="1" t="n">
-        <v>46226.44326388889</v>
+        <v>46153.56069444444</v>
       </c>
       <c r="Q635" s="1" t="n">
-        <v>46226.44326388889</v>
+        <v>46153.56069444444</v>
       </c>
       <c r="R635" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S635" t="inlineStr">
         <is>
@@ -36648,12 +36648,12 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>sislyn47</t>
+          <t>simple.lady065</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sislyn47</t>
+          <t>https://www.tiktok.com/@simple.lady065</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -36680,10 +36680,10 @@
         </is>
       </c>
       <c r="P636" s="1" t="n">
-        <v>46231.94196759259</v>
+        <v>46226.44326388889</v>
       </c>
       <c r="Q636" s="1" t="n">
-        <v>46231.94196759259</v>
+        <v>46226.44326388889</v>
       </c>
       <c r="R636" t="n">
         <v>4.8</v>
@@ -36703,12 +36703,12 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>sister.abena223</t>
+          <t>sislyn47</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sister.abena223</t>
+          <t>https://www.tiktok.com/@sislyn47</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -36735,10 +36735,10 @@
         </is>
       </c>
       <c r="P637" s="1" t="n">
-        <v>46212.49475694444</v>
+        <v>46231.94196759259</v>
       </c>
       <c r="Q637" s="1" t="n">
-        <v>46212.49475694444</v>
+        <v>46231.94196759259</v>
       </c>
       <c r="R637" t="n">
         <v>4.8</v>
@@ -36758,12 +36758,12 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>siyandagumede3</t>
+          <t>sister.abena223</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@siyandagumede3</t>
+          <t>https://www.tiktok.com/@sister.abena223</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
@@ -36790,10 +36790,10 @@
         </is>
       </c>
       <c r="P638" s="1" t="n">
-        <v>46230.84641203703</v>
+        <v>46212.49475694444</v>
       </c>
       <c r="Q638" s="1" t="n">
-        <v>46230.84641203703</v>
+        <v>46212.49475694444</v>
       </c>
       <c r="R638" t="n">
         <v>4.8</v>
@@ -36813,12 +36813,12 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>smashd.it</t>
+          <t>siyandagumede3</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smashd.it</t>
+          <t>https://www.tiktok.com/@siyandagumede3</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -36832,26 +36832,26 @@
       <c r="K639" t="inlineStr"/>
       <c r="L639" t="inlineStr"/>
       <c r="M639" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P639" s="1" t="n">
-        <v>46194.95645833333</v>
+        <v>46230.84641203703</v>
       </c>
       <c r="Q639" s="1" t="n">
-        <v>46195.87739583333</v>
+        <v>46230.84641203703</v>
       </c>
       <c r="R639" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="S639" t="inlineStr">
         <is>
@@ -36868,12 +36868,12 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>smile4me_24</t>
+          <t>smashd.it</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smile4me_24</t>
+          <t>https://www.tiktok.com/@smashd.it</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -36882,16 +36882,12 @@
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="inlineStr"/>
       <c r="H640" t="inlineStr"/>
-      <c r="I640" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I640" t="inlineStr"/>
       <c r="J640" t="inlineStr"/>
       <c r="K640" t="inlineStr"/>
       <c r="L640" t="inlineStr"/>
       <c r="M640" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N640" t="inlineStr">
         <is>
@@ -36900,17 +36896,17 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P640" s="1" t="n">
-        <v>46209.88681712963</v>
+        <v>46194.95645833333</v>
       </c>
       <c r="Q640" s="1" t="n">
-        <v>46209.88681712963</v>
+        <v>46195.87739583333</v>
       </c>
       <c r="R640" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S640" t="inlineStr">
         <is>
@@ -36927,12 +36923,12 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>snowhite007</t>
+          <t>smile4me_24</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@snowhite007</t>
+          <t>https://www.tiktok.com/@smile4me_24</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -36943,7 +36939,7 @@
       <c r="H641" t="inlineStr"/>
       <c r="I641" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J641" t="inlineStr"/>
@@ -36954,7 +36950,7 @@
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
@@ -36963,13 +36959,13 @@
         </is>
       </c>
       <c r="P641" s="1" t="n">
-        <v>46213.96833333333</v>
+        <v>46209.88681712963</v>
       </c>
       <c r="Q641" s="1" t="n">
-        <v>46213.96833333333</v>
+        <v>46209.88681712963</v>
       </c>
       <c r="R641" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S641" t="inlineStr">
         <is>
@@ -36986,12 +36982,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>softsparkle21</t>
+          <t>snowhite007</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@softsparkle21</t>
+          <t>https://www.tiktok.com/@snowhite007</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -37000,7 +36996,11 @@
       <c r="F642" t="inlineStr"/>
       <c r="G642" t="inlineStr"/>
       <c r="H642" t="inlineStr"/>
-      <c r="I642" t="inlineStr"/>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr"/>
       <c r="L642" t="inlineStr"/>
@@ -37018,10 +37018,10 @@
         </is>
       </c>
       <c r="P642" s="1" t="n">
-        <v>46230.59473379629</v>
+        <v>46213.96833333333</v>
       </c>
       <c r="Q642" s="1" t="n">
-        <v>46230.59473379629</v>
+        <v>46213.96833333333</v>
       </c>
       <c r="R642" t="n">
         <v>4.8</v>
@@ -37041,12 +37041,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>sofy_0786</t>
+          <t>softsparkle21</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sofy_0786</t>
+          <t>https://www.tiktok.com/@softsparkle21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -37055,11 +37055,7 @@
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="inlineStr"/>
       <c r="H643" t="inlineStr"/>
-      <c r="I643" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
+      <c r="I643" t="inlineStr"/>
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr"/>
       <c r="L643" t="inlineStr"/>
@@ -37077,10 +37073,10 @@
         </is>
       </c>
       <c r="P643" s="1" t="n">
-        <v>46215.35962962963</v>
+        <v>46230.59473379629</v>
       </c>
       <c r="Q643" s="1" t="n">
-        <v>46215.35962962963</v>
+        <v>46230.59473379629</v>
       </c>
       <c r="R643" t="n">
         <v>4.8</v>
@@ -37100,12 +37096,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>sola.akinyemi5</t>
+          <t>sofy_0786</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sola.akinyemi5</t>
+          <t>https://www.tiktok.com/@sofy_0786</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -37114,7 +37110,11 @@
       <c r="F644" t="inlineStr"/>
       <c r="G644" t="inlineStr"/>
       <c r="H644" t="inlineStr"/>
-      <c r="I644" t="inlineStr"/>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J644" t="inlineStr"/>
       <c r="K644" t="inlineStr"/>
       <c r="L644" t="inlineStr"/>
@@ -37132,10 +37132,10 @@
         </is>
       </c>
       <c r="P644" s="1" t="n">
-        <v>46207.86487268518</v>
+        <v>46215.35962962963</v>
       </c>
       <c r="Q644" s="1" t="n">
-        <v>46207.86487268518</v>
+        <v>46215.35962962963</v>
       </c>
       <c r="R644" t="n">
         <v>4.8</v>
@@ -37155,12 +37155,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>sophiaababio</t>
+          <t>sola.akinyemi5</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sophiaababio</t>
+          <t>https://www.tiktok.com/@sola.akinyemi5</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
@@ -37169,11 +37169,7 @@
       <c r="F645" t="inlineStr"/>
       <c r="G645" t="inlineStr"/>
       <c r="H645" t="inlineStr"/>
-      <c r="I645" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I645" t="inlineStr"/>
       <c r="J645" t="inlineStr"/>
       <c r="K645" t="inlineStr"/>
       <c r="L645" t="inlineStr"/>
@@ -37182,7 +37178,7 @@
       </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
@@ -37191,13 +37187,13 @@
         </is>
       </c>
       <c r="P645" s="1" t="n">
-        <v>46181.97809027778</v>
+        <v>46207.86487268518</v>
       </c>
       <c r="Q645" s="1" t="n">
-        <v>46181.97809027778</v>
+        <v>46207.86487268518</v>
       </c>
       <c r="R645" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S645" t="inlineStr">
         <is>
@@ -37214,12 +37210,12 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>sophiemarie1994</t>
+          <t>sophiaababio</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sophiemarie1994</t>
+          <t>https://www.tiktok.com/@sophiaababio</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -37228,7 +37224,11 @@
       <c r="F646" t="inlineStr"/>
       <c r="G646" t="inlineStr"/>
       <c r="H646" t="inlineStr"/>
-      <c r="I646" t="inlineStr"/>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J646" t="inlineStr"/>
       <c r="K646" t="inlineStr"/>
       <c r="L646" t="inlineStr"/>
@@ -37242,14 +37242,14 @@
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P646" s="1" t="n">
-        <v>46217.84153935185</v>
+        <v>46181.97809027778</v>
       </c>
       <c r="Q646" s="1" t="n">
-        <v>46217.84153935185</v>
+        <v>46181.97809027778</v>
       </c>
       <c r="R646" t="n">
         <v>6</v>
@@ -37269,12 +37269,12 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>sophx.03</t>
+          <t>sophiemarie1994</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sophx.03</t>
+          <t>https://www.tiktok.com/@sophiemarie1994</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -37301,10 +37301,10 @@
         </is>
       </c>
       <c r="P647" s="1" t="n">
-        <v>46170.72229166667</v>
+        <v>46217.84153935185</v>
       </c>
       <c r="Q647" s="1" t="n">
-        <v>46170.72229166667</v>
+        <v>46217.84153935185</v>
       </c>
       <c r="R647" t="n">
         <v>6</v>
@@ -37324,12 +37324,12 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>soulsensation3</t>
+          <t>sophx.03</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soulsensation3</t>
+          <t>https://www.tiktok.com/@sophx.03</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -37347,22 +37347,22 @@
       </c>
       <c r="N648" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P648" s="1" t="n">
-        <v>46210.89850694445</v>
+        <v>46170.72229166667</v>
       </c>
       <c r="Q648" s="1" t="n">
-        <v>46210.89850694445</v>
+        <v>46170.72229166667</v>
       </c>
       <c r="R648" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S648" t="inlineStr">
         <is>
@@ -37379,12 +37379,12 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>sowugah74</t>
+          <t>soulsensation3</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sowugah74</t>
+          <t>https://www.tiktok.com/@soulsensation3</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -37411,10 +37411,10 @@
         </is>
       </c>
       <c r="P649" s="1" t="n">
-        <v>46207.67658564815</v>
+        <v>46210.89850694445</v>
       </c>
       <c r="Q649" s="1" t="n">
-        <v>46207.67658564815</v>
+        <v>46210.89850694445</v>
       </c>
       <c r="R649" t="n">
         <v>4.8</v>
@@ -37434,12 +37434,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>stacecaldridge</t>
+          <t>sowugah74</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stacecaldridge</t>
+          <t>https://www.tiktok.com/@sowugah74</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -37453,26 +37453,26 @@
       <c r="K650" t="inlineStr"/>
       <c r="L650" t="inlineStr"/>
       <c r="M650" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N650" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT), seller</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P650" s="1" t="n">
-        <v>46249.70214120371</v>
+        <v>46207.67658564815</v>
       </c>
       <c r="Q650" s="1" t="n">
-        <v>46249.70214120371</v>
+        <v>46207.67658564815</v>
       </c>
       <c r="R650" t="n">
-        <v>11.9</v>
+        <v>4.8</v>
       </c>
       <c r="S650" t="inlineStr">
         <is>
@@ -37489,12 +37489,12 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>stellaezigbo1</t>
+          <t>stacecaldridge</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stellaezigbo1</t>
+          <t>https://www.tiktok.com/@stacecaldridge</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -37503,35 +37503,31 @@
       <c r="F651" t="inlineStr"/>
       <c r="G651" t="inlineStr"/>
       <c r="H651" t="inlineStr"/>
-      <c r="I651" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I651" t="inlineStr"/>
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="inlineStr"/>
       <c r="L651" t="inlineStr"/>
       <c r="M651" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N651" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P651" s="1" t="n">
-        <v>46162.27979166667</v>
+        <v>46249.70214120371</v>
       </c>
       <c r="Q651" s="1" t="n">
-        <v>46162.27979166667</v>
+        <v>46249.70214120371</v>
       </c>
       <c r="R651" t="n">
-        <v>6</v>
+        <v>11.9</v>
       </c>
       <c r="S651" t="inlineStr">
         <is>
@@ -37548,12 +37544,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>steph73416</t>
+          <t>stellaezigbo1</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@steph73416</t>
+          <t>https://www.tiktok.com/@stellaezigbo1</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -37562,7 +37558,11 @@
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="inlineStr"/>
       <c r="H652" t="inlineStr"/>
-      <c r="I652" t="inlineStr"/>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J652" t="inlineStr"/>
       <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr"/>
@@ -37576,14 +37576,14 @@
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P652" s="1" t="n">
-        <v>46217.75144675926</v>
+        <v>46162.27979166667</v>
       </c>
       <c r="Q652" s="1" t="n">
-        <v>46217.75144675926</v>
+        <v>46162.27979166667</v>
       </c>
       <c r="R652" t="n">
         <v>6</v>
@@ -37603,12 +37603,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>stephaddy19</t>
+          <t>steph73416</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stephaddy19</t>
+          <t>https://www.tiktok.com/@steph73416</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -37617,11 +37617,7 @@
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr"/>
-      <c r="I653" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I653" t="inlineStr"/>
       <c r="J653" t="inlineStr"/>
       <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr"/>
@@ -37630,22 +37626,22 @@
       </c>
       <c r="N653" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P653" s="1" t="n">
-        <v>46230.58262731481</v>
+        <v>46217.75144675926</v>
       </c>
       <c r="Q653" s="1" t="n">
-        <v>46230.58262731481</v>
+        <v>46217.75144675926</v>
       </c>
       <c r="R653" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S653" t="inlineStr">
         <is>
@@ -37662,12 +37658,12 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>steve2210shgoogle</t>
+          <t>stephaddy19</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@steve2210shgoogle</t>
+          <t>https://www.tiktok.com/@stephaddy19</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -37676,7 +37672,11 @@
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="inlineStr"/>
       <c r="H654" t="inlineStr"/>
-      <c r="I654" t="inlineStr"/>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J654" t="inlineStr"/>
       <c r="K654" t="inlineStr"/>
       <c r="L654" t="inlineStr"/>
@@ -37694,10 +37694,10 @@
         </is>
       </c>
       <c r="P654" s="1" t="n">
-        <v>46219.45165509259</v>
+        <v>46230.58262731481</v>
       </c>
       <c r="Q654" s="1" t="n">
-        <v>46219.45165509259</v>
+        <v>46230.58262731481</v>
       </c>
       <c r="R654" t="n">
         <v>4.8</v>
@@ -37717,12 +37717,12 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>styled388</t>
+          <t>steve2210shgoogle</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@styled388</t>
+          <t>https://www.tiktok.com/@steve2210shgoogle</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -37740,22 +37740,22 @@
       </c>
       <c r="N655" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P655" s="1" t="n">
-        <v>46198.62712962963</v>
+        <v>46219.45165509259</v>
       </c>
       <c r="Q655" s="1" t="n">
-        <v>46198.62712962963</v>
+        <v>46219.45165509259</v>
       </c>
       <c r="R655" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S655" t="inlineStr">
         <is>
@@ -37772,12 +37772,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>subdoink</t>
+          <t>styled388</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@subdoink</t>
+          <t>https://www.tiktok.com/@styled388</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -37786,11 +37786,7 @@
       <c r="F656" t="inlineStr"/>
       <c r="G656" t="inlineStr"/>
       <c r="H656" t="inlineStr"/>
-      <c r="I656" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I656" t="inlineStr"/>
       <c r="J656" t="inlineStr"/>
       <c r="K656" t="inlineStr"/>
       <c r="L656" t="inlineStr"/>
@@ -37799,22 +37795,22 @@
       </c>
       <c r="N656" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P656" s="1" t="n">
-        <v>46209.28653935185</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q656" s="1" t="n">
-        <v>46209.28653935185</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R656" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S656" t="inlineStr">
         <is>
@@ -37831,12 +37827,12 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>sue00288</t>
+          <t>subdoink</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sue00288</t>
+          <t>https://www.tiktok.com/@subdoink</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -37845,7 +37841,11 @@
       <c r="F657" t="inlineStr"/>
       <c r="G657" t="inlineStr"/>
       <c r="H657" t="inlineStr"/>
-      <c r="I657" t="inlineStr"/>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J657" t="inlineStr"/>
       <c r="K657" t="inlineStr"/>
       <c r="L657" t="inlineStr"/>
@@ -37863,10 +37863,10 @@
         </is>
       </c>
       <c r="P657" s="1" t="n">
-        <v>46212.45952546296</v>
+        <v>46209.28653935185</v>
       </c>
       <c r="Q657" s="1" t="n">
-        <v>46212.45952546296</v>
+        <v>46209.28653935185</v>
       </c>
       <c r="R657" t="n">
         <v>4.8</v>
@@ -37886,12 +37886,12 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>suegraham1960</t>
+          <t>sue00288</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suegraham1960</t>
+          <t>https://www.tiktok.com/@sue00288</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -37909,22 +37909,22 @@
       </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P658" s="1" t="n">
-        <v>46202.87236111111</v>
+        <v>46212.45952546296</v>
       </c>
       <c r="Q658" s="1" t="n">
-        <v>46202.87236111111</v>
+        <v>46212.45952546296</v>
       </c>
       <c r="R658" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S658" t="inlineStr">
         <is>
@@ -37941,12 +37941,12 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>sufficientgod111</t>
+          <t>suegraham1960</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sufficientgod111</t>
+          <t>https://www.tiktok.com/@suegraham1960</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -37964,22 +37964,22 @@
       </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P659" s="1" t="n">
-        <v>46216.57333333333</v>
+        <v>46202.87236111111</v>
       </c>
       <c r="Q659" s="1" t="n">
-        <v>46216.57333333333</v>
+        <v>46202.87236111111</v>
       </c>
       <c r="R659" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S659" t="inlineStr">
         <is>
@@ -37996,12 +37996,12 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>suni.lama48</t>
+          <t>sufficientgod111</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suni.lama48</t>
+          <t>https://www.tiktok.com/@sufficientgod111</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -38010,11 +38010,7 @@
       <c r="F660" t="inlineStr"/>
       <c r="G660" t="inlineStr"/>
       <c r="H660" t="inlineStr"/>
-      <c r="I660" t="inlineStr">
-        <is>
-          <t>East/SE Asian</t>
-        </is>
-      </c>
+      <c r="I660" t="inlineStr"/>
       <c r="J660" t="inlineStr"/>
       <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr"/>
@@ -38032,10 +38028,10 @@
         </is>
       </c>
       <c r="P660" s="1" t="n">
-        <v>46229.81106481481</v>
+        <v>46216.57333333333</v>
       </c>
       <c r="Q660" s="1" t="n">
-        <v>46229.81106481481</v>
+        <v>46216.57333333333</v>
       </c>
       <c r="R660" t="n">
         <v>4.8</v>
@@ -38055,12 +38051,12 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>sunny21321_</t>
+          <t>suni.lama48</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sunny21321_</t>
+          <t>https://www.tiktok.com/@suni.lama48</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -38069,7 +38065,11 @@
       <c r="F661" t="inlineStr"/>
       <c r="G661" t="inlineStr"/>
       <c r="H661" t="inlineStr"/>
-      <c r="I661" t="inlineStr"/>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J661" t="inlineStr"/>
       <c r="K661" t="inlineStr"/>
       <c r="L661" t="inlineStr"/>
@@ -38087,10 +38087,10 @@
         </is>
       </c>
       <c r="P661" s="1" t="n">
-        <v>46221.63746527778</v>
+        <v>46229.81106481481</v>
       </c>
       <c r="Q661" s="1" t="n">
-        <v>46221.63746527778</v>
+        <v>46229.81106481481</v>
       </c>
       <c r="R661" t="n">
         <v>4.8</v>
@@ -38110,12 +38110,12 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>sunshine_2216</t>
+          <t>sunny21321_</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sunshine_2216</t>
+          <t>https://www.tiktok.com/@sunny21321_</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -38142,10 +38142,10 @@
         </is>
       </c>
       <c r="P662" s="1" t="n">
-        <v>46209.41216435185</v>
+        <v>46221.63746527778</v>
       </c>
       <c r="Q662" s="1" t="n">
-        <v>46209.41216435185</v>
+        <v>46221.63746527778</v>
       </c>
       <c r="R662" t="n">
         <v>4.8</v>
@@ -38165,12 +38165,12 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>superninjagyal</t>
+          <t>sunshine_2216</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@superninjagyal</t>
+          <t>https://www.tiktok.com/@sunshine_2216</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -38197,10 +38197,10 @@
         </is>
       </c>
       <c r="P663" s="1" t="n">
-        <v>46234.56545138889</v>
+        <v>46209.41216435185</v>
       </c>
       <c r="Q663" s="1" t="n">
-        <v>46234.56545138889</v>
+        <v>46209.41216435185</v>
       </c>
       <c r="R663" t="n">
         <v>4.8</v>
@@ -38220,12 +38220,12 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>susanmbugua</t>
+          <t>superninjagyal</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@susanmbugua</t>
+          <t>https://www.tiktok.com/@superninjagyal</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -38234,11 +38234,7 @@
       <c r="F664" t="inlineStr"/>
       <c r="G664" t="inlineStr"/>
       <c r="H664" t="inlineStr"/>
-      <c r="I664" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I664" t="inlineStr"/>
       <c r="J664" t="inlineStr"/>
       <c r="K664" t="inlineStr"/>
       <c r="L664" t="inlineStr"/>
@@ -38256,10 +38252,10 @@
         </is>
       </c>
       <c r="P664" s="1" t="n">
-        <v>46221.3227662037</v>
+        <v>46234.56545138889</v>
       </c>
       <c r="Q664" s="1" t="n">
-        <v>46221.3227662037</v>
+        <v>46234.56545138889</v>
       </c>
       <c r="R664" t="n">
         <v>4.8</v>
@@ -38279,12 +38275,12 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>sweetblessinglove</t>
+          <t>susanmbugua</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sweetblessinglove</t>
+          <t>https://www.tiktok.com/@susanmbugua</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -38295,7 +38291,7 @@
       <c r="H665" t="inlineStr"/>
       <c r="I665" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J665" t="inlineStr"/>
@@ -38315,10 +38311,10 @@
         </is>
       </c>
       <c r="P665" s="1" t="n">
-        <v>46208.97574074074</v>
+        <v>46221.3227662037</v>
       </c>
       <c r="Q665" s="1" t="n">
-        <v>46208.97574074074</v>
+        <v>46221.3227662037</v>
       </c>
       <c r="R665" t="n">
         <v>4.8</v>
@@ -38338,12 +38334,12 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>sweetestebby</t>
+          <t>sweetblessinglove</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sweetestebby</t>
+          <t>https://www.tiktok.com/@sweetblessinglove</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -38352,7 +38348,11 @@
       <c r="F666" t="inlineStr"/>
       <c r="G666" t="inlineStr"/>
       <c r="H666" t="inlineStr"/>
-      <c r="I666" t="inlineStr"/>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J666" t="inlineStr"/>
       <c r="K666" t="inlineStr"/>
       <c r="L666" t="inlineStr"/>
@@ -38370,10 +38370,10 @@
         </is>
       </c>
       <c r="P666" s="1" t="n">
-        <v>46221.38238425926</v>
+        <v>46208.97574074074</v>
       </c>
       <c r="Q666" s="1" t="n">
-        <v>46221.38238425926</v>
+        <v>46208.97574074074</v>
       </c>
       <c r="R666" t="n">
         <v>4.8</v>
@@ -38393,12 +38393,12 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>syeda_ahmed35</t>
+          <t>sweetestebby</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@syeda_ahmed35</t>
+          <t>https://www.tiktok.com/@sweetestebby</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -38425,10 +38425,10 @@
         </is>
       </c>
       <c r="P667" s="1" t="n">
-        <v>46227.88446759259</v>
+        <v>46221.38238425926</v>
       </c>
       <c r="Q667" s="1" t="n">
-        <v>46227.88446759259</v>
+        <v>46221.38238425926</v>
       </c>
       <c r="R667" t="n">
         <v>4.8</v>
@@ -38448,12 +38448,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>sylhetimumukworld</t>
+          <t>syeda_ahmed35</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sylhetimumukworld</t>
+          <t>https://www.tiktok.com/@syeda_ahmed35</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -38471,56 +38471,44 @@
       </c>
       <c r="N668" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P668" s="1" t="n">
-        <v>46212.55766203703</v>
+        <v>46227.88446759259</v>
       </c>
       <c r="Q668" s="1" t="n">
-        <v>46212.55766203703</v>
+        <v>46227.88446759259</v>
       </c>
       <c r="R668" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S668" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T668" t="n">
-        <v>1</v>
-      </c>
-      <c r="U668" t="n">
-        <v>0</v>
-      </c>
-      <c r="V668" t="n">
-        <v>0</v>
-      </c>
-      <c r="W668" t="n">
-        <v>3</v>
-      </c>
-      <c r="X668" s="1" t="n">
-        <v>46214</v>
-      </c>
-      <c r="Y668" t="n">
-        <v>1</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T668" t="inlineStr"/>
+      <c r="U668" t="inlineStr"/>
+      <c r="V668" t="inlineStr"/>
+      <c r="W668" t="inlineStr"/>
+      <c r="X668" t="inlineStr"/>
+      <c r="Y668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>szept.aeris</t>
+          <t>sylhetimumukworld</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@szept.aeris</t>
+          <t>https://www.tiktok.com/@sylhetimumukworld</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -38547,10 +38535,10 @@
         </is>
       </c>
       <c r="P669" s="1" t="n">
-        <v>46215.73248842593</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="Q669" s="1" t="n">
-        <v>46215.73248842593</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="R669" t="n">
         <v>6</v>
@@ -38570,24 +38558,24 @@
         <v>0</v>
       </c>
       <c r="W669" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X669" s="1" t="n">
-        <v>46224</v>
+        <v>46214</v>
       </c>
       <c r="Y669" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>tanasoko8</t>
+          <t>szept.aeris</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tanasoko8</t>
+          <t>https://www.tiktok.com/@szept.aeris</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -38596,11 +38584,7 @@
       <c r="F670" t="inlineStr"/>
       <c r="G670" t="inlineStr"/>
       <c r="H670" t="inlineStr"/>
-      <c r="I670" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I670" t="inlineStr"/>
       <c r="J670" t="inlineStr"/>
       <c r="K670" t="inlineStr"/>
       <c r="L670" t="inlineStr"/>
@@ -38609,44 +38593,56 @@
       </c>
       <c r="N670" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P670" s="1" t="n">
-        <v>46210.31453703704</v>
+        <v>46215.73248842593</v>
       </c>
       <c r="Q670" s="1" t="n">
-        <v>46210.31453703704</v>
+        <v>46215.73248842593</v>
       </c>
       <c r="R670" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S670" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T670" t="inlineStr"/>
-      <c r="U670" t="inlineStr"/>
-      <c r="V670" t="inlineStr"/>
-      <c r="W670" t="inlineStr"/>
-      <c r="X670" t="inlineStr"/>
-      <c r="Y670" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T670" t="n">
+        <v>1</v>
+      </c>
+      <c r="U670" t="n">
+        <v>0</v>
+      </c>
+      <c r="V670" t="n">
+        <v>0</v>
+      </c>
+      <c r="W670" t="n">
+        <v>2</v>
+      </c>
+      <c r="X670" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="Y670" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>tanny340</t>
+          <t>tanasoko8</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tanny340</t>
+          <t>https://www.tiktok.com/@tanasoko8</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -38655,7 +38651,11 @@
       <c r="F671" t="inlineStr"/>
       <c r="G671" t="inlineStr"/>
       <c r="H671" t="inlineStr"/>
-      <c r="I671" t="inlineStr"/>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J671" t="inlineStr"/>
       <c r="K671" t="inlineStr"/>
       <c r="L671" t="inlineStr"/>
@@ -38673,10 +38673,10 @@
         </is>
       </c>
       <c r="P671" s="1" t="n">
-        <v>46224.71663194444</v>
+        <v>46210.31453703704</v>
       </c>
       <c r="Q671" s="1" t="n">
-        <v>46224.71663194444</v>
+        <v>46210.31453703704</v>
       </c>
       <c r="R671" t="n">
         <v>4.8</v>
@@ -38696,12 +38696,12 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>tasnimah.ali</t>
+          <t>tanny340</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tasnimah.ali</t>
+          <t>https://www.tiktok.com/@tanny340</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -38719,7 +38719,7 @@
       </c>
       <c r="N672" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
@@ -38728,13 +38728,13 @@
         </is>
       </c>
       <c r="P672" s="1" t="n">
-        <v>46183.97074074074</v>
+        <v>46224.71663194444</v>
       </c>
       <c r="Q672" s="1" t="n">
-        <v>46183.97074074074</v>
+        <v>46224.71663194444</v>
       </c>
       <c r="R672" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S672" t="inlineStr">
         <is>
@@ -38751,12 +38751,12 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>tasteoflemon666</t>
+          <t>tasnimah.ali</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tasteoflemon666</t>
+          <t>https://www.tiktok.com/@tasnimah.ali</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -38779,14 +38779,14 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P673" s="1" t="n">
-        <v>46221.49270833333</v>
+        <v>46183.97074074074</v>
       </c>
       <c r="Q673" s="1" t="n">
-        <v>46221.49270833333</v>
+        <v>46183.97074074074</v>
       </c>
       <c r="R673" t="n">
         <v>6</v>
@@ -38806,12 +38806,12 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>technopaedia</t>
+          <t>tasteoflemon666</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@technopaedia</t>
+          <t>https://www.tiktok.com/@tasteoflemon666</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -38829,22 +38829,22 @@
       </c>
       <c r="N674" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P674" s="1" t="n">
-        <v>46222.49525462963</v>
+        <v>46221.49270833333</v>
       </c>
       <c r="Q674" s="1" t="n">
-        <v>46222.49525462963</v>
+        <v>46221.49270833333</v>
       </c>
       <c r="R674" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S674" t="inlineStr">
         <is>
@@ -38861,12 +38861,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>teemama329</t>
+          <t>technopaedia</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teemama329</t>
+          <t>https://www.tiktok.com/@technopaedia</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -38893,10 +38893,10 @@
         </is>
       </c>
       <c r="P675" s="1" t="n">
-        <v>46207.83660879629</v>
+        <v>46222.49525462963</v>
       </c>
       <c r="Q675" s="1" t="n">
-        <v>46207.83660879629</v>
+        <v>46222.49525462963</v>
       </c>
       <c r="R675" t="n">
         <v>4.8</v>
@@ -38916,12 +38916,12 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>teeto2021</t>
+          <t>teemama329</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teeto2021</t>
+          <t>https://www.tiktok.com/@teemama329</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -38930,11 +38930,7 @@
       <c r="F676" t="inlineStr"/>
       <c r="G676" t="inlineStr"/>
       <c r="H676" t="inlineStr"/>
-      <c r="I676" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I676" t="inlineStr"/>
       <c r="J676" t="inlineStr"/>
       <c r="K676" t="inlineStr"/>
       <c r="L676" t="inlineStr"/>
@@ -38952,10 +38948,10 @@
         </is>
       </c>
       <c r="P676" s="1" t="n">
-        <v>46209.51795138889</v>
+        <v>46207.83660879629</v>
       </c>
       <c r="Q676" s="1" t="n">
-        <v>46209.51795138889</v>
+        <v>46207.83660879629</v>
       </c>
       <c r="R676" t="n">
         <v>4.8</v>
@@ -38975,12 +38971,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>teewhyj31</t>
+          <t>teeto2021</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teewhyj31</t>
+          <t>https://www.tiktok.com/@teeto2021</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -38989,7 +38985,11 @@
       <c r="F677" t="inlineStr"/>
       <c r="G677" t="inlineStr"/>
       <c r="H677" t="inlineStr"/>
-      <c r="I677" t="inlineStr"/>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J677" t="inlineStr"/>
       <c r="K677" t="inlineStr"/>
       <c r="L677" t="inlineStr"/>
@@ -39007,10 +39007,10 @@
         </is>
       </c>
       <c r="P677" s="1" t="n">
-        <v>46234.72247685185</v>
+        <v>46209.51795138889</v>
       </c>
       <c r="Q677" s="1" t="n">
-        <v>46234.72247685185</v>
+        <v>46209.51795138889</v>
       </c>
       <c r="R677" t="n">
         <v>4.8</v>
@@ -39030,12 +39030,12 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>temidiresholagbad</t>
+          <t>teewhyj31</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temidiresholagbad</t>
+          <t>https://www.tiktok.com/@teewhyj31</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -39062,10 +39062,10 @@
         </is>
       </c>
       <c r="P678" s="1" t="n">
-        <v>46210.48326388889</v>
+        <v>46234.72247685185</v>
       </c>
       <c r="Q678" s="1" t="n">
-        <v>46210.48326388889</v>
+        <v>46234.72247685185</v>
       </c>
       <c r="R678" t="n">
         <v>4.8</v>
@@ -39085,12 +39085,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>temmiedee68</t>
+          <t>temidiresholagbad</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temmiedee68</t>
+          <t>https://www.tiktok.com/@temidiresholagbad</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -39108,7 +39108,7 @@
       </c>
       <c r="N679" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O679" t="inlineStr">
@@ -39117,13 +39117,13 @@
         </is>
       </c>
       <c r="P679" s="1" t="n">
-        <v>46248.75665509259</v>
+        <v>46210.48326388889</v>
       </c>
       <c r="Q679" s="1" t="n">
-        <v>46248.75665509259</v>
+        <v>46210.48326388889</v>
       </c>
       <c r="R679" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S679" t="inlineStr">
         <is>
@@ -39140,12 +39140,12 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>thaminanoore</t>
+          <t>temmiedee68</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thaminanoore</t>
+          <t>https://www.tiktok.com/@temmiedee68</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -39163,7 +39163,7 @@
       </c>
       <c r="N680" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
@@ -39172,13 +39172,13 @@
         </is>
       </c>
       <c r="P680" s="1" t="n">
-        <v>46212.65239583333</v>
+        <v>46248.75665509259</v>
       </c>
       <c r="Q680" s="1" t="n">
-        <v>46212.65239583333</v>
+        <v>46248.75665509259</v>
       </c>
       <c r="R680" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S680" t="inlineStr">
         <is>
@@ -39195,12 +39195,12 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>the.witchy.wander</t>
+          <t>thaminanoore</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the.witchy.wander</t>
+          <t>https://www.tiktok.com/@thaminanoore</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -39218,56 +39218,44 @@
       </c>
       <c r="N681" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P681" s="1" t="n">
-        <v>46196.76916666667</v>
+        <v>46212.65239583333</v>
       </c>
       <c r="Q681" s="1" t="n">
-        <v>46196.76916666667</v>
+        <v>46212.65239583333</v>
       </c>
       <c r="R681" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S681" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T681" t="n">
-        <v>1</v>
-      </c>
-      <c r="U681" t="n">
-        <v>0</v>
-      </c>
-      <c r="V681" t="n">
-        <v>0</v>
-      </c>
-      <c r="W681" t="n">
-        <v>3</v>
-      </c>
-      <c r="X681" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="Y681" t="n">
-        <v>6</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T681" t="inlineStr"/>
+      <c r="U681" t="inlineStr"/>
+      <c r="V681" t="inlineStr"/>
+      <c r="W681" t="inlineStr"/>
+      <c r="X681" t="inlineStr"/>
+      <c r="Y681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>the_akins2</t>
+          <t>the.witchy.wander</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_akins2</t>
+          <t>https://www.tiktok.com/@the.witchy.wander</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -39276,11 +39264,7 @@
       <c r="F682" t="inlineStr"/>
       <c r="G682" t="inlineStr"/>
       <c r="H682" t="inlineStr"/>
-      <c r="I682" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I682" t="inlineStr"/>
       <c r="J682" t="inlineStr"/>
       <c r="K682" t="inlineStr"/>
       <c r="L682" t="inlineStr"/>
@@ -39289,44 +39273,56 @@
       </c>
       <c r="N682" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P682" s="1" t="n">
-        <v>46222.77729166667</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="Q682" s="1" t="n">
-        <v>46222.77729166667</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="R682" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S682" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T682" t="inlineStr"/>
-      <c r="U682" t="inlineStr"/>
-      <c r="V682" t="inlineStr"/>
-      <c r="W682" t="inlineStr"/>
-      <c r="X682" t="inlineStr"/>
-      <c r="Y682" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T682" t="n">
+        <v>1</v>
+      </c>
+      <c r="U682" t="n">
+        <v>0</v>
+      </c>
+      <c r="V682" t="n">
+        <v>0</v>
+      </c>
+      <c r="W682" t="n">
+        <v>3</v>
+      </c>
+      <c r="X682" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="Y682" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>the_bulife_family</t>
+          <t>the_akins2</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_bulife_family</t>
+          <t>https://www.tiktok.com/@the_akins2</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -39335,7 +39331,11 @@
       <c r="F683" t="inlineStr"/>
       <c r="G683" t="inlineStr"/>
       <c r="H683" t="inlineStr"/>
-      <c r="I683" t="inlineStr"/>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J683" t="inlineStr"/>
       <c r="K683" t="inlineStr"/>
       <c r="L683" t="inlineStr"/>
@@ -39344,56 +39344,44 @@
       </c>
       <c r="N683" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P683" s="1" t="n">
-        <v>46225.93480324074</v>
+        <v>46222.77729166667</v>
       </c>
       <c r="Q683" s="1" t="n">
-        <v>46225.93480324074</v>
+        <v>46222.77729166667</v>
       </c>
       <c r="R683" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T683" t="n">
-        <v>1</v>
-      </c>
-      <c r="U683" t="n">
-        <v>0</v>
-      </c>
-      <c r="V683" t="n">
-        <v>0</v>
-      </c>
-      <c r="W683" t="n">
-        <v>3</v>
-      </c>
-      <c r="X683" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="Y683" t="n">
-        <v>4</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T683" t="inlineStr"/>
+      <c r="U683" t="inlineStr"/>
+      <c r="V683" t="inlineStr"/>
+      <c r="W683" t="inlineStr"/>
+      <c r="X683" t="inlineStr"/>
+      <c r="Y683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>the_kanyinsola_brand</t>
+          <t>the_bulife_family</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_kanyinsola_brand</t>
+          <t>https://www.tiktok.com/@the_bulife_family</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -39411,44 +39399,56 @@
       </c>
       <c r="N684" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P684" s="1" t="n">
-        <v>46225.71144675926</v>
+        <v>46225.93480324074</v>
       </c>
       <c r="Q684" s="1" t="n">
-        <v>46225.71144675926</v>
+        <v>46225.93480324074</v>
       </c>
       <c r="R684" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T684" t="inlineStr"/>
-      <c r="U684" t="inlineStr"/>
-      <c r="V684" t="inlineStr"/>
-      <c r="W684" t="inlineStr"/>
-      <c r="X684" t="inlineStr"/>
-      <c r="Y684" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T684" t="n">
+        <v>1</v>
+      </c>
+      <c r="U684" t="n">
+        <v>0</v>
+      </c>
+      <c r="V684" t="n">
+        <v>0</v>
+      </c>
+      <c r="W684" t="n">
+        <v>3</v>
+      </c>
+      <c r="X684" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="Y684" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>thea.w.finds</t>
+          <t>the_kanyinsola_brand</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thea.w.finds</t>
+          <t>https://www.tiktok.com/@the_kanyinsola_brand</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -39466,56 +39466,44 @@
       </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P685" s="1" t="n">
-        <v>46249.46394675926</v>
+        <v>46225.71144675926</v>
       </c>
       <c r="Q685" s="1" t="n">
-        <v>46249.46394675926</v>
+        <v>46225.71144675926</v>
       </c>
       <c r="R685" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S685" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T685" t="n">
-        <v>3</v>
-      </c>
-      <c r="U685" t="n">
-        <v>353.8</v>
-      </c>
-      <c r="V685" t="n">
-        <v>6</v>
-      </c>
-      <c r="W685" t="n">
-        <v>10391</v>
-      </c>
-      <c r="X685" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="Y685" t="n">
-        <v>-6</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T685" t="inlineStr"/>
+      <c r="U685" t="inlineStr"/>
+      <c r="V685" t="inlineStr"/>
+      <c r="W685" t="inlineStr"/>
+      <c r="X685" t="inlineStr"/>
+      <c r="Y685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>theresaboakye74</t>
+          <t>thea.w.finds</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theresaboakye74</t>
+          <t>https://www.tiktok.com/@thea.w.finds</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -39533,44 +39521,56 @@
       </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P686" s="1" t="n">
-        <v>46230.67072916667</v>
+        <v>46249.46394675926</v>
       </c>
       <c r="Q686" s="1" t="n">
-        <v>46230.67072916667</v>
+        <v>46249.46394675926</v>
       </c>
       <c r="R686" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T686" t="inlineStr"/>
-      <c r="U686" t="inlineStr"/>
-      <c r="V686" t="inlineStr"/>
-      <c r="W686" t="inlineStr"/>
-      <c r="X686" t="inlineStr"/>
-      <c r="Y686" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T686" t="n">
+        <v>3</v>
+      </c>
+      <c r="U686" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="V686" t="n">
+        <v>6</v>
+      </c>
+      <c r="W686" t="n">
+        <v>10391</v>
+      </c>
+      <c r="X686" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="Y686" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>thetripleteez</t>
+          <t>theresaboakye74</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thetripleteez</t>
+          <t>https://www.tiktok.com/@theresaboakye74</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -39588,56 +39588,44 @@
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P687" s="1" t="n">
-        <v>46198.62644675926</v>
+        <v>46230.67072916667</v>
       </c>
       <c r="Q687" s="1" t="n">
-        <v>46198.62644675926</v>
+        <v>46230.67072916667</v>
       </c>
       <c r="R687" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S687" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T687" t="n">
-        <v>1</v>
-      </c>
-      <c r="U687" t="n">
-        <v>0</v>
-      </c>
-      <c r="V687" t="n">
-        <v>0</v>
-      </c>
-      <c r="W687" t="n">
-        <v>5</v>
-      </c>
-      <c r="X687" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="Y687" t="n">
-        <v>1</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T687" t="inlineStr"/>
+      <c r="U687" t="inlineStr"/>
+      <c r="V687" t="inlineStr"/>
+      <c r="W687" t="inlineStr"/>
+      <c r="X687" t="inlineStr"/>
+      <c r="Y687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>thumandpea123</t>
+          <t>thetripleteez</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thumandpea123</t>
+          <t>https://www.tiktok.com/@thetripleteez</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -39655,44 +39643,56 @@
       </c>
       <c r="N688" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P688" s="1" t="n">
-        <v>46219.8472800926</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="Q688" s="1" t="n">
-        <v>46219.8472800926</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="R688" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S688" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T688" t="inlineStr"/>
-      <c r="U688" t="inlineStr"/>
-      <c r="V688" t="inlineStr"/>
-      <c r="W688" t="inlineStr"/>
-      <c r="X688" t="inlineStr"/>
-      <c r="Y688" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T688" t="n">
+        <v>1</v>
+      </c>
+      <c r="U688" t="n">
+        <v>0</v>
+      </c>
+      <c r="V688" t="n">
+        <v>0</v>
+      </c>
+      <c r="W688" t="n">
+        <v>5</v>
+      </c>
+      <c r="X688" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="Y688" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>tifeyhslash</t>
+          <t>thumandpea123</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tifeyhslash</t>
+          <t>https://www.tiktok.com/@thumandpea123</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -39710,56 +39710,44 @@
       </c>
       <c r="N689" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P689" s="1" t="n">
-        <v>46220.44594907408</v>
+        <v>46219.8472800926</v>
       </c>
       <c r="Q689" s="1" t="n">
-        <v>46220.44594907408</v>
+        <v>46219.8472800926</v>
       </c>
       <c r="R689" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S689" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T689" t="n">
-        <v>1</v>
-      </c>
-      <c r="U689" t="n">
-        <v>0</v>
-      </c>
-      <c r="V689" t="n">
-        <v>0</v>
-      </c>
-      <c r="W689" t="n">
-        <v>7</v>
-      </c>
-      <c r="X689" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="Y689" t="n">
-        <v>5</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T689" t="inlineStr"/>
+      <c r="U689" t="inlineStr"/>
+      <c r="V689" t="inlineStr"/>
+      <c r="W689" t="inlineStr"/>
+      <c r="X689" t="inlineStr"/>
+      <c r="Y689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>tiktok.comusershaza</t>
+          <t>tifeyhslash</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktok.comusershaza</t>
+          <t>https://www.tiktok.com/@tifeyhslash</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -39777,44 +39765,56 @@
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P690" s="1" t="n">
-        <v>46234.01479166667</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="Q690" s="1" t="n">
-        <v>46234.01479166667</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="R690" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S690" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T690" t="inlineStr"/>
-      <c r="U690" t="inlineStr"/>
-      <c r="V690" t="inlineStr"/>
-      <c r="W690" t="inlineStr"/>
-      <c r="X690" t="inlineStr"/>
-      <c r="Y690" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T690" t="n">
+        <v>1</v>
+      </c>
+      <c r="U690" t="n">
+        <v>0</v>
+      </c>
+      <c r="V690" t="n">
+        <v>0</v>
+      </c>
+      <c r="W690" t="n">
+        <v>7</v>
+      </c>
+      <c r="X690" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Y690" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>tiktokshop19944</t>
+          <t>tiktok.comusershaza</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktokshop19944</t>
+          <t>https://www.tiktok.com/@tiktok.comusershaza</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
@@ -39832,56 +39832,44 @@
       </c>
       <c r="N691" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P691" s="1" t="n">
-        <v>46221.60188657408</v>
+        <v>46234.01479166667</v>
       </c>
       <c r="Q691" s="1" t="n">
-        <v>46221.60188657408</v>
+        <v>46234.01479166667</v>
       </c>
       <c r="R691" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S691" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T691" t="n">
-        <v>1</v>
-      </c>
-      <c r="U691" t="n">
-        <v>0</v>
-      </c>
-      <c r="V691" t="n">
-        <v>0</v>
-      </c>
-      <c r="W691" t="n">
-        <v>5</v>
-      </c>
-      <c r="X691" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="Y691" t="n">
-        <v>4</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T691" t="inlineStr"/>
+      <c r="U691" t="inlineStr"/>
+      <c r="V691" t="inlineStr"/>
+      <c r="W691" t="inlineStr"/>
+      <c r="X691" t="inlineStr"/>
+      <c r="Y691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>tiktokuserssssssww</t>
+          <t>tiktokshop19944</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktokuserssssssww</t>
+          <t>https://www.tiktok.com/@tiktokshop19944</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -39904,39 +39892,51 @@
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P692" s="1" t="n">
-        <v>46201.06403935186</v>
+        <v>46221.60188657408</v>
       </c>
       <c r="Q692" s="1" t="n">
-        <v>46201.06403935186</v>
+        <v>46221.60188657408</v>
       </c>
       <c r="R692" t="n">
         <v>6</v>
       </c>
       <c r="S692" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T692" t="inlineStr"/>
-      <c r="U692" t="inlineStr"/>
-      <c r="V692" t="inlineStr"/>
-      <c r="W692" t="inlineStr"/>
-      <c r="X692" t="inlineStr"/>
-      <c r="Y692" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T692" t="n">
+        <v>1</v>
+      </c>
+      <c r="U692" t="n">
+        <v>0</v>
+      </c>
+      <c r="V692" t="n">
+        <v>0</v>
+      </c>
+      <c r="W692" t="n">
+        <v>5</v>
+      </c>
+      <c r="X692" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Y692" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>tinamwie</t>
+          <t>tiktokuserssssssww</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinamwie</t>
+          <t>https://www.tiktok.com/@tiktokuserssssssww</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -39954,7 +39954,7 @@
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
@@ -39963,13 +39963,13 @@
         </is>
       </c>
       <c r="P693" s="1" t="n">
-        <v>46224.66335648148</v>
+        <v>46201.06403935186</v>
       </c>
       <c r="Q693" s="1" t="n">
-        <v>46224.66335648148</v>
+        <v>46201.06403935186</v>
       </c>
       <c r="R693" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S693" t="inlineStr">
         <is>
@@ -39986,12 +39986,12 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>tinash1330</t>
+          <t>tinamwie</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinash1330</t>
+          <t>https://www.tiktok.com/@tinamwie</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
@@ -40018,10 +40018,10 @@
         </is>
       </c>
       <c r="P694" s="1" t="n">
-        <v>46221.52363425926</v>
+        <v>46224.66335648148</v>
       </c>
       <c r="Q694" s="1" t="n">
-        <v>46221.52363425926</v>
+        <v>46224.66335648148</v>
       </c>
       <c r="R694" t="n">
         <v>4.8</v>
@@ -40041,12 +40041,12 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>tinashairandbeauty</t>
+          <t>tinash1330</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinashairandbeauty</t>
+          <t>https://www.tiktok.com/@tinash1330</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -40064,7 +40064,7 @@
       </c>
       <c r="N695" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
@@ -40073,13 +40073,13 @@
         </is>
       </c>
       <c r="P695" s="1" t="n">
-        <v>46153.36642361111</v>
+        <v>46221.52363425926</v>
       </c>
       <c r="Q695" s="1" t="n">
-        <v>46153.36642361111</v>
+        <v>46221.52363425926</v>
       </c>
       <c r="R695" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S695" t="inlineStr">
         <is>
@@ -40096,12 +40096,12 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>tinugold123</t>
+          <t>tinashairandbeauty</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinugold123</t>
+          <t>https://www.tiktok.com/@tinashairandbeauty</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -40128,10 +40128,10 @@
         </is>
       </c>
       <c r="P696" s="1" t="n">
-        <v>46238.029375</v>
+        <v>46153.36642361111</v>
       </c>
       <c r="Q696" s="1" t="n">
-        <v>46238.029375</v>
+        <v>46153.36642361111</v>
       </c>
       <c r="R696" t="n">
         <v>6</v>
@@ -40151,12 +40151,12 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>tirzahbyoneal</t>
+          <t>tinugold123</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tirzahbyoneal</t>
+          <t>https://www.tiktok.com/@tinugold123</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -40183,10 +40183,10 @@
         </is>
       </c>
       <c r="P697" s="1" t="n">
-        <v>46201.90878472223</v>
+        <v>46238.029375</v>
       </c>
       <c r="Q697" s="1" t="n">
-        <v>46201.90878472223</v>
+        <v>46238.029375</v>
       </c>
       <c r="R697" t="n">
         <v>6</v>
@@ -40206,12 +40206,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>titiagboola</t>
+          <t>tirzahbyoneal</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@titiagboola</t>
+          <t>https://www.tiktok.com/@tirzahbyoneal</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -40229,7 +40229,7 @@
       </c>
       <c r="N698" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
@@ -40238,13 +40238,13 @@
         </is>
       </c>
       <c r="P698" s="1" t="n">
-        <v>46209.72179398148</v>
+        <v>46201.90878472223</v>
       </c>
       <c r="Q698" s="1" t="n">
-        <v>46209.72179398148</v>
+        <v>46201.90878472223</v>
       </c>
       <c r="R698" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S698" t="inlineStr">
         <is>
@@ -40261,12 +40261,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>titilayosanusi</t>
+          <t>titiagboola</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@titilayosanusi</t>
+          <t>https://www.tiktok.com/@titiagboola</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -40275,11 +40275,7 @@
       <c r="F699" t="inlineStr"/>
       <c r="G699" t="inlineStr"/>
       <c r="H699" t="inlineStr"/>
-      <c r="I699" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I699" t="inlineStr"/>
       <c r="J699" t="inlineStr"/>
       <c r="K699" t="inlineStr"/>
       <c r="L699" t="inlineStr"/>
@@ -40297,10 +40293,10 @@
         </is>
       </c>
       <c r="P699" s="1" t="n">
-        <v>46217.10659722222</v>
+        <v>46209.72179398148</v>
       </c>
       <c r="Q699" s="1" t="n">
-        <v>46217.10659722222</v>
+        <v>46209.72179398148</v>
       </c>
       <c r="R699" t="n">
         <v>4.8</v>
@@ -40320,12 +40316,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>titty.titty8</t>
+          <t>titilayosanusi</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@titty.titty8</t>
+          <t>https://www.tiktok.com/@titilayosanusi</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -40334,7 +40330,11 @@
       <c r="F700" t="inlineStr"/>
       <c r="G700" t="inlineStr"/>
       <c r="H700" t="inlineStr"/>
-      <c r="I700" t="inlineStr"/>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J700" t="inlineStr"/>
       <c r="K700" t="inlineStr"/>
       <c r="L700" t="inlineStr"/>
@@ -40352,10 +40352,10 @@
         </is>
       </c>
       <c r="P700" s="1" t="n">
-        <v>46218.68445601852</v>
+        <v>46217.10659722222</v>
       </c>
       <c r="Q700" s="1" t="n">
-        <v>46218.68445601852</v>
+        <v>46217.10659722222</v>
       </c>
       <c r="R700" t="n">
         <v>4.8</v>
@@ -40375,12 +40375,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>to_biiiii1</t>
+          <t>titty.titty8</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@to_biiiii1</t>
+          <t>https://www.tiktok.com/@titty.titty8</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -40398,7 +40398,7 @@
       </c>
       <c r="N701" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O701" t="inlineStr">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="P701" s="1" t="n">
-        <v>46250.35457175926</v>
+        <v>46218.68445601852</v>
       </c>
       <c r="Q701" s="1" t="n">
-        <v>46250.35457175926</v>
+        <v>46218.68445601852</v>
       </c>
       <c r="R701" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S701" t="inlineStr">
         <is>
@@ -40430,12 +40430,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>tolaniogunlesi998</t>
+          <t>to_biiiii1</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tolaniogunlesi998</t>
+          <t>https://www.tiktok.com/@to_biiiii1</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -40444,11 +40444,7 @@
       <c r="F702" t="inlineStr"/>
       <c r="G702" t="inlineStr"/>
       <c r="H702" t="inlineStr"/>
-      <c r="I702" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I702" t="inlineStr"/>
       <c r="J702" t="inlineStr"/>
       <c r="K702" t="inlineStr"/>
       <c r="L702" t="inlineStr"/>
@@ -40457,7 +40453,7 @@
       </c>
       <c r="N702" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O702" t="inlineStr">
@@ -40466,13 +40462,13 @@
         </is>
       </c>
       <c r="P702" s="1" t="n">
-        <v>46216.5428587963</v>
+        <v>46250.35457175926</v>
       </c>
       <c r="Q702" s="1" t="n">
-        <v>46216.5428587963</v>
+        <v>46250.35457175926</v>
       </c>
       <c r="R702" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S702" t="inlineStr">
         <is>
@@ -40489,12 +40485,12 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>tomo.265</t>
+          <t>tolaniogunlesi998</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tomo.265</t>
+          <t>https://www.tiktok.com/@tolaniogunlesi998</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -40503,7 +40499,11 @@
       <c r="F703" t="inlineStr"/>
       <c r="G703" t="inlineStr"/>
       <c r="H703" t="inlineStr"/>
-      <c r="I703" t="inlineStr"/>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J703" t="inlineStr"/>
       <c r="K703" t="inlineStr"/>
       <c r="L703" t="inlineStr"/>
@@ -40521,10 +40521,10 @@
         </is>
       </c>
       <c r="P703" s="1" t="n">
-        <v>46227.50211805556</v>
+        <v>46216.5428587963</v>
       </c>
       <c r="Q703" s="1" t="n">
-        <v>46227.50211805556</v>
+        <v>46216.5428587963</v>
       </c>
       <c r="R703" t="n">
         <v>4.8</v>
@@ -40544,12 +40544,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>tony03672</t>
+          <t>tomo.265</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tony03672</t>
+          <t>https://www.tiktok.com/@tomo.265</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -40567,22 +40567,22 @@
       </c>
       <c r="N704" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P704" s="1" t="n">
-        <v>45993.6759375</v>
+        <v>46227.50211805556</v>
       </c>
       <c r="Q704" s="1" t="n">
-        <v>45993.6759375</v>
+        <v>46227.50211805556</v>
       </c>
       <c r="R704" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="S704" t="inlineStr">
         <is>
@@ -40599,12 +40599,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>topinsonjoe</t>
+          <t>tony03672</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topinsonjoe</t>
+          <t>https://www.tiktok.com/@tony03672</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -40622,22 +40622,22 @@
       </c>
       <c r="N705" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P705" s="1" t="n">
-        <v>46219.29</v>
+        <v>45993.6759375</v>
       </c>
       <c r="Q705" s="1" t="n">
-        <v>46219.29</v>
+        <v>45993.6759375</v>
       </c>
       <c r="R705" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S705" t="inlineStr">
         <is>
@@ -40654,12 +40654,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>toyin.georgetaylo</t>
+          <t>topinsonjoe</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toyin.georgetaylo</t>
+          <t>https://www.tiktok.com/@topinsonjoe</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -40686,10 +40686,10 @@
         </is>
       </c>
       <c r="P706" s="1" t="n">
-        <v>46220.63767361111</v>
+        <v>46219.29</v>
       </c>
       <c r="Q706" s="1" t="n">
-        <v>46220.63767361111</v>
+        <v>46219.29</v>
       </c>
       <c r="R706" t="n">
         <v>4.8</v>
@@ -40709,12 +40709,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>toyinedos</t>
+          <t>toyin.georgetaylo</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toyinedos</t>
+          <t>https://www.tiktok.com/@toyin.georgetaylo</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -40741,10 +40741,10 @@
         </is>
       </c>
       <c r="P707" s="1" t="n">
-        <v>46238.3083912037</v>
+        <v>46220.63767361111</v>
       </c>
       <c r="Q707" s="1" t="n">
-        <v>46238.3083912037</v>
+        <v>46220.63767361111</v>
       </c>
       <c r="R707" t="n">
         <v>4.8</v>
@@ -40764,12 +40764,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>traetari1</t>
+          <t>toyinedos</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@traetari1</t>
+          <t>https://www.tiktok.com/@toyinedos</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -40778,11 +40778,7 @@
       <c r="F708" t="inlineStr"/>
       <c r="G708" t="inlineStr"/>
       <c r="H708" t="inlineStr"/>
-      <c r="I708" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I708" t="inlineStr"/>
       <c r="J708" t="inlineStr"/>
       <c r="K708" t="inlineStr"/>
       <c r="L708" t="inlineStr"/>
@@ -40800,10 +40796,10 @@
         </is>
       </c>
       <c r="P708" s="1" t="n">
-        <v>46238.87353009259</v>
+        <v>46238.3083912037</v>
       </c>
       <c r="Q708" s="1" t="n">
-        <v>46238.87353009259</v>
+        <v>46238.3083912037</v>
       </c>
       <c r="R708" t="n">
         <v>4.8</v>
@@ -40823,12 +40819,12 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>treasure.lope</t>
+          <t>traetari1</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@treasure.lope</t>
+          <t>https://www.tiktok.com/@traetari1</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -40839,7 +40835,7 @@
       <c r="H709" t="inlineStr"/>
       <c r="I709" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J709" t="inlineStr"/>
@@ -40859,10 +40855,10 @@
         </is>
       </c>
       <c r="P709" s="1" t="n">
-        <v>46207.89181712963</v>
+        <v>46238.87353009259</v>
       </c>
       <c r="Q709" s="1" t="n">
-        <v>46207.89181712963</v>
+        <v>46238.87353009259</v>
       </c>
       <c r="R709" t="n">
         <v>4.8</v>
@@ -40882,12 +40878,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>treasurerealm64</t>
+          <t>treasure.lope</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@treasurerealm64</t>
+          <t>https://www.tiktok.com/@treasure.lope</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -40896,7 +40892,11 @@
       <c r="F710" t="inlineStr"/>
       <c r="G710" t="inlineStr"/>
       <c r="H710" t="inlineStr"/>
-      <c r="I710" t="inlineStr"/>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J710" t="inlineStr"/>
       <c r="K710" t="inlineStr"/>
       <c r="L710" t="inlineStr"/>
@@ -40914,10 +40914,10 @@
         </is>
       </c>
       <c r="P710" s="1" t="n">
-        <v>46230.82032407408</v>
+        <v>46207.89181712963</v>
       </c>
       <c r="Q710" s="1" t="n">
-        <v>46230.82032407408</v>
+        <v>46207.89181712963</v>
       </c>
       <c r="R710" t="n">
         <v>4.8</v>
@@ -40937,12 +40937,12 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>tricia.xo1</t>
+          <t>treasurerealm64</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tricia.xo1</t>
+          <t>https://www.tiktok.com/@treasurerealm64</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -40951,11 +40951,7 @@
       <c r="F711" t="inlineStr"/>
       <c r="G711" t="inlineStr"/>
       <c r="H711" t="inlineStr"/>
-      <c r="I711" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I711" t="inlineStr"/>
       <c r="J711" t="inlineStr"/>
       <c r="K711" t="inlineStr"/>
       <c r="L711" t="inlineStr"/>
@@ -40973,10 +40969,10 @@
         </is>
       </c>
       <c r="P711" s="1" t="n">
-        <v>46209.36672453704</v>
+        <v>46230.82032407408</v>
       </c>
       <c r="Q711" s="1" t="n">
-        <v>46209.36672453704</v>
+        <v>46230.82032407408</v>
       </c>
       <c r="R711" t="n">
         <v>4.8</v>
@@ -40996,12 +40992,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>triplehoney8</t>
+          <t>tricia.xo1</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triplehoney8</t>
+          <t>https://www.tiktok.com/@tricia.xo1</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -41010,7 +41006,11 @@
       <c r="F712" t="inlineStr"/>
       <c r="G712" t="inlineStr"/>
       <c r="H712" t="inlineStr"/>
-      <c r="I712" t="inlineStr"/>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J712" t="inlineStr"/>
       <c r="K712" t="inlineStr"/>
       <c r="L712" t="inlineStr"/>
@@ -41028,10 +41028,10 @@
         </is>
       </c>
       <c r="P712" s="1" t="n">
-        <v>46239.38399305556</v>
+        <v>46209.36672453704</v>
       </c>
       <c r="Q712" s="1" t="n">
-        <v>46239.38399305556</v>
+        <v>46209.36672453704</v>
       </c>
       <c r="R712" t="n">
         <v>4.8</v>
@@ -41051,12 +41051,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>truesizetryons</t>
+          <t>triplehoney8</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@truesizetryons</t>
+          <t>https://www.tiktok.com/@triplehoney8</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -41074,22 +41074,22 @@
       </c>
       <c r="N713" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P713" s="1" t="n">
-        <v>46210.49572916667</v>
+        <v>46239.38399305556</v>
       </c>
       <c r="Q713" s="1" t="n">
-        <v>46210.49572916667</v>
+        <v>46239.38399305556</v>
       </c>
       <c r="R713" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S713" t="inlineStr">
         <is>
@@ -41106,12 +41106,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>tuturasdumitru</t>
+          <t>truesizetryons</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tuturasdumitru</t>
+          <t>https://www.tiktok.com/@truesizetryons</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
@@ -41129,22 +41129,22 @@
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P714" s="1" t="n">
-        <v>46208.76107638889</v>
+        <v>46210.49572916667</v>
       </c>
       <c r="Q714" s="1" t="n">
-        <v>46208.76107638889</v>
+        <v>46210.49572916667</v>
       </c>
       <c r="R714" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S714" t="inlineStr">
         <is>
@@ -41161,12 +41161,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>twasjael</t>
+          <t>tuturasdumitru</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@twasjael</t>
+          <t>https://www.tiktok.com/@tuturasdumitru</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
@@ -41175,11 +41175,7 @@
       <c r="F715" t="inlineStr"/>
       <c r="G715" t="inlineStr"/>
       <c r="H715" t="inlineStr"/>
-      <c r="I715" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I715" t="inlineStr"/>
       <c r="J715" t="inlineStr"/>
       <c r="K715" t="inlineStr"/>
       <c r="L715" t="inlineStr"/>
@@ -41197,10 +41193,10 @@
         </is>
       </c>
       <c r="P715" s="1" t="n">
-        <v>46232.34398148148</v>
+        <v>46208.76107638889</v>
       </c>
       <c r="Q715" s="1" t="n">
-        <v>46232.34398148148</v>
+        <v>46208.76107638889</v>
       </c>
       <c r="R715" t="n">
         <v>4.8</v>
@@ -41220,12 +41216,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>uh.numnumnum</t>
+          <t>twasjael</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uh.numnumnum</t>
+          <t>https://www.tiktok.com/@twasjael</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
@@ -41234,7 +41230,11 @@
       <c r="F716" t="inlineStr"/>
       <c r="G716" t="inlineStr"/>
       <c r="H716" t="inlineStr"/>
-      <c r="I716" t="inlineStr"/>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J716" t="inlineStr"/>
       <c r="K716" t="inlineStr"/>
       <c r="L716" t="inlineStr"/>
@@ -41252,10 +41252,10 @@
         </is>
       </c>
       <c r="P716" s="1" t="n">
-        <v>46226.59572916666</v>
+        <v>46232.34398148148</v>
       </c>
       <c r="Q716" s="1" t="n">
-        <v>46226.59572916666</v>
+        <v>46232.34398148148</v>
       </c>
       <c r="R716" t="n">
         <v>4.8</v>
@@ -41275,12 +41275,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>ukhtimuslima21</t>
+          <t>uh.numnumnum</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ukhtimuslima21</t>
+          <t>https://www.tiktok.com/@uh.numnumnum</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
@@ -41307,10 +41307,10 @@
         </is>
       </c>
       <c r="P717" s="1" t="n">
-        <v>46224.76721064815</v>
+        <v>46226.59572916666</v>
       </c>
       <c r="Q717" s="1" t="n">
-        <v>46224.76721064815</v>
+        <v>46226.59572916666</v>
       </c>
       <c r="R717" t="n">
         <v>4.8</v>
@@ -41330,12 +41330,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>umaadhussain</t>
+          <t>ukhtimuslima21</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@umaadhussain</t>
+          <t>https://www.tiktok.com/@ukhtimuslima21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
@@ -41344,11 +41344,7 @@
       <c r="F718" t="inlineStr"/>
       <c r="G718" t="inlineStr"/>
       <c r="H718" t="inlineStr"/>
-      <c r="I718" t="inlineStr">
-        <is>
-          <t>Middle Eastern/Arab</t>
-        </is>
-      </c>
+      <c r="I718" t="inlineStr"/>
       <c r="J718" t="inlineStr"/>
       <c r="K718" t="inlineStr"/>
       <c r="L718" t="inlineStr"/>
@@ -41366,10 +41362,10 @@
         </is>
       </c>
       <c r="P718" s="1" t="n">
-        <v>46209.50694444445</v>
+        <v>46224.76721064815</v>
       </c>
       <c r="Q718" s="1" t="n">
-        <v>46209.50694444445</v>
+        <v>46224.76721064815</v>
       </c>
       <c r="R718" t="n">
         <v>4.8</v>
@@ -41389,12 +41385,12 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>urlovemakisedits2</t>
+          <t>umaadhussain</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@urlovemakisedits2</t>
+          <t>https://www.tiktok.com/@umaadhussain</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
@@ -41403,7 +41399,11 @@
       <c r="F719" t="inlineStr"/>
       <c r="G719" t="inlineStr"/>
       <c r="H719" t="inlineStr"/>
-      <c r="I719" t="inlineStr"/>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J719" t="inlineStr"/>
       <c r="K719" t="inlineStr"/>
       <c r="L719" t="inlineStr"/>
@@ -41421,10 +41421,10 @@
         </is>
       </c>
       <c r="P719" s="1" t="n">
-        <v>46223.48380787037</v>
+        <v>46209.50694444445</v>
       </c>
       <c r="Q719" s="1" t="n">
-        <v>46223.48380787037</v>
+        <v>46209.50694444445</v>
       </c>
       <c r="R719" t="n">
         <v>4.8</v>
@@ -41444,12 +41444,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>user003204305</t>
+          <t>urlovemakisedits2</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user003204305</t>
+          <t>https://www.tiktok.com/@urlovemakisedits2</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -41476,10 +41476,10 @@
         </is>
       </c>
       <c r="P720" s="1" t="n">
-        <v>46207.6971412037</v>
+        <v>46223.48380787037</v>
       </c>
       <c r="Q720" s="1" t="n">
-        <v>46207.6971412037</v>
+        <v>46223.48380787037</v>
       </c>
       <c r="R720" t="n">
         <v>4.8</v>
@@ -41499,12 +41499,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>user13822840075788</t>
+          <t>user003204305</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user13822840075788</t>
+          <t>https://www.tiktok.com/@user003204305</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -41531,10 +41531,10 @@
         </is>
       </c>
       <c r="P721" s="1" t="n">
-        <v>46210.92520833333</v>
+        <v>46207.6971412037</v>
       </c>
       <c r="Q721" s="1" t="n">
-        <v>46210.92520833333</v>
+        <v>46207.6971412037</v>
       </c>
       <c r="R721" t="n">
         <v>4.8</v>
@@ -41554,12 +41554,12 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>user1466702213394</t>
+          <t>user13822840075788</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user1466702213394</t>
+          <t>https://www.tiktok.com/@user13822840075788</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
@@ -41568,11 +41568,7 @@
       <c r="F722" t="inlineStr"/>
       <c r="G722" t="inlineStr"/>
       <c r="H722" t="inlineStr"/>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t>Hispanic/Latino</t>
-        </is>
-      </c>
+      <c r="I722" t="inlineStr"/>
       <c r="J722" t="inlineStr"/>
       <c r="K722" t="inlineStr"/>
       <c r="L722" t="inlineStr"/>
@@ -41590,10 +41586,10 @@
         </is>
       </c>
       <c r="P722" s="1" t="n">
-        <v>46234.47584490741</v>
+        <v>46210.92520833333</v>
       </c>
       <c r="Q722" s="1" t="n">
-        <v>46234.47584490741</v>
+        <v>46210.92520833333</v>
       </c>
       <c r="R722" t="n">
         <v>4.8</v>
@@ -41613,12 +41609,12 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>user1524873803257</t>
+          <t>user1466702213394</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user1524873803257</t>
+          <t>https://www.tiktok.com/@user1466702213394</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
@@ -41627,7 +41623,11 @@
       <c r="F723" t="inlineStr"/>
       <c r="G723" t="inlineStr"/>
       <c r="H723" t="inlineStr"/>
-      <c r="I723" t="inlineStr"/>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
       <c r="J723" t="inlineStr"/>
       <c r="K723" t="inlineStr"/>
       <c r="L723" t="inlineStr"/>
@@ -41645,10 +41645,10 @@
         </is>
       </c>
       <c r="P723" s="1" t="n">
-        <v>46227.23572916666</v>
+        <v>46234.47584490741</v>
       </c>
       <c r="Q723" s="1" t="n">
-        <v>46227.23572916666</v>
+        <v>46234.47584490741</v>
       </c>
       <c r="R723" t="n">
         <v>4.8</v>
@@ -41668,12 +41668,12 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>user15510211574576</t>
+          <t>user1524873803257</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user15510211574576</t>
+          <t>https://www.tiktok.com/@user1524873803257</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
@@ -41700,10 +41700,10 @@
         </is>
       </c>
       <c r="P724" s="1" t="n">
-        <v>46210.85340277778</v>
+        <v>46227.23572916666</v>
       </c>
       <c r="Q724" s="1" t="n">
-        <v>46210.85340277778</v>
+        <v>46227.23572916666</v>
       </c>
       <c r="R724" t="n">
         <v>4.8</v>
@@ -41723,12 +41723,12 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>user167101076</t>
+          <t>user15510211574576</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user167101076</t>
+          <t>https://www.tiktok.com/@user15510211574576</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
@@ -41746,56 +41746,44 @@
       </c>
       <c r="N725" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P725" s="1" t="n">
-        <v>46226.00116898148</v>
+        <v>46210.85340277778</v>
       </c>
       <c r="Q725" s="1" t="n">
-        <v>46226.00116898148</v>
+        <v>46210.85340277778</v>
       </c>
       <c r="R725" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S725" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T725" t="n">
-        <v>1</v>
-      </c>
-      <c r="U725" t="n">
-        <v>41.99</v>
-      </c>
-      <c r="V725" t="n">
-        <v>1</v>
-      </c>
-      <c r="W725" t="n">
-        <v>1</v>
-      </c>
-      <c r="X725" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="Y725" t="n">
-        <v>3</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T725" t="inlineStr"/>
+      <c r="U725" t="inlineStr"/>
+      <c r="V725" t="inlineStr"/>
+      <c r="W725" t="inlineStr"/>
+      <c r="X725" t="inlineStr"/>
+      <c r="Y725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>user1849538441054</t>
+          <t>user167101076</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user1849538441054</t>
+          <t>https://www.tiktok.com/@user167101076</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
@@ -41813,44 +41801,56 @@
       </c>
       <c r="N726" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P726" s="1" t="n">
-        <v>46234.65694444445</v>
+        <v>46226.00116898148</v>
       </c>
       <c r="Q726" s="1" t="n">
-        <v>46234.65694444445</v>
+        <v>46226.00116898148</v>
       </c>
       <c r="R726" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S726" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T726" t="inlineStr"/>
-      <c r="U726" t="inlineStr"/>
-      <c r="V726" t="inlineStr"/>
-      <c r="W726" t="inlineStr"/>
-      <c r="X726" t="inlineStr"/>
-      <c r="Y726" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T726" t="n">
+        <v>1</v>
+      </c>
+      <c r="U726" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="V726" t="n">
+        <v>1</v>
+      </c>
+      <c r="W726" t="n">
+        <v>1</v>
+      </c>
+      <c r="X726" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="Y726" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>user2067381855385</t>
+          <t>user1849538441054</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2067381855385</t>
+          <t>https://www.tiktok.com/@user1849538441054</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -41877,10 +41877,10 @@
         </is>
       </c>
       <c r="P727" s="1" t="n">
-        <v>46215.89106481482</v>
+        <v>46234.65694444445</v>
       </c>
       <c r="Q727" s="1" t="n">
-        <v>46215.89106481482</v>
+        <v>46234.65694444445</v>
       </c>
       <c r="R727" t="n">
         <v>4.8</v>
@@ -41900,12 +41900,12 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>user2133928667610</t>
+          <t>user2067381855385</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2133928667610</t>
+          <t>https://www.tiktok.com/@user2067381855385</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -41932,10 +41932,10 @@
         </is>
       </c>
       <c r="P728" s="1" t="n">
-        <v>46238.9434837963</v>
+        <v>46215.89106481482</v>
       </c>
       <c r="Q728" s="1" t="n">
-        <v>46238.9434837963</v>
+        <v>46215.89106481482</v>
       </c>
       <c r="R728" t="n">
         <v>4.8</v>
@@ -41955,12 +41955,12 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>user24484259047033</t>
+          <t>user2133928667610</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user24484259047033</t>
+          <t>https://www.tiktok.com/@user2133928667610</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
@@ -41978,7 +41978,7 @@
       </c>
       <c r="N729" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O729" t="inlineStr">
@@ -41987,13 +41987,13 @@
         </is>
       </c>
       <c r="P729" s="1" t="n">
-        <v>46178.61515046296</v>
+        <v>46238.9434837963</v>
       </c>
       <c r="Q729" s="1" t="n">
-        <v>46178.61515046296</v>
+        <v>46238.9434837963</v>
       </c>
       <c r="R729" t="n">
-        <v>12.4</v>
+        <v>4.8</v>
       </c>
       <c r="S729" t="inlineStr">
         <is>
@@ -42010,12 +42010,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>user2499773111198</t>
+          <t>user24484259047033</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2499773111198</t>
+          <t>https://www.tiktok.com/@user24484259047033</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -42033,7 +42033,7 @@
       </c>
       <c r="N730" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O730" t="inlineStr">
@@ -42042,13 +42042,13 @@
         </is>
       </c>
       <c r="P730" s="1" t="n">
-        <v>46225.03729166667</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="Q730" s="1" t="n">
-        <v>46225.03729166667</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="R730" t="n">
-        <v>4.8</v>
+        <v>12.4</v>
       </c>
       <c r="S730" t="inlineStr">
         <is>
@@ -42065,12 +42065,12 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>user2509825076594</t>
+          <t>user2499773111198</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2509825076594</t>
+          <t>https://www.tiktok.com/@user2499773111198</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -42079,11 +42079,7 @@
       <c r="F731" t="inlineStr"/>
       <c r="G731" t="inlineStr"/>
       <c r="H731" t="inlineStr"/>
-      <c r="I731" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I731" t="inlineStr"/>
       <c r="J731" t="inlineStr"/>
       <c r="K731" t="inlineStr"/>
       <c r="L731" t="inlineStr"/>
@@ -42101,10 +42097,10 @@
         </is>
       </c>
       <c r="P731" s="1" t="n">
-        <v>46231.6984837963</v>
+        <v>46225.03729166667</v>
       </c>
       <c r="Q731" s="1" t="n">
-        <v>46231.6984837963</v>
+        <v>46225.03729166667</v>
       </c>
       <c r="R731" t="n">
         <v>4.8</v>
@@ -42124,12 +42120,12 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>user2611154757676</t>
+          <t>user2509825076594</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2611154757676</t>
+          <t>https://www.tiktok.com/@user2509825076594</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -42160,10 +42156,10 @@
         </is>
       </c>
       <c r="P732" s="1" t="n">
-        <v>46231.88670138889</v>
+        <v>46231.6984837963</v>
       </c>
       <c r="Q732" s="1" t="n">
-        <v>46231.88670138889</v>
+        <v>46231.6984837963</v>
       </c>
       <c r="R732" t="n">
         <v>4.8</v>
@@ -42183,12 +42179,12 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>user2997965690229</t>
+          <t>user2611154757676</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2997965690229</t>
+          <t>https://www.tiktok.com/@user2611154757676</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -42210,22 +42206,22 @@
       </c>
       <c r="N733" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P733" s="1" t="n">
-        <v>46248.79699074074</v>
+        <v>46231.88670138889</v>
       </c>
       <c r="Q733" s="1" t="n">
-        <v>46248.79699074074</v>
+        <v>46231.88670138889</v>
       </c>
       <c r="R733" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S733" t="inlineStr">
         <is>
@@ -42242,12 +42238,12 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>user3002455420</t>
+          <t>user2997965690229</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3002455420</t>
+          <t>https://www.tiktok.com/@user2997965690229</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -42256,7 +42252,11 @@
       <c r="F734" t="inlineStr"/>
       <c r="G734" t="inlineStr"/>
       <c r="H734" t="inlineStr"/>
-      <c r="I734" t="inlineStr"/>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J734" t="inlineStr"/>
       <c r="K734" t="inlineStr"/>
       <c r="L734" t="inlineStr"/>
@@ -42265,22 +42265,22 @@
       </c>
       <c r="N734" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P734" s="1" t="n">
-        <v>46225.82162037037</v>
+        <v>46248.79699074074</v>
       </c>
       <c r="Q734" s="1" t="n">
-        <v>46225.82162037037</v>
+        <v>46248.79699074074</v>
       </c>
       <c r="R734" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S734" t="inlineStr">
         <is>
@@ -42297,12 +42297,12 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>user307169220</t>
+          <t>user3002455420</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user307169220</t>
+          <t>https://www.tiktok.com/@user3002455420</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
@@ -42329,10 +42329,10 @@
         </is>
       </c>
       <c r="P735" s="1" t="n">
-        <v>46222.65678240741</v>
+        <v>46225.82162037037</v>
       </c>
       <c r="Q735" s="1" t="n">
-        <v>46222.65678240741</v>
+        <v>46225.82162037037</v>
       </c>
       <c r="R735" t="n">
         <v>4.8</v>
@@ -42352,12 +42352,12 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>user3606227777348</t>
+          <t>user307169220</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3606227777348</t>
+          <t>https://www.tiktok.com/@user307169220</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
@@ -42375,7 +42375,7 @@
       </c>
       <c r="N736" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O736" t="inlineStr">
@@ -42384,13 +42384,13 @@
         </is>
       </c>
       <c r="P736" s="1" t="n">
-        <v>46185.40584490741</v>
+        <v>46222.65678240741</v>
       </c>
       <c r="Q736" s="1" t="n">
-        <v>46185.40584490741</v>
+        <v>46222.65678240741</v>
       </c>
       <c r="R736" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S736" t="inlineStr">
         <is>
@@ -42407,12 +42407,12 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>user3955918607485</t>
+          <t>user3606227777348</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3955918607485</t>
+          <t>https://www.tiktok.com/@user3606227777348</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -42430,7 +42430,7 @@
       </c>
       <c r="N737" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
@@ -42439,13 +42439,13 @@
         </is>
       </c>
       <c r="P737" s="1" t="n">
-        <v>46221.53251157407</v>
+        <v>46185.40584490741</v>
       </c>
       <c r="Q737" s="1" t="n">
-        <v>46221.53251157407</v>
+        <v>46185.40584490741</v>
       </c>
       <c r="R737" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S737" t="inlineStr">
         <is>
@@ -42462,12 +42462,12 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>user411982221</t>
+          <t>user3955918607485</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user411982221</t>
+          <t>https://www.tiktok.com/@user3955918607485</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -42476,11 +42476,7 @@
       <c r="F738" t="inlineStr"/>
       <c r="G738" t="inlineStr"/>
       <c r="H738" t="inlineStr"/>
-      <c r="I738" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I738" t="inlineStr"/>
       <c r="J738" t="inlineStr"/>
       <c r="K738" t="inlineStr"/>
       <c r="L738" t="inlineStr"/>
@@ -42498,10 +42494,10 @@
         </is>
       </c>
       <c r="P738" s="1" t="n">
-        <v>46216.60361111111</v>
+        <v>46221.53251157407</v>
       </c>
       <c r="Q738" s="1" t="n">
-        <v>46216.60361111111</v>
+        <v>46221.53251157407</v>
       </c>
       <c r="R738" t="n">
         <v>4.8</v>
@@ -42521,12 +42517,12 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>user42180953</t>
+          <t>user411982221</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user42180953</t>
+          <t>https://www.tiktok.com/@user411982221</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -42535,7 +42531,11 @@
       <c r="F739" t="inlineStr"/>
       <c r="G739" t="inlineStr"/>
       <c r="H739" t="inlineStr"/>
-      <c r="I739" t="inlineStr"/>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J739" t="inlineStr"/>
       <c r="K739" t="inlineStr"/>
       <c r="L739" t="inlineStr"/>
@@ -42553,10 +42553,10 @@
         </is>
       </c>
       <c r="P739" s="1" t="n">
-        <v>46215.97638888889</v>
+        <v>46216.60361111111</v>
       </c>
       <c r="Q739" s="1" t="n">
-        <v>46215.97638888889</v>
+        <v>46216.60361111111</v>
       </c>
       <c r="R739" t="n">
         <v>4.8</v>
@@ -42576,12 +42576,12 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>user450470676288</t>
+          <t>user42180953</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user450470676288</t>
+          <t>https://www.tiktok.com/@user42180953</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -42608,10 +42608,10 @@
         </is>
       </c>
       <c r="P740" s="1" t="n">
-        <v>46225.3074537037</v>
+        <v>46215.97638888889</v>
       </c>
       <c r="Q740" s="1" t="n">
-        <v>46225.3074537037</v>
+        <v>46215.97638888889</v>
       </c>
       <c r="R740" t="n">
         <v>4.8</v>
@@ -42631,12 +42631,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>user458118102612</t>
+          <t>user450470676288</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user458118102612</t>
+          <t>https://www.tiktok.com/@user450470676288</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -42645,11 +42645,7 @@
       <c r="F741" t="inlineStr"/>
       <c r="G741" t="inlineStr"/>
       <c r="H741" t="inlineStr"/>
-      <c r="I741" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I741" t="inlineStr"/>
       <c r="J741" t="inlineStr"/>
       <c r="K741" t="inlineStr"/>
       <c r="L741" t="inlineStr"/>
@@ -42667,10 +42663,10 @@
         </is>
       </c>
       <c r="P741" s="1" t="n">
-        <v>46217.40354166667</v>
+        <v>46225.3074537037</v>
       </c>
       <c r="Q741" s="1" t="n">
-        <v>46217.40354166667</v>
+        <v>46225.3074537037</v>
       </c>
       <c r="R741" t="n">
         <v>4.8</v>
@@ -42690,12 +42686,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>user467542615061</t>
+          <t>user458118102612</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user467542615061</t>
+          <t>https://www.tiktok.com/@user458118102612</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -42704,7 +42700,11 @@
       <c r="F742" t="inlineStr"/>
       <c r="G742" t="inlineStr"/>
       <c r="H742" t="inlineStr"/>
-      <c r="I742" t="inlineStr"/>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J742" t="inlineStr"/>
       <c r="K742" t="inlineStr"/>
       <c r="L742" t="inlineStr"/>
@@ -42722,10 +42722,10 @@
         </is>
       </c>
       <c r="P742" s="1" t="n">
-        <v>46212.24355324074</v>
+        <v>46217.40354166667</v>
       </c>
       <c r="Q742" s="1" t="n">
-        <v>46212.24355324074</v>
+        <v>46217.40354166667</v>
       </c>
       <c r="R742" t="n">
         <v>4.8</v>
@@ -42745,12 +42745,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>user4688052396059</t>
+          <t>user467542615061</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4688052396059</t>
+          <t>https://www.tiktok.com/@user467542615061</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -42777,10 +42777,10 @@
         </is>
       </c>
       <c r="P743" s="1" t="n">
-        <v>46207.57041666667</v>
+        <v>46212.24355324074</v>
       </c>
       <c r="Q743" s="1" t="n">
-        <v>46207.57041666667</v>
+        <v>46212.24355324074</v>
       </c>
       <c r="R743" t="n">
         <v>4.8</v>
@@ -42800,12 +42800,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>user5007976343248</t>
+          <t>user4688052396059</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5007976343248</t>
+          <t>https://www.tiktok.com/@user4688052396059</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -42832,10 +42832,10 @@
         </is>
       </c>
       <c r="P744" s="1" t="n">
-        <v>46232.6764699074</v>
+        <v>46207.57041666667</v>
       </c>
       <c r="Q744" s="1" t="n">
-        <v>46232.6764699074</v>
+        <v>46207.57041666667</v>
       </c>
       <c r="R744" t="n">
         <v>4.8</v>
@@ -42855,12 +42855,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>user50112483538821</t>
+          <t>user5007976343248</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user50112483538821</t>
+          <t>https://www.tiktok.com/@user5007976343248</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
@@ -42887,10 +42887,10 @@
         </is>
       </c>
       <c r="P745" s="1" t="n">
-        <v>46225.41709490741</v>
+        <v>46232.6764699074</v>
       </c>
       <c r="Q745" s="1" t="n">
-        <v>46225.41709490741</v>
+        <v>46232.6764699074</v>
       </c>
       <c r="R745" t="n">
         <v>4.8</v>
@@ -42910,12 +42910,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>user5167483848722</t>
+          <t>user50112483538821</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5167483848722</t>
+          <t>https://www.tiktok.com/@user50112483538821</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -42942,10 +42942,10 @@
         </is>
       </c>
       <c r="P746" s="1" t="n">
-        <v>46216.00447916667</v>
+        <v>46225.41709490741</v>
       </c>
       <c r="Q746" s="1" t="n">
-        <v>46216.00447916667</v>
+        <v>46225.41709490741</v>
       </c>
       <c r="R746" t="n">
         <v>4.8</v>
@@ -42965,12 +42965,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>user5366244810788</t>
+          <t>user5167483848722</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5366244810788</t>
+          <t>https://www.tiktok.com/@user5167483848722</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
@@ -42997,10 +42997,10 @@
         </is>
       </c>
       <c r="P747" s="1" t="n">
-        <v>46220.09133101852</v>
+        <v>46216.00447916667</v>
       </c>
       <c r="Q747" s="1" t="n">
-        <v>46220.09133101852</v>
+        <v>46216.00447916667</v>
       </c>
       <c r="R747" t="n">
         <v>4.8</v>
@@ -43020,12 +43020,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>user59838594031894</t>
+          <t>user5366244810788</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user59838594031894</t>
+          <t>https://www.tiktok.com/@user5366244810788</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
@@ -43043,7 +43043,7 @@
       </c>
       <c r="N748" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O748" t="inlineStr">
@@ -43052,13 +43052,13 @@
         </is>
       </c>
       <c r="P748" s="1" t="n">
-        <v>46238.55344907408</v>
+        <v>46220.09133101852</v>
       </c>
       <c r="Q748" s="1" t="n">
-        <v>46238.55344907408</v>
+        <v>46220.09133101852</v>
       </c>
       <c r="R748" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S748" t="inlineStr">
         <is>
@@ -43075,12 +43075,12 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>user630548237</t>
+          <t>user59838594031894</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user630548237</t>
+          <t>https://www.tiktok.com/@user59838594031894</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
@@ -43098,7 +43098,7 @@
       </c>
       <c r="N749" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O749" t="inlineStr">
@@ -43107,13 +43107,13 @@
         </is>
       </c>
       <c r="P749" s="1" t="n">
-        <v>46212.98568287037</v>
+        <v>46238.55344907408</v>
       </c>
       <c r="Q749" s="1" t="n">
-        <v>46212.98568287037</v>
+        <v>46238.55344907408</v>
       </c>
       <c r="R749" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S749" t="inlineStr">
         <is>
@@ -43130,12 +43130,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>user6333787981304</t>
+          <t>user630548237</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6333787981304</t>
+          <t>https://www.tiktok.com/@user630548237</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
@@ -43153,7 +43153,7 @@
       </c>
       <c r="N750" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O750" t="inlineStr">
@@ -43162,13 +43162,13 @@
         </is>
       </c>
       <c r="P750" s="1" t="n">
-        <v>46218.50613425926</v>
+        <v>46212.98568287037</v>
       </c>
       <c r="Q750" s="1" t="n">
-        <v>46218.50613425926</v>
+        <v>46212.98568287037</v>
       </c>
       <c r="R750" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S750" t="inlineStr">
         <is>
@@ -43185,12 +43185,12 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>user6678773820675</t>
+          <t>user6333787981304</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6678773820675</t>
+          <t>https://www.tiktok.com/@user6333787981304</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
@@ -43208,7 +43208,7 @@
       </c>
       <c r="N751" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O751" t="inlineStr">
@@ -43217,13 +43217,13 @@
         </is>
       </c>
       <c r="P751" s="1" t="n">
-        <v>46218.53957175926</v>
+        <v>46218.50613425926</v>
       </c>
       <c r="Q751" s="1" t="n">
-        <v>46218.53957175926</v>
+        <v>46218.50613425926</v>
       </c>
       <c r="R751" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S751" t="inlineStr">
         <is>
@@ -43240,12 +43240,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>user67333378229996</t>
+          <t>user6678773820675</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user67333378229996</t>
+          <t>https://www.tiktok.com/@user6678773820675</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
@@ -43272,10 +43272,10 @@
         </is>
       </c>
       <c r="P752" s="1" t="n">
-        <v>46234.39538194444</v>
+        <v>46218.53957175926</v>
       </c>
       <c r="Q752" s="1" t="n">
-        <v>46234.39538194444</v>
+        <v>46218.53957175926</v>
       </c>
       <c r="R752" t="n">
         <v>4.8</v>
@@ -43295,12 +43295,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>user6737190678194</t>
+          <t>user67333378229996</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6737190678194</t>
+          <t>https://www.tiktok.com/@user67333378229996</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
@@ -43327,10 +43327,10 @@
         </is>
       </c>
       <c r="P753" s="1" t="n">
-        <v>46222.63238425926</v>
+        <v>46234.39538194444</v>
       </c>
       <c r="Q753" s="1" t="n">
-        <v>46222.63238425926</v>
+        <v>46234.39538194444</v>
       </c>
       <c r="R753" t="n">
         <v>4.8</v>
@@ -43350,12 +43350,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>user6892760169821</t>
+          <t>user6737190678194</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6892760169821</t>
+          <t>https://www.tiktok.com/@user6737190678194</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
@@ -43382,10 +43382,10 @@
         </is>
       </c>
       <c r="P754" s="1" t="n">
-        <v>46208.68979166666</v>
+        <v>46222.63238425926</v>
       </c>
       <c r="Q754" s="1" t="n">
-        <v>46208.68979166666</v>
+        <v>46222.63238425926</v>
       </c>
       <c r="R754" t="n">
         <v>4.8</v>
@@ -43405,12 +43405,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>user6962927106649</t>
+          <t>user6892760169821</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6962927106649</t>
+          <t>https://www.tiktok.com/@user6892760169821</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -43419,11 +43419,7 @@
       <c r="F755" t="inlineStr"/>
       <c r="G755" t="inlineStr"/>
       <c r="H755" t="inlineStr"/>
-      <c r="I755" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
+      <c r="I755" t="inlineStr"/>
       <c r="J755" t="inlineStr"/>
       <c r="K755" t="inlineStr"/>
       <c r="L755" t="inlineStr"/>
@@ -43441,10 +43437,10 @@
         </is>
       </c>
       <c r="P755" s="1" t="n">
-        <v>46220.98945601852</v>
+        <v>46208.68979166666</v>
       </c>
       <c r="Q755" s="1" t="n">
-        <v>46220.98945601852</v>
+        <v>46208.68979166666</v>
       </c>
       <c r="R755" t="n">
         <v>4.8</v>
@@ -43464,12 +43460,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>user7232137600814</t>
+          <t>user6962927106649</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7232137600814</t>
+          <t>https://www.tiktok.com/@user6962927106649</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
@@ -43478,7 +43474,11 @@
       <c r="F756" t="inlineStr"/>
       <c r="G756" t="inlineStr"/>
       <c r="H756" t="inlineStr"/>
-      <c r="I756" t="inlineStr"/>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J756" t="inlineStr"/>
       <c r="K756" t="inlineStr"/>
       <c r="L756" t="inlineStr"/>
@@ -43496,10 +43496,10 @@
         </is>
       </c>
       <c r="P756" s="1" t="n">
-        <v>46216.11149305556</v>
+        <v>46220.98945601852</v>
       </c>
       <c r="Q756" s="1" t="n">
-        <v>46216.11149305556</v>
+        <v>46220.98945601852</v>
       </c>
       <c r="R756" t="n">
         <v>4.8</v>
@@ -43519,12 +43519,12 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>user7411816032779</t>
+          <t>user7232137600814</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7411816032779</t>
+          <t>https://www.tiktok.com/@user7232137600814</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
@@ -43551,10 +43551,10 @@
         </is>
       </c>
       <c r="P757" s="1" t="n">
-        <v>46231.93748842592</v>
+        <v>46216.11149305556</v>
       </c>
       <c r="Q757" s="1" t="n">
-        <v>46231.93748842592</v>
+        <v>46216.11149305556</v>
       </c>
       <c r="R757" t="n">
         <v>4.8</v>
@@ -43574,12 +43574,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>user7888882185294</t>
+          <t>user7411816032779</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7888882185294</t>
+          <t>https://www.tiktok.com/@user7411816032779</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
@@ -43606,10 +43606,10 @@
         </is>
       </c>
       <c r="P758" s="1" t="n">
-        <v>46217.0528587963</v>
+        <v>46231.93748842592</v>
       </c>
       <c r="Q758" s="1" t="n">
-        <v>46217.0528587963</v>
+        <v>46231.93748842592</v>
       </c>
       <c r="R758" t="n">
         <v>4.8</v>
@@ -43629,12 +43629,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>user8008669545474</t>
+          <t>user7888882185294</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8008669545474</t>
+          <t>https://www.tiktok.com/@user7888882185294</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -43652,22 +43652,22 @@
       </c>
       <c r="N759" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O759" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P759" s="1" t="n">
-        <v>45981.84152777777</v>
+        <v>46217.0528587963</v>
       </c>
       <c r="Q759" s="1" t="n">
-        <v>45981.84152777777</v>
+        <v>46217.0528587963</v>
       </c>
       <c r="R759" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="S759" t="inlineStr">
         <is>
@@ -43684,12 +43684,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>user8134650348013</t>
+          <t>user8008669545474</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8134650348013</t>
+          <t>https://www.tiktok.com/@user8008669545474</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
@@ -43707,22 +43707,22 @@
       </c>
       <c r="N760" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O760" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P760" s="1" t="n">
-        <v>46217.49246527778</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="Q760" s="1" t="n">
-        <v>46217.49246527778</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="R760" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S760" t="inlineStr">
         <is>
@@ -43739,12 +43739,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>user8376211816358</t>
+          <t>user8134650348013</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8376211816358</t>
+          <t>https://www.tiktok.com/@user8134650348013</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
@@ -43771,10 +43771,10 @@
         </is>
       </c>
       <c r="P761" s="1" t="n">
-        <v>46219.42800925926</v>
+        <v>46217.49246527778</v>
       </c>
       <c r="Q761" s="1" t="n">
-        <v>46219.42800925926</v>
+        <v>46217.49246527778</v>
       </c>
       <c r="R761" t="n">
         <v>4.8</v>
@@ -43794,12 +43794,12 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>user8387816340732</t>
+          <t>user8376211816358</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8387816340732</t>
+          <t>https://www.tiktok.com/@user8376211816358</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -43826,10 +43826,10 @@
         </is>
       </c>
       <c r="P762" s="1" t="n">
-        <v>46231.80520833333</v>
+        <v>46219.42800925926</v>
       </c>
       <c r="Q762" s="1" t="n">
-        <v>46231.80520833333</v>
+        <v>46219.42800925926</v>
       </c>
       <c r="R762" t="n">
         <v>4.8</v>
@@ -43849,12 +43849,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>user866w5p9rl9</t>
+          <t>user8387816340732</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user866w5p9rl9</t>
+          <t>https://www.tiktok.com/@user8387816340732</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
@@ -43872,22 +43872,22 @@
       </c>
       <c r="N763" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O763" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P763" s="1" t="n">
-        <v>46053.63612268519</v>
+        <v>46231.80520833333</v>
       </c>
       <c r="Q763" s="1" t="n">
-        <v>46053.63612268519</v>
+        <v>46231.80520833333</v>
       </c>
       <c r="R763" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S763" t="inlineStr">
         <is>
@@ -43904,12 +43904,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>user88181884284463</t>
+          <t>user866w5p9rl9</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user88181884284463</t>
+          <t>https://www.tiktok.com/@user866w5p9rl9</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
@@ -43927,22 +43927,22 @@
       </c>
       <c r="N764" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O764" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P764" s="1" t="n">
-        <v>46210.45086805556</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="Q764" s="1" t="n">
-        <v>46210.45086805556</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="R764" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S764" t="inlineStr">
         <is>
@@ -43959,12 +43959,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>user9090397839153</t>
+          <t>user88181884284463</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9090397839153</t>
+          <t>https://www.tiktok.com/@user88181884284463</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
@@ -43991,10 +43991,10 @@
         </is>
       </c>
       <c r="P765" s="1" t="n">
-        <v>46208.69571759259</v>
+        <v>46210.45086805556</v>
       </c>
       <c r="Q765" s="1" t="n">
-        <v>46208.69571759259</v>
+        <v>46210.45086805556</v>
       </c>
       <c r="R765" t="n">
         <v>4.8</v>
@@ -44014,12 +44014,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>user9760096301617</t>
+          <t>user9090397839153</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9760096301617</t>
+          <t>https://www.tiktok.com/@user9090397839153</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
@@ -44028,11 +44028,7 @@
       <c r="F766" t="inlineStr"/>
       <c r="G766" t="inlineStr"/>
       <c r="H766" t="inlineStr"/>
-      <c r="I766" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
+      <c r="I766" t="inlineStr"/>
       <c r="J766" t="inlineStr"/>
       <c r="K766" t="inlineStr"/>
       <c r="L766" t="inlineStr"/>
@@ -44050,10 +44046,10 @@
         </is>
       </c>
       <c r="P766" s="1" t="n">
-        <v>46227.566875</v>
+        <v>46208.69571759259</v>
       </c>
       <c r="Q766" s="1" t="n">
-        <v>46227.566875</v>
+        <v>46208.69571759259</v>
       </c>
       <c r="R766" t="n">
         <v>4.8</v>
@@ -44073,12 +44069,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>usernamelarchinoo</t>
+          <t>user9760096301617</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@usernamelarchinoo</t>
+          <t>https://www.tiktok.com/@user9760096301617</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
@@ -44087,7 +44083,11 @@
       <c r="F767" t="inlineStr"/>
       <c r="G767" t="inlineStr"/>
       <c r="H767" t="inlineStr"/>
-      <c r="I767" t="inlineStr"/>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J767" t="inlineStr"/>
       <c r="K767" t="inlineStr"/>
       <c r="L767" t="inlineStr"/>
@@ -44105,10 +44105,10 @@
         </is>
       </c>
       <c r="P767" s="1" t="n">
-        <v>46209.84040509259</v>
+        <v>46227.566875</v>
       </c>
       <c r="Q767" s="1" t="n">
-        <v>46209.84040509259</v>
+        <v>46227.566875</v>
       </c>
       <c r="R767" t="n">
         <v>4.8</v>
@@ -44128,12 +44128,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>uyi_guobadia1976</t>
+          <t>usernamelarchinoo</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uyi_guobadia1976</t>
+          <t>https://www.tiktok.com/@usernamelarchinoo</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -44142,11 +44142,7 @@
       <c r="F768" t="inlineStr"/>
       <c r="G768" t="inlineStr"/>
       <c r="H768" t="inlineStr"/>
-      <c r="I768" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I768" t="inlineStr"/>
       <c r="J768" t="inlineStr"/>
       <c r="K768" t="inlineStr"/>
       <c r="L768" t="inlineStr"/>
@@ -44164,10 +44160,10 @@
         </is>
       </c>
       <c r="P768" s="1" t="n">
-        <v>46229.67628472222</v>
+        <v>46209.84040509259</v>
       </c>
       <c r="Q768" s="1" t="n">
-        <v>46229.67628472222</v>
+        <v>46209.84040509259</v>
       </c>
       <c r="R768" t="n">
         <v>4.8</v>
@@ -44187,12 +44183,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>vanfoxhamah</t>
+          <t>uyi_guobadia1976</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vanfoxhamah</t>
+          <t>https://www.tiktok.com/@uyi_guobadia1976</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
@@ -44223,10 +44219,10 @@
         </is>
       </c>
       <c r="P769" s="1" t="n">
-        <v>46223.24950231481</v>
+        <v>46229.67628472222</v>
       </c>
       <c r="Q769" s="1" t="n">
-        <v>46223.24950231481</v>
+        <v>46229.67628472222</v>
       </c>
       <c r="R769" t="n">
         <v>4.8</v>
@@ -44246,12 +44242,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>virginglo</t>
+          <t>vanfoxhamah</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@virginglo</t>
+          <t>https://www.tiktok.com/@vanfoxhamah</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
@@ -44282,10 +44278,10 @@
         </is>
       </c>
       <c r="P770" s="1" t="n">
-        <v>46209.88831018518</v>
+        <v>46223.24950231481</v>
       </c>
       <c r="Q770" s="1" t="n">
-        <v>46209.88831018518</v>
+        <v>46223.24950231481</v>
       </c>
       <c r="R770" t="n">
         <v>4.8</v>
@@ -44305,12 +44301,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>vision.rift</t>
+          <t>virginglo</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vision.rift</t>
+          <t>https://www.tiktok.com/@virginglo</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
@@ -44332,22 +44328,22 @@
       </c>
       <c r="N771" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O771" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P771" s="1" t="n">
-        <v>45965.5908449074</v>
+        <v>46209.88831018518</v>
       </c>
       <c r="Q771" s="1" t="n">
-        <v>45965.5908449074</v>
+        <v>46209.88831018518</v>
       </c>
       <c r="R771" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S771" t="inlineStr">
         <is>
@@ -44364,12 +44360,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>vivian.shobogun.backup</t>
+          <t>vision.rift</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vivian.shobogun.backup</t>
+          <t>https://www.tiktok.com/@vision.rift</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -44391,22 +44387,22 @@
       </c>
       <c r="N772" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O772" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P772" s="1" t="n">
-        <v>46222.26184027778</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="Q772" s="1" t="n">
-        <v>46222.26184027778</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="R772" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S772" t="inlineStr">
         <is>
@@ -44423,12 +44419,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>vivianokeke98</t>
+          <t>vivian.shobogun.backup</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vivianokeke98</t>
+          <t>https://www.tiktok.com/@vivian.shobogun.backup</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
@@ -44437,7 +44433,11 @@
       <c r="F773" t="inlineStr"/>
       <c r="G773" t="inlineStr"/>
       <c r="H773" t="inlineStr"/>
-      <c r="I773" t="inlineStr"/>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J773" t="inlineStr"/>
       <c r="K773" t="inlineStr"/>
       <c r="L773" t="inlineStr"/>
@@ -44455,10 +44455,10 @@
         </is>
       </c>
       <c r="P773" s="1" t="n">
-        <v>46232.40989583333</v>
+        <v>46222.26184027778</v>
       </c>
       <c r="Q773" s="1" t="n">
-        <v>46232.40989583333</v>
+        <v>46222.26184027778</v>
       </c>
       <c r="R773" t="n">
         <v>4.8</v>
@@ -44478,12 +44478,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>vytyglrl</t>
+          <t>vivianokeke98</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vytyglrl</t>
+          <t>https://www.tiktok.com/@vivianokeke98</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
@@ -44501,7 +44501,7 @@
       </c>
       <c r="N774" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O774" t="inlineStr">
@@ -44510,13 +44510,13 @@
         </is>
       </c>
       <c r="P774" s="1" t="n">
-        <v>46235.07810185185</v>
+        <v>46232.40989583333</v>
       </c>
       <c r="Q774" s="1" t="n">
-        <v>46235.07810185185</v>
+        <v>46232.40989583333</v>
       </c>
       <c r="R774" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S774" t="inlineStr">
         <is>
@@ -44533,12 +44533,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>walex0880</t>
+          <t>vytyglrl</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@walex0880</t>
+          <t>https://www.tiktok.com/@vytyglrl</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
@@ -44556,7 +44556,7 @@
       </c>
       <c r="N775" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O775" t="inlineStr">
@@ -44565,13 +44565,13 @@
         </is>
       </c>
       <c r="P775" s="1" t="n">
-        <v>46238.89991898148</v>
+        <v>46235.07810185185</v>
       </c>
       <c r="Q775" s="1" t="n">
-        <v>46238.89991898148</v>
+        <v>46235.07810185185</v>
       </c>
       <c r="R775" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S775" t="inlineStr">
         <is>
@@ -44588,12 +44588,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>wankycandle</t>
+          <t>walex0880</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wankycandle</t>
+          <t>https://www.tiktok.com/@walex0880</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -44611,22 +44611,22 @@
       </c>
       <c r="N776" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O776" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P776" s="1" t="n">
-        <v>46206.37778935185</v>
+        <v>46238.89991898148</v>
       </c>
       <c r="Q776" s="1" t="n">
-        <v>46206.37778935185</v>
+        <v>46238.89991898148</v>
       </c>
       <c r="R776" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S776" t="inlineStr">
         <is>
@@ -44643,12 +44643,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>waq78690</t>
+          <t>wankycandle</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waq78690</t>
+          <t>https://www.tiktok.com/@wankycandle</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -44657,11 +44657,7 @@
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="inlineStr"/>
       <c r="H777" t="inlineStr"/>
-      <c r="I777" t="inlineStr">
-        <is>
-          <t>South Asian</t>
-        </is>
-      </c>
+      <c r="I777" t="inlineStr"/>
       <c r="J777" t="inlineStr"/>
       <c r="K777" t="inlineStr"/>
       <c r="L777" t="inlineStr"/>
@@ -44679,10 +44675,10 @@
         </is>
       </c>
       <c r="P777" s="1" t="n">
-        <v>46220.91548611111</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="Q777" s="1" t="n">
-        <v>46220.91548611111</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="R777" t="n">
         <v>6</v>
@@ -44702,12 +44698,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>wassava4</t>
+          <t>waq78690</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wassava4</t>
+          <t>https://www.tiktok.com/@waq78690</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
@@ -44718,7 +44714,7 @@
       <c r="H778" t="inlineStr"/>
       <c r="I778" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J778" t="inlineStr"/>
@@ -44729,22 +44725,22 @@
       </c>
       <c r="N778" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O778" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P778" s="1" t="n">
-        <v>46221.72733796296</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="Q778" s="1" t="n">
-        <v>46221.72733796296</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="R778" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S778" t="inlineStr">
         <is>
@@ -44761,12 +44757,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>waxtee0</t>
+          <t>wassava4</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waxtee0</t>
+          <t>https://www.tiktok.com/@wassava4</t>
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
@@ -44775,7 +44771,11 @@
       <c r="F779" t="inlineStr"/>
       <c r="G779" t="inlineStr"/>
       <c r="H779" t="inlineStr"/>
-      <c r="I779" t="inlineStr"/>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J779" t="inlineStr"/>
       <c r="K779" t="inlineStr"/>
       <c r="L779" t="inlineStr"/>
@@ -44793,10 +44793,10 @@
         </is>
       </c>
       <c r="P779" s="1" t="n">
-        <v>46230.38460648148</v>
+        <v>46221.72733796296</v>
       </c>
       <c r="Q779" s="1" t="n">
-        <v>46230.38460648148</v>
+        <v>46221.72733796296</v>
       </c>
       <c r="R779" t="n">
         <v>4.8</v>
@@ -44816,12 +44816,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>wealth2869</t>
+          <t>waxtee0</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wealth2869</t>
+          <t>https://www.tiktok.com/@waxtee0</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -44848,10 +44848,10 @@
         </is>
       </c>
       <c r="P780" s="1" t="n">
-        <v>46222.32829861111</v>
+        <v>46230.38460648148</v>
       </c>
       <c r="Q780" s="1" t="n">
-        <v>46222.32829861111</v>
+        <v>46230.38460648148</v>
       </c>
       <c r="R780" t="n">
         <v>4.8</v>
@@ -44871,12 +44871,12 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>wendykhan19</t>
+          <t>wealth2869</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wendykhan19</t>
+          <t>https://www.tiktok.com/@wealth2869</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
@@ -44903,10 +44903,10 @@
         </is>
       </c>
       <c r="P781" s="1" t="n">
-        <v>46213.43940972222</v>
+        <v>46222.32829861111</v>
       </c>
       <c r="Q781" s="1" t="n">
-        <v>46213.43940972222</v>
+        <v>46222.32829861111</v>
       </c>
       <c r="R781" t="n">
         <v>4.8</v>
@@ -44926,12 +44926,12 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>whatdoes09</t>
+          <t>wendykhan19</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@whatdoes09</t>
+          <t>https://www.tiktok.com/@wendykhan19</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -44958,10 +44958,10 @@
         </is>
       </c>
       <c r="P782" s="1" t="n">
-        <v>46224.32761574074</v>
+        <v>46213.43940972222</v>
       </c>
       <c r="Q782" s="1" t="n">
-        <v>46224.32761574074</v>
+        <v>46213.43940972222</v>
       </c>
       <c r="R782" t="n">
         <v>4.8</v>
@@ -44981,12 +44981,12 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>whoisedwina.x</t>
+          <t>whatdoes09</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@whoisedwina.x</t>
+          <t>https://www.tiktok.com/@whatdoes09</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -45013,10 +45013,10 @@
         </is>
       </c>
       <c r="P783" s="1" t="n">
-        <v>46238.83828703704</v>
+        <v>46224.32761574074</v>
       </c>
       <c r="Q783" s="1" t="n">
-        <v>46238.83828703704</v>
+        <v>46224.32761574074</v>
       </c>
       <c r="R783" t="n">
         <v>4.8</v>
@@ -45036,12 +45036,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>williams.olumide5</t>
+          <t>whoisedwina.x</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@williams.olumide5</t>
+          <t>https://www.tiktok.com/@whoisedwina.x</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -45068,10 +45068,10 @@
         </is>
       </c>
       <c r="P784" s="1" t="n">
-        <v>46208.69674768519</v>
+        <v>46238.83828703704</v>
       </c>
       <c r="Q784" s="1" t="n">
-        <v>46208.69674768519</v>
+        <v>46238.83828703704</v>
       </c>
       <c r="R784" t="n">
         <v>4.8</v>
@@ -45091,12 +45091,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>willow_mama23</t>
+          <t>williams.olumide5</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@willow_mama23</t>
+          <t>https://www.tiktok.com/@williams.olumide5</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -45114,7 +45114,7 @@
       </c>
       <c r="N785" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O785" t="inlineStr">
@@ -45123,13 +45123,13 @@
         </is>
       </c>
       <c r="P785" s="1" t="n">
-        <v>46250.84450231482</v>
+        <v>46208.69674768519</v>
       </c>
       <c r="Q785" s="1" t="n">
-        <v>46250.84450231482</v>
+        <v>46208.69674768519</v>
       </c>
       <c r="R785" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S785" t="inlineStr">
         <is>
@@ -45146,12 +45146,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>womeninspiration5</t>
+          <t>willow_mama23</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@womeninspiration5</t>
+          <t>https://www.tiktok.com/@willow_mama23</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
@@ -45174,17 +45174,17 @@
       </c>
       <c r="O786" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P786" s="1" t="n">
-        <v>45939.98240740741</v>
+        <v>46250.84450231482</v>
       </c>
       <c r="Q786" s="1" t="n">
-        <v>45939.98240740741</v>
+        <v>46250.84450231482</v>
       </c>
       <c r="R786" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="S786" t="inlineStr">
         <is>
@@ -45201,12 +45201,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>xheyitsbeccax</t>
+          <t>womeninspiration5</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xheyitsbeccax</t>
+          <t>https://www.tiktok.com/@womeninspiration5</t>
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
@@ -45220,26 +45220,26 @@
       <c r="K787" t="inlineStr"/>
       <c r="L787" t="inlineStr"/>
       <c r="M787" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N787" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Other</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O787" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT), seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P787" s="1" t="n">
-        <v>46250.04033564815</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="Q787" s="1" t="n">
-        <v>46250.04033564815</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="R787" t="n">
-        <v>11.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S787" t="inlineStr">
         <is>
@@ -45256,12 +45256,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>xhollycolhounx</t>
+          <t>xheyitsbeccax</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xhollycolhounx</t>
+          <t>https://www.tiktok.com/@xheyitsbeccax</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -45275,26 +45275,26 @@
       <c r="K788" t="inlineStr"/>
       <c r="L788" t="inlineStr"/>
       <c r="M788" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N788" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O788" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P788" s="1" t="n">
-        <v>46198.62712962963</v>
+        <v>46250.04033564815</v>
       </c>
       <c r="Q788" s="1" t="n">
-        <v>46198.62712962963</v>
+        <v>46250.04033564815</v>
       </c>
       <c r="R788" t="n">
-        <v>6</v>
+        <v>11.9</v>
       </c>
       <c r="S788" t="inlineStr">
         <is>
@@ -45311,12 +45311,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>xstarharry</t>
+          <t>xhollycolhounx</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xstarharry</t>
+          <t>https://www.tiktok.com/@xhollycolhounx</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
@@ -45325,11 +45325,7 @@
       <c r="F789" t="inlineStr"/>
       <c r="G789" t="inlineStr"/>
       <c r="H789" t="inlineStr"/>
-      <c r="I789" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I789" t="inlineStr"/>
       <c r="J789" t="inlineStr"/>
       <c r="K789" t="inlineStr"/>
       <c r="L789" t="inlineStr"/>
@@ -45338,22 +45334,22 @@
       </c>
       <c r="N789" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O789" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P789" s="1" t="n">
-        <v>46219.35070601852</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q789" s="1" t="n">
-        <v>46219.35070601852</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R789" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S789" t="inlineStr">
         <is>
@@ -45370,12 +45366,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>y_ddraig69</t>
+          <t>xstarharry</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@y_ddraig69</t>
+          <t>https://www.tiktok.com/@xstarharry</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
@@ -45384,31 +45380,35 @@
       <c r="F790" t="inlineStr"/>
       <c r="G790" t="inlineStr"/>
       <c r="H790" t="inlineStr"/>
-      <c r="I790" t="inlineStr"/>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J790" t="inlineStr"/>
       <c r="K790" t="inlineStr"/>
       <c r="L790" t="inlineStr"/>
       <c r="M790" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N790" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O790" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT), seller</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P790" s="1" t="n">
-        <v>46249.74936342592</v>
+        <v>46219.35070601852</v>
       </c>
       <c r="Q790" s="1" t="n">
-        <v>46249.749375</v>
+        <v>46219.35070601852</v>
       </c>
       <c r="R790" t="n">
-        <v>11.9</v>
+        <v>4.8</v>
       </c>
       <c r="S790" t="inlineStr">
         <is>
@@ -45425,12 +45425,12 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>yahwehshaven</t>
+          <t>y_ddraig69</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yahwehshaven</t>
+          <t>https://www.tiktok.com/@y_ddraig69</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -45444,26 +45444,26 @@
       <c r="K791" t="inlineStr"/>
       <c r="L791" t="inlineStr"/>
       <c r="M791" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N791" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O791" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P791" s="1" t="n">
-        <v>46228.34030092593</v>
+        <v>46249.74936342592</v>
       </c>
       <c r="Q791" s="1" t="n">
-        <v>46228.34030092593</v>
+        <v>46249.749375</v>
       </c>
       <c r="R791" t="n">
-        <v>4.8</v>
+        <v>11.9</v>
       </c>
       <c r="S791" t="inlineStr">
         <is>
@@ -45480,12 +45480,12 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>yamaalieujobe</t>
+          <t>yahwehshaven</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yamaalieujobe</t>
+          <t>https://www.tiktok.com/@yahwehshaven</t>
         </is>
       </c>
       <c r="C792" t="inlineStr"/>
@@ -45494,11 +45494,7 @@
       <c r="F792" t="inlineStr"/>
       <c r="G792" t="inlineStr"/>
       <c r="H792" t="inlineStr"/>
-      <c r="I792" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I792" t="inlineStr"/>
       <c r="J792" t="inlineStr"/>
       <c r="K792" t="inlineStr"/>
       <c r="L792" t="inlineStr"/>
@@ -45516,10 +45512,10 @@
         </is>
       </c>
       <c r="P792" s="1" t="n">
-        <v>46219.66237268518</v>
+        <v>46228.34030092593</v>
       </c>
       <c r="Q792" s="1" t="n">
-        <v>46219.66237268518</v>
+        <v>46228.34030092593</v>
       </c>
       <c r="R792" t="n">
         <v>4.8</v>
@@ -45539,12 +45535,12 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>yamania.2024</t>
+          <t>yamaalieujobe</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yamania.2024</t>
+          <t>https://www.tiktok.com/@yamaalieujobe</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
@@ -45553,7 +45549,11 @@
       <c r="F793" t="inlineStr"/>
       <c r="G793" t="inlineStr"/>
       <c r="H793" t="inlineStr"/>
-      <c r="I793" t="inlineStr"/>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J793" t="inlineStr"/>
       <c r="K793" t="inlineStr"/>
       <c r="L793" t="inlineStr"/>
@@ -45571,10 +45571,10 @@
         </is>
       </c>
       <c r="P793" s="1" t="n">
-        <v>46209.50663194444</v>
+        <v>46219.66237268518</v>
       </c>
       <c r="Q793" s="1" t="n">
-        <v>46209.50663194444</v>
+        <v>46219.66237268518</v>
       </c>
       <c r="R793" t="n">
         <v>4.8</v>
@@ -45594,12 +45594,12 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>yemi0417</t>
+          <t>yamania.2024</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemi0417</t>
+          <t>https://www.tiktok.com/@yamania.2024</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
@@ -45626,10 +45626,10 @@
         </is>
       </c>
       <c r="P794" s="1" t="n">
-        <v>46208.78111111111</v>
+        <v>46209.50663194444</v>
       </c>
       <c r="Q794" s="1" t="n">
-        <v>46208.78111111111</v>
+        <v>46209.50663194444</v>
       </c>
       <c r="R794" t="n">
         <v>4.8</v>
@@ -45649,12 +45649,12 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>yemisi0906</t>
+          <t>yemi0417</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemisi0906</t>
+          <t>https://www.tiktok.com/@yemi0417</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
@@ -45681,10 +45681,10 @@
         </is>
       </c>
       <c r="P795" s="1" t="n">
-        <v>46213.52189814814</v>
+        <v>46208.78111111111</v>
       </c>
       <c r="Q795" s="1" t="n">
-        <v>46213.52189814814</v>
+        <v>46208.78111111111</v>
       </c>
       <c r="R795" t="n">
         <v>4.8</v>
@@ -45704,12 +45704,12 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>yemisi_81</t>
+          <t>yemisi0906</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemisi_81</t>
+          <t>https://www.tiktok.com/@yemisi0906</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
@@ -45718,11 +45718,7 @@
       <c r="F796" t="inlineStr"/>
       <c r="G796" t="inlineStr"/>
       <c r="H796" t="inlineStr"/>
-      <c r="I796" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I796" t="inlineStr"/>
       <c r="J796" t="inlineStr"/>
       <c r="K796" t="inlineStr"/>
       <c r="L796" t="inlineStr"/>
@@ -45740,10 +45736,10 @@
         </is>
       </c>
       <c r="P796" s="1" t="n">
-        <v>46238.41952546296</v>
+        <v>46213.52189814814</v>
       </c>
       <c r="Q796" s="1" t="n">
-        <v>46238.41952546296</v>
+        <v>46213.52189814814</v>
       </c>
       <c r="R796" t="n">
         <v>4.8</v>
@@ -45763,12 +45759,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>yimika24</t>
+          <t>yemisi_81</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yimika24</t>
+          <t>https://www.tiktok.com/@yemisi_81</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
@@ -45777,7 +45773,11 @@
       <c r="F797" t="inlineStr"/>
       <c r="G797" t="inlineStr"/>
       <c r="H797" t="inlineStr"/>
-      <c r="I797" t="inlineStr"/>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J797" t="inlineStr"/>
       <c r="K797" t="inlineStr"/>
       <c r="L797" t="inlineStr"/>
@@ -45795,10 +45795,10 @@
         </is>
       </c>
       <c r="P797" s="1" t="n">
-        <v>46227.66070601852</v>
+        <v>46238.41952546296</v>
       </c>
       <c r="Q797" s="1" t="n">
-        <v>46227.66070601852</v>
+        <v>46238.41952546296</v>
       </c>
       <c r="R797" t="n">
         <v>4.8</v>
@@ -45818,12 +45818,12 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>yinkus520</t>
+          <t>yimika24</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yinkus520</t>
+          <t>https://www.tiktok.com/@yimika24</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
@@ -45850,10 +45850,10 @@
         </is>
       </c>
       <c r="P798" s="1" t="n">
-        <v>46223.694375</v>
+        <v>46227.66070601852</v>
       </c>
       <c r="Q798" s="1" t="n">
-        <v>46223.694375</v>
+        <v>46227.66070601852</v>
       </c>
       <c r="R798" t="n">
         <v>4.8</v>
@@ -45873,12 +45873,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>yocharlton</t>
+          <t>yinkus520</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yocharlton</t>
+          <t>https://www.tiktok.com/@yinkus520</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
@@ -45887,11 +45887,7 @@
       <c r="F799" t="inlineStr"/>
       <c r="G799" t="inlineStr"/>
       <c r="H799" t="inlineStr"/>
-      <c r="I799" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I799" t="inlineStr"/>
       <c r="J799" t="inlineStr"/>
       <c r="K799" t="inlineStr"/>
       <c r="L799" t="inlineStr"/>
@@ -45909,10 +45905,10 @@
         </is>
       </c>
       <c r="P799" s="1" t="n">
-        <v>46232.3164699074</v>
+        <v>46223.694375</v>
       </c>
       <c r="Q799" s="1" t="n">
-        <v>46232.3164699074</v>
+        <v>46223.694375</v>
       </c>
       <c r="R799" t="n">
         <v>4.8</v>
@@ -45932,12 +45928,12 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>yvette.chance8</t>
+          <t>yocharlton</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yvette.chance8</t>
+          <t>https://www.tiktok.com/@yocharlton</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
@@ -45946,7 +45942,11 @@
       <c r="F800" t="inlineStr"/>
       <c r="G800" t="inlineStr"/>
       <c r="H800" t="inlineStr"/>
-      <c r="I800" t="inlineStr"/>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J800" t="inlineStr"/>
       <c r="K800" t="inlineStr"/>
       <c r="L800" t="inlineStr"/>
@@ -45955,22 +45955,22 @@
       </c>
       <c r="N800" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O800" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P800" s="1" t="n">
-        <v>45990.94167824074</v>
+        <v>46232.3164699074</v>
       </c>
       <c r="Q800" s="1" t="n">
-        <v>45990.94167824074</v>
+        <v>46232.3164699074</v>
       </c>
       <c r="R800" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S800" t="inlineStr">
         <is>
@@ -45987,12 +45987,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>zabi.azmhh</t>
+          <t>yvette.chance8</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zabi.azmhh</t>
+          <t>https://www.tiktok.com/@yvette.chance8</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
@@ -46001,11 +46001,7 @@
       <c r="F801" t="inlineStr"/>
       <c r="G801" t="inlineStr"/>
       <c r="H801" t="inlineStr"/>
-      <c r="I801" t="inlineStr">
-        <is>
-          <t>Middle Eastern/Arab</t>
-        </is>
-      </c>
+      <c r="I801" t="inlineStr"/>
       <c r="J801" t="inlineStr"/>
       <c r="K801" t="inlineStr"/>
       <c r="L801" t="inlineStr"/>
@@ -46014,22 +46010,22 @@
       </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O801" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P801" s="1" t="n">
-        <v>46208.71684027778</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="Q801" s="1" t="n">
-        <v>46208.71684027778</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="R801" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S801" t="inlineStr">
         <is>
@@ -46046,12 +46042,12 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>zachandmama2</t>
+          <t>zabi.azmhh</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zachandmama2</t>
+          <t>https://www.tiktok.com/@zabi.azmhh</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
@@ -46060,7 +46056,11 @@
       <c r="F802" t="inlineStr"/>
       <c r="G802" t="inlineStr"/>
       <c r="H802" t="inlineStr"/>
-      <c r="I802" t="inlineStr"/>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J802" t="inlineStr"/>
       <c r="K802" t="inlineStr"/>
       <c r="L802" t="inlineStr"/>
@@ -46069,22 +46069,22 @@
       </c>
       <c r="N802" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O802" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P802" s="1" t="n">
-        <v>46192.860625</v>
+        <v>46208.71684027778</v>
       </c>
       <c r="Q802" s="1" t="n">
-        <v>46192.860625</v>
+        <v>46208.71684027778</v>
       </c>
       <c r="R802" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S802" t="inlineStr">
         <is>
@@ -46101,12 +46101,12 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>zaheersheikh786</t>
+          <t>zachandmama2</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zaheersheikh786</t>
+          <t>https://www.tiktok.com/@zachandmama2</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
@@ -46133,10 +46133,10 @@
         </is>
       </c>
       <c r="P803" s="1" t="n">
-        <v>45913.74726851852</v>
+        <v>46192.860625</v>
       </c>
       <c r="Q803" s="1" t="n">
-        <v>45913.74726851852</v>
+        <v>46192.860625</v>
       </c>
       <c r="R803" t="n">
         <v>6</v>
@@ -46156,12 +46156,12 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>zaifa.jahan4</t>
+          <t>zaheersheikh786</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zaifa.jahan4</t>
+          <t>https://www.tiktok.com/@zaheersheikh786</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -46175,7 +46175,7 @@
       <c r="K804" t="inlineStr"/>
       <c r="L804" t="inlineStr"/>
       <c r="M804" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N804" t="inlineStr">
         <is>
@@ -46188,47 +46188,35 @@
         </is>
       </c>
       <c r="P804" s="1" t="n">
-        <v>46210.44793981482</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="Q804" s="1" t="n">
-        <v>46230.33136574074</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="R804" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="S804" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T804" t="n">
-        <v>2</v>
-      </c>
-      <c r="U804" t="n">
-        <v>122.82</v>
-      </c>
-      <c r="V804" t="n">
-        <v>3</v>
-      </c>
-      <c r="W804" t="n">
-        <v>6</v>
-      </c>
-      <c r="X804" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="Y804" t="n">
-        <v>7</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T804" t="inlineStr"/>
+      <c r="U804" t="inlineStr"/>
+      <c r="V804" t="inlineStr"/>
+      <c r="W804" t="inlineStr"/>
+      <c r="X804" t="inlineStr"/>
+      <c r="Y804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>zainab36576</t>
+          <t>zaifa.jahan4</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zainab36576</t>
+          <t>https://www.tiktok.com/@zaifa.jahan4</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
@@ -46237,16 +46225,12 @@
       <c r="F805" t="inlineStr"/>
       <c r="G805" t="inlineStr"/>
       <c r="H805" t="inlineStr"/>
-      <c r="I805" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I805" t="inlineStr"/>
       <c r="J805" t="inlineStr"/>
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="inlineStr"/>
       <c r="M805" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N805" t="inlineStr">
         <is>
@@ -46259,35 +46243,47 @@
         </is>
       </c>
       <c r="P805" s="1" t="n">
-        <v>46244.3722337963</v>
+        <v>46210.44793981482</v>
       </c>
       <c r="Q805" s="1" t="n">
-        <v>46244.3722337963</v>
+        <v>46230.33136574074</v>
       </c>
       <c r="R805" t="n">
+        <v>12</v>
+      </c>
+      <c r="S805" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T805" t="n">
+        <v>2</v>
+      </c>
+      <c r="U805" t="n">
+        <v>122.82</v>
+      </c>
+      <c r="V805" t="n">
+        <v>3</v>
+      </c>
+      <c r="W805" t="n">
         <v>6</v>
       </c>
-      <c r="S805" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T805" t="inlineStr"/>
-      <c r="U805" t="inlineStr"/>
-      <c r="V805" t="inlineStr"/>
-      <c r="W805" t="inlineStr"/>
-      <c r="X805" t="inlineStr"/>
-      <c r="Y805" t="inlineStr"/>
+      <c r="X805" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="Y805" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>zara.hussein2</t>
+          <t>zainab36576</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zara.hussein2</t>
+          <t>https://www.tiktok.com/@zainab36576</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
@@ -46298,7 +46294,7 @@
       <c r="H806" t="inlineStr"/>
       <c r="I806" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J806" t="inlineStr"/>
@@ -46309,22 +46305,22 @@
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O806" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P806" s="1" t="n">
-        <v>46234.76921296296</v>
+        <v>46244.3722337963</v>
       </c>
       <c r="Q806" s="1" t="n">
-        <v>46234.76921296296</v>
+        <v>46244.3722337963</v>
       </c>
       <c r="R806" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S806" t="inlineStr">
         <is>
@@ -46341,12 +46337,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>ze.b20</t>
+          <t>zara.hussein2</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ze.b20</t>
+          <t>https://www.tiktok.com/@zara.hussein2</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
@@ -46355,7 +46351,11 @@
       <c r="F807" t="inlineStr"/>
       <c r="G807" t="inlineStr"/>
       <c r="H807" t="inlineStr"/>
-      <c r="I807" t="inlineStr"/>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J807" t="inlineStr"/>
       <c r="K807" t="inlineStr"/>
       <c r="L807" t="inlineStr"/>
@@ -46373,10 +46373,10 @@
         </is>
       </c>
       <c r="P807" s="1" t="n">
-        <v>46208.82376157407</v>
+        <v>46234.76921296296</v>
       </c>
       <c r="Q807" s="1" t="n">
-        <v>46208.82376157407</v>
+        <v>46234.76921296296</v>
       </c>
       <c r="R807" t="n">
         <v>4.8</v>
@@ -46396,12 +46396,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>zeesummer3</t>
+          <t>ze.b20</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zeesummer3</t>
+          <t>https://www.tiktok.com/@ze.b20</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
@@ -46428,10 +46428,10 @@
         </is>
       </c>
       <c r="P808" s="1" t="n">
-        <v>46234.76131944444</v>
+        <v>46208.82376157407</v>
       </c>
       <c r="Q808" s="1" t="n">
-        <v>46234.76131944444</v>
+        <v>46208.82376157407</v>
       </c>
       <c r="R808" t="n">
         <v>4.8</v>
@@ -46451,12 +46451,12 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>zembii</t>
+          <t>zeesummer3</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zembii</t>
+          <t>https://www.tiktok.com/@zeesummer3</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
@@ -46474,56 +46474,44 @@
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O809" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P809" s="1" t="n">
-        <v>46221.60350694445</v>
+        <v>46234.76131944444</v>
       </c>
       <c r="Q809" s="1" t="n">
-        <v>46221.60350694445</v>
+        <v>46234.76131944444</v>
       </c>
       <c r="R809" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S809" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T809" t="n">
-        <v>2</v>
-      </c>
-      <c r="U809" t="n">
-        <v>0</v>
-      </c>
-      <c r="V809" t="n">
-        <v>0</v>
-      </c>
-      <c r="W809" t="n">
-        <v>6</v>
-      </c>
-      <c r="X809" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="Y809" t="n">
-        <v>3</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T809" t="inlineStr"/>
+      <c r="U809" t="inlineStr"/>
+      <c r="V809" t="inlineStr"/>
+      <c r="W809" t="inlineStr"/>
+      <c r="X809" t="inlineStr"/>
+      <c r="Y809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>zia.choudhury2</t>
+          <t>zembii</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zia.choudhury2</t>
+          <t>https://www.tiktok.com/@zembii</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
@@ -46541,44 +46529,56 @@
       </c>
       <c r="N810" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O810" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P810" s="1" t="n">
-        <v>46209.59967592593</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="Q810" s="1" t="n">
-        <v>46209.59967592593</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="R810" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S810" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T810" t="inlineStr"/>
-      <c r="U810" t="inlineStr"/>
-      <c r="V810" t="inlineStr"/>
-      <c r="W810" t="inlineStr"/>
-      <c r="X810" t="inlineStr"/>
-      <c r="Y810" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T810" t="n">
+        <v>2</v>
+      </c>
+      <c r="U810" t="n">
+        <v>0</v>
+      </c>
+      <c r="V810" t="n">
+        <v>0</v>
+      </c>
+      <c r="W810" t="n">
+        <v>6</v>
+      </c>
+      <c r="X810" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="Y810" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>zommy45</t>
+          <t>zia.choudhury2</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zommy45</t>
+          <t>https://www.tiktok.com/@zia.choudhury2</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
@@ -46587,11 +46587,7 @@
       <c r="F811" t="inlineStr"/>
       <c r="G811" t="inlineStr"/>
       <c r="H811" t="inlineStr"/>
-      <c r="I811" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I811" t="inlineStr"/>
       <c r="J811" t="inlineStr"/>
       <c r="K811" t="inlineStr"/>
       <c r="L811" t="inlineStr"/>
@@ -46609,10 +46605,10 @@
         </is>
       </c>
       <c r="P811" s="1" t="n">
-        <v>46209.55960648148</v>
+        <v>46209.59967592593</v>
       </c>
       <c r="Q811" s="1" t="n">
-        <v>46209.55960648148</v>
+        <v>46209.59967592593</v>
       </c>
       <c r="R811" t="n">
         <v>4.8</v>
@@ -46632,12 +46628,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>zooniasman098</t>
+          <t>zommy45</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zooniasman098</t>
+          <t>https://www.tiktok.com/@zommy45</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
@@ -46646,7 +46642,11 @@
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="inlineStr"/>
       <c r="H812" t="inlineStr"/>
-      <c r="I812" t="inlineStr"/>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J812" t="inlineStr"/>
       <c r="K812" t="inlineStr"/>
       <c r="L812" t="inlineStr"/>
@@ -46664,10 +46664,10 @@
         </is>
       </c>
       <c r="P812" s="1" t="n">
-        <v>46223.54319444444</v>
+        <v>46209.55960648148</v>
       </c>
       <c r="Q812" s="1" t="n">
-        <v>46223.54319444444</v>
+        <v>46209.55960648148</v>
       </c>
       <c r="R812" t="n">
         <v>4.8</v>
@@ -46687,12 +46687,12 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>zoooweemamaa</t>
+          <t>zooniasman098</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zoooweemamaa</t>
+          <t>https://www.tiktok.com/@zooniasman098</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
@@ -46719,10 +46719,10 @@
         </is>
       </c>
       <c r="P813" s="1" t="n">
-        <v>46230.43392361111</v>
+        <v>46223.54319444444</v>
       </c>
       <c r="Q813" s="1" t="n">
-        <v>46230.43392361111</v>
+        <v>46223.54319444444</v>
       </c>
       <c r="R813" t="n">
         <v>4.8</v>
@@ -46739,6 +46739,61 @@
       <c r="X813" t="inlineStr"/>
       <c r="Y813" t="inlineStr"/>
     </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>zoooweemamaa</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@zoooweemamaa</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr"/>
+      <c r="D814" t="inlineStr"/>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="inlineStr"/>
+      <c r="J814" t="inlineStr"/>
+      <c r="K814" t="inlineStr"/>
+      <c r="L814" t="inlineStr"/>
+      <c r="M814" t="n">
+        <v>1</v>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>Lemon Ginger</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>seller</t>
+        </is>
+      </c>
+      <c r="P814" s="1" t="n">
+        <v>46230.43392361111</v>
+      </c>
+      <c r="Q814" s="1" t="n">
+        <v>46230.43392361111</v>
+      </c>
+      <c r="R814" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S814" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T814" t="inlineStr"/>
+      <c r="U814" t="inlineStr"/>
+      <c r="V814" t="inlineStr"/>
+      <c r="W814" t="inlineStr"/>
+      <c r="X814" t="inlineStr"/>
+      <c r="Y814" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -8249,19 +8249,19 @@
         <v>5</v>
       </c>
       <c r="U136" t="n">
-        <v>58.44</v>
+        <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="X136" s="1" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="Y136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -13793,16 +13793,16 @@
         </is>
       </c>
       <c r="T233" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U233" t="n">
-        <v>0</v>
+        <v>30.02</v>
       </c>
       <c r="V233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W233" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="X233" s="1" t="n">
         <v>46246</v>
@@ -15224,15 +15224,27 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T258" t="inlineStr"/>
-      <c r="U258" t="inlineStr"/>
-      <c r="V258" t="inlineStr"/>
-      <c r="W258" t="inlineStr"/>
-      <c r="X258" t="inlineStr"/>
-      <c r="Y258" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T258" t="n">
+        <v>1</v>
+      </c>
+      <c r="U258" t="n">
+        <v>82.29000000000001</v>
+      </c>
+      <c r="V258" t="n">
+        <v>4</v>
+      </c>
+      <c r="W258" t="n">
+        <v>4</v>
+      </c>
+      <c r="X258" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -28849,15 +28861,27 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T497" t="inlineStr"/>
-      <c r="U497" t="inlineStr"/>
-      <c r="V497" t="inlineStr"/>
-      <c r="W497" t="inlineStr"/>
-      <c r="X497" t="inlineStr"/>
-      <c r="Y497" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T497" t="n">
+        <v>1</v>
+      </c>
+      <c r="U497" t="n">
+        <v>0</v>
+      </c>
+      <c r="V497" t="n">
+        <v>0</v>
+      </c>
+      <c r="W497" t="n">
+        <v>13</v>
+      </c>
+      <c r="X497" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="Y497" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -39544,7 +39568,7 @@
         </is>
       </c>
       <c r="T686" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U686" t="n">
         <v>353.8</v>
@@ -39553,7 +39577,7 @@
         <v>6</v>
       </c>
       <c r="W686" t="n">
-        <v>10391</v>
+        <v>11073</v>
       </c>
       <c r="X686" s="1" t="n">
         <v>46244</v>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -619,7 +619,11 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -676,7 +680,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -733,7 +737,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -961,7 +969,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1185,7 +1197,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1409,7 +1425,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1519,7 +1539,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1629,7 +1653,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -2026,7 +2054,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2313,7 +2345,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2545,7 +2581,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2891,7 +2931,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -3017,7 +3061,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -3186,7 +3234,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3469,7 +3521,11 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3634,7 +3690,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3703,7 +3763,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -3760,7 +3820,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -4204,7 +4268,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
@@ -4428,7 +4496,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
@@ -4939,7 +5011,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -5108,7 +5184,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
@@ -5501,7 +5581,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -5556,7 +5640,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
@@ -5611,7 +5699,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
@@ -5666,7 +5758,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
@@ -5890,7 +5986,11 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
@@ -6409,7 +6509,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
@@ -6523,7 +6627,11 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
@@ -6578,7 +6686,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
@@ -6633,7 +6745,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
@@ -6749,7 +6865,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -6981,7 +7097,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -7435,7 +7551,11 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
@@ -7545,7 +7665,11 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
@@ -8064,7 +8188,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
@@ -8340,7 +8468,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
@@ -8568,7 +8700,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
@@ -8767,7 +8903,7 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
@@ -8938,7 +9074,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
@@ -9339,7 +9479,11 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
@@ -9394,7 +9538,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
@@ -9567,7 +9715,11 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
@@ -9734,7 +9886,7 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
@@ -9793,7 +9945,7 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
@@ -9850,7 +10002,11 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
@@ -10353,7 +10509,11 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
@@ -10597,7 +10757,11 @@
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
@@ -10652,7 +10816,11 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
@@ -10764,7 +10932,7 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J180" t="inlineStr"/>
@@ -10876,7 +11044,11 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
@@ -11100,7 +11272,11 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
@@ -11438,7 +11614,11 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
@@ -11717,7 +11897,11 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
@@ -11945,7 +12129,11 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
@@ -12000,7 +12188,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
@@ -12456,7 +12648,11 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
@@ -12631,7 +12827,7 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J213" t="inlineStr"/>
@@ -12690,7 +12886,7 @@
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J214" t="inlineStr"/>
@@ -12806,7 +13002,11 @@
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
@@ -12920,7 +13120,11 @@
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
@@ -13030,7 +13234,11 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
@@ -13486,7 +13694,11 @@
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
@@ -13596,7 +13808,11 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
@@ -13761,7 +13977,11 @@
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
@@ -13828,7 +14048,11 @@
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
@@ -13883,7 +14107,11 @@
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
@@ -14219,7 +14447,7 @@
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J241" t="inlineStr"/>
@@ -14337,7 +14565,7 @@
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -14394,7 +14622,11 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
@@ -14508,7 +14740,11 @@
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
@@ -14575,7 +14811,11 @@
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
@@ -15139,7 +15379,7 @@
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J257" t="inlineStr"/>
@@ -15196,7 +15436,11 @@
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
@@ -15322,7 +15566,11 @@
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
@@ -15377,7 +15625,11 @@
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
@@ -16057,7 +16309,11 @@
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
@@ -16238,7 +16494,11 @@
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
@@ -16427,7 +16687,11 @@
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
@@ -16977,7 +17241,11 @@
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
@@ -17087,7 +17355,11 @@
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
@@ -17197,7 +17469,11 @@
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr"/>
@@ -17307,7 +17583,11 @@
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr"/>
@@ -17834,7 +18114,11 @@
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
@@ -17889,7 +18173,11 @@
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr"/>
@@ -18113,7 +18401,11 @@
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr"/>
@@ -18282,7 +18574,11 @@
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr"/>
@@ -18451,7 +18747,11 @@
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
@@ -18620,7 +18920,11 @@
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr"/>
@@ -19009,7 +19313,11 @@
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr"/>
@@ -19066,7 +19374,7 @@
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="J326" t="inlineStr"/>
@@ -19241,7 +19549,11 @@
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr"/>
@@ -19351,7 +19663,11 @@
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr"/>
@@ -19465,7 +19781,11 @@
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr"/>
@@ -19575,7 +19895,11 @@
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr"/>
@@ -19630,7 +19954,11 @@
       <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr"/>
@@ -19795,7 +20123,11 @@
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
@@ -19909,7 +20241,11 @@
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr"/>
@@ -20033,7 +20369,7 @@
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J343" t="inlineStr"/>
@@ -20265,7 +20601,7 @@
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="J347" t="inlineStr"/>
@@ -20324,7 +20660,7 @@
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J348" t="inlineStr"/>
@@ -20605,7 +20941,11 @@
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr"/>
@@ -20719,7 +21059,11 @@
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr"/>
       <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
@@ -20829,7 +21173,11 @@
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
@@ -20939,7 +21287,11 @@
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr"/>
@@ -21049,7 +21401,11 @@
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr"/>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
@@ -21175,7 +21531,11 @@
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr"/>
@@ -21285,7 +21645,11 @@
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
@@ -21340,7 +21704,11 @@
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr"/>
@@ -21450,7 +21818,11 @@
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr"/>
@@ -21560,7 +21932,11 @@
       <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr"/>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr"/>
@@ -21906,7 +22282,11 @@
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr"/>
@@ -22413,7 +22793,11 @@
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr"/>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr"/>
@@ -22523,7 +22907,11 @@
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
-      <c r="I387" t="inlineStr"/>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
@@ -22578,7 +22966,11 @@
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr"/>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
@@ -22700,7 +23092,11 @@
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr"/>
-      <c r="I390" t="inlineStr"/>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr"/>
@@ -22755,7 +23151,11 @@
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr"/>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
@@ -23364,7 +23764,11 @@
       <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr"/>
@@ -23486,7 +23890,11 @@
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
-      <c r="I404" t="inlineStr"/>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr"/>
@@ -23541,7 +23949,11 @@
       <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr"/>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr"/>
@@ -23596,7 +24008,11 @@
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
-      <c r="I406" t="inlineStr"/>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr"/>
@@ -23663,7 +24079,11 @@
       <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr"/>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr"/>
@@ -23883,7 +24303,11 @@
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr"/>
-      <c r="I411" t="inlineStr"/>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr"/>
@@ -23993,7 +24417,11 @@
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr"/>
-      <c r="I413" t="inlineStr"/>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr"/>
@@ -24217,7 +24645,11 @@
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr"/>
-      <c r="I417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr"/>
@@ -24272,7 +24704,11 @@
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr"/>
-      <c r="I418" t="inlineStr"/>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr"/>
@@ -24732,7 +25168,11 @@
       <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr"/>
-      <c r="I426" t="inlineStr"/>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr"/>
@@ -24976,7 +25416,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I430" t="inlineStr"/>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J430" t="inlineStr">
         <is>
           <t>5.85</t>
@@ -25216,7 +25660,11 @@
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr"/>
-      <c r="I434" t="inlineStr"/>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr"/>
@@ -25332,7 +25780,7 @@
       <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="J436" t="inlineStr"/>
@@ -25499,7 +25947,11 @@
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr"/>
-      <c r="I439" t="inlineStr"/>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
@@ -25611,7 +26063,7 @@
       <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="J441" t="inlineStr"/>
@@ -25668,7 +26120,11 @@
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr"/>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
@@ -26242,7 +26698,11 @@
       <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr"/>
-      <c r="I452" t="inlineStr"/>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr"/>
@@ -26297,7 +26757,11 @@
       <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr"/>
-      <c r="I453" t="inlineStr"/>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr"/>
@@ -26407,7 +26871,11 @@
       <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr"/>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr"/>
@@ -26753,7 +27221,11 @@
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr"/>
-      <c r="I461" t="inlineStr"/>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr"/>
@@ -27225,7 +27697,11 @@
       <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr"/>
-      <c r="I469" t="inlineStr"/>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
@@ -27736,7 +28212,11 @@
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr"/>
-      <c r="I478" t="inlineStr"/>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr"/>
@@ -27791,7 +28271,11 @@
       <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr"/>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr"/>
@@ -27917,7 +28401,11 @@
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr"/>
-      <c r="I481" t="inlineStr"/>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr"/>
@@ -28204,7 +28692,11 @@
       <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr"/>
       <c r="H486" t="inlineStr"/>
-      <c r="I486" t="inlineStr"/>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr"/>
       <c r="L486" t="inlineStr"/>
@@ -28259,7 +28751,11 @@
       <c r="F487" t="inlineStr"/>
       <c r="G487" t="inlineStr"/>
       <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr"/>
       <c r="L487" t="inlineStr"/>
@@ -29289,7 +29785,11 @@
       <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr"/>
       <c r="H505" t="inlineStr"/>
-      <c r="I505" t="inlineStr"/>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr"/>
@@ -29454,7 +29954,11 @@
       <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr"/>
       <c r="H508" t="inlineStr"/>
-      <c r="I508" t="inlineStr"/>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr"/>
@@ -29564,7 +30068,11 @@
       <c r="F510" t="inlineStr"/>
       <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr"/>
-      <c r="I510" t="inlineStr"/>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr"/>
@@ -29847,7 +30355,11 @@
       <c r="F515" t="inlineStr"/>
       <c r="G515" t="inlineStr"/>
       <c r="H515" t="inlineStr"/>
-      <c r="I515" t="inlineStr"/>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr"/>
@@ -29961,7 +30473,11 @@
       <c r="F517" t="inlineStr"/>
       <c r="G517" t="inlineStr"/>
       <c r="H517" t="inlineStr"/>
-      <c r="I517" t="inlineStr"/>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr"/>
@@ -30468,7 +30984,11 @@
       <c r="F526" t="inlineStr"/>
       <c r="G526" t="inlineStr"/>
       <c r="H526" t="inlineStr"/>
-      <c r="I526" t="inlineStr"/>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr"/>
       <c r="L526" t="inlineStr"/>
@@ -31148,7 +31668,11 @@
       <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr"/>
-      <c r="I538" t="inlineStr"/>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr"/>
       <c r="L538" t="inlineStr"/>
@@ -31203,7 +31727,11 @@
       <c r="F539" t="inlineStr"/>
       <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr"/>
-      <c r="I539" t="inlineStr"/>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr"/>
       <c r="L539" t="inlineStr"/>
@@ -31258,7 +31786,11 @@
       <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr"/>
-      <c r="I540" t="inlineStr"/>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr"/>
       <c r="L540" t="inlineStr"/>
@@ -31368,7 +31900,11 @@
       <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr"/>
       <c r="H542" t="inlineStr"/>
-      <c r="I542" t="inlineStr"/>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr"/>
       <c r="L542" t="inlineStr"/>
@@ -31478,7 +32014,11 @@
       <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr"/>
       <c r="H544" t="inlineStr"/>
-      <c r="I544" t="inlineStr"/>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr"/>
       <c r="L544" t="inlineStr"/>
@@ -31653,7 +32193,7 @@
       <c r="H547" t="inlineStr"/>
       <c r="I547" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J547" t="inlineStr"/>
@@ -32174,7 +32714,11 @@
       <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr"/>
       <c r="H556" t="inlineStr"/>
-      <c r="I556" t="inlineStr"/>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr"/>
       <c r="L556" t="inlineStr"/>
@@ -32457,7 +33001,11 @@
       <c r="F561" t="inlineStr"/>
       <c r="G561" t="inlineStr"/>
       <c r="H561" t="inlineStr"/>
-      <c r="I561" t="inlineStr"/>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr"/>
       <c r="L561" t="inlineStr"/>
@@ -32681,7 +33229,11 @@
       <c r="F565" t="inlineStr"/>
       <c r="G565" t="inlineStr"/>
       <c r="H565" t="inlineStr"/>
-      <c r="I565" t="inlineStr"/>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr"/>
       <c r="L565" t="inlineStr"/>
@@ -32901,7 +33453,11 @@
       <c r="F569" t="inlineStr"/>
       <c r="G569" t="inlineStr"/>
       <c r="H569" t="inlineStr"/>
-      <c r="I569" t="inlineStr"/>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr"/>
       <c r="L569" t="inlineStr"/>
@@ -32956,7 +33512,11 @@
       <c r="F570" t="inlineStr"/>
       <c r="G570" t="inlineStr"/>
       <c r="H570" t="inlineStr"/>
-      <c r="I570" t="inlineStr"/>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr"/>
       <c r="L570" t="inlineStr"/>
@@ -33408,7 +33968,11 @@
       <c r="F578" t="inlineStr"/>
       <c r="G578" t="inlineStr"/>
       <c r="H578" t="inlineStr"/>
-      <c r="I578" t="inlineStr"/>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr"/>
       <c r="L578" t="inlineStr"/>
@@ -33852,7 +34416,11 @@
       <c r="F586" t="inlineStr"/>
       <c r="G586" t="inlineStr"/>
       <c r="H586" t="inlineStr"/>
-      <c r="I586" t="inlineStr"/>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr"/>
       <c r="L586" t="inlineStr"/>
@@ -34019,7 +34587,7 @@
       <c r="H589" t="inlineStr"/>
       <c r="I589" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J589" t="inlineStr"/>
@@ -34245,7 +34813,11 @@
       <c r="F593" t="inlineStr"/>
       <c r="G593" t="inlineStr"/>
       <c r="H593" t="inlineStr"/>
-      <c r="I593" t="inlineStr"/>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr"/>
       <c r="L593" t="inlineStr"/>
@@ -34422,7 +34994,11 @@
       <c r="F596" t="inlineStr"/>
       <c r="G596" t="inlineStr"/>
       <c r="H596" t="inlineStr"/>
-      <c r="I596" t="inlineStr"/>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr"/>
       <c r="L596" t="inlineStr"/>
@@ -34532,7 +35108,11 @@
       <c r="F598" t="inlineStr"/>
       <c r="G598" t="inlineStr"/>
       <c r="H598" t="inlineStr"/>
-      <c r="I598" t="inlineStr"/>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr"/>
@@ -34752,7 +35332,11 @@
       <c r="F602" t="inlineStr"/>
       <c r="G602" t="inlineStr"/>
       <c r="H602" t="inlineStr"/>
-      <c r="I602" t="inlineStr"/>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr"/>
@@ -34929,7 +35513,11 @@
       <c r="F605" t="inlineStr"/>
       <c r="G605" t="inlineStr"/>
       <c r="H605" t="inlineStr"/>
-      <c r="I605" t="inlineStr"/>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr"/>
@@ -34984,7 +35572,11 @@
       <c r="F606" t="inlineStr"/>
       <c r="G606" t="inlineStr"/>
       <c r="H606" t="inlineStr"/>
-      <c r="I606" t="inlineStr"/>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr"/>
@@ -35263,7 +35855,11 @@
       <c r="F611" t="inlineStr"/>
       <c r="G611" t="inlineStr"/>
       <c r="H611" t="inlineStr"/>
-      <c r="I611" t="inlineStr"/>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr"/>
       <c r="L611" t="inlineStr"/>
@@ -35660,7 +36256,11 @@
       <c r="F618" t="inlineStr"/>
       <c r="G618" t="inlineStr"/>
       <c r="H618" t="inlineStr"/>
-      <c r="I618" t="inlineStr"/>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr"/>
       <c r="L618" t="inlineStr"/>
@@ -35939,7 +36539,11 @@
       <c r="F623" t="inlineStr"/>
       <c r="G623" t="inlineStr"/>
       <c r="H623" t="inlineStr"/>
-      <c r="I623" t="inlineStr"/>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr"/>
       <c r="L623" t="inlineStr"/>
@@ -36049,7 +36653,11 @@
       <c r="F625" t="inlineStr"/>
       <c r="G625" t="inlineStr"/>
       <c r="H625" t="inlineStr"/>
-      <c r="I625" t="inlineStr"/>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr"/>
@@ -36344,7 +36952,11 @@
       <c r="F630" t="inlineStr"/>
       <c r="G630" t="inlineStr"/>
       <c r="H630" t="inlineStr"/>
-      <c r="I630" t="inlineStr"/>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr"/>
       <c r="L630" t="inlineStr"/>
@@ -36741,7 +37353,11 @@
       <c r="F637" t="inlineStr"/>
       <c r="G637" t="inlineStr"/>
       <c r="H637" t="inlineStr"/>
-      <c r="I637" t="inlineStr"/>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J637" t="inlineStr"/>
       <c r="K637" t="inlineStr"/>
       <c r="L637" t="inlineStr"/>
@@ -36851,7 +37467,11 @@
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="inlineStr"/>
       <c r="H639" t="inlineStr"/>
-      <c r="I639" t="inlineStr"/>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J639" t="inlineStr"/>
       <c r="K639" t="inlineStr"/>
       <c r="L639" t="inlineStr"/>
@@ -37079,7 +37699,11 @@
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="inlineStr"/>
       <c r="H643" t="inlineStr"/>
-      <c r="I643" t="inlineStr"/>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr"/>
       <c r="L643" t="inlineStr"/>
@@ -37136,7 +37760,7 @@
       <c r="H644" t="inlineStr"/>
       <c r="I644" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J644" t="inlineStr"/>
@@ -37250,7 +37874,7 @@
       <c r="H646" t="inlineStr"/>
       <c r="I646" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J646" t="inlineStr"/>
@@ -37362,7 +37986,11 @@
       <c r="F648" t="inlineStr"/>
       <c r="G648" t="inlineStr"/>
       <c r="H648" t="inlineStr"/>
-      <c r="I648" t="inlineStr"/>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J648" t="inlineStr"/>
       <c r="K648" t="inlineStr"/>
       <c r="L648" t="inlineStr"/>
@@ -37527,7 +38155,11 @@
       <c r="F651" t="inlineStr"/>
       <c r="G651" t="inlineStr"/>
       <c r="H651" t="inlineStr"/>
-      <c r="I651" t="inlineStr"/>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="inlineStr"/>
       <c r="L651" t="inlineStr"/>
@@ -37641,7 +38273,11 @@
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr"/>
-      <c r="I653" t="inlineStr"/>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J653" t="inlineStr"/>
       <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr"/>
@@ -37810,7 +38446,11 @@
       <c r="F656" t="inlineStr"/>
       <c r="G656" t="inlineStr"/>
       <c r="H656" t="inlineStr"/>
-      <c r="I656" t="inlineStr"/>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J656" t="inlineStr"/>
       <c r="K656" t="inlineStr"/>
       <c r="L656" t="inlineStr"/>
@@ -37979,7 +38619,11 @@
       <c r="F659" t="inlineStr"/>
       <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr"/>
-      <c r="I659" t="inlineStr"/>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J659" t="inlineStr"/>
       <c r="K659" t="inlineStr"/>
       <c r="L659" t="inlineStr"/>
@@ -38374,7 +39018,7 @@
       <c r="H666" t="inlineStr"/>
       <c r="I666" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J666" t="inlineStr"/>
@@ -38608,7 +39252,11 @@
       <c r="F670" t="inlineStr"/>
       <c r="G670" t="inlineStr"/>
       <c r="H670" t="inlineStr"/>
-      <c r="I670" t="inlineStr"/>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J670" t="inlineStr"/>
       <c r="K670" t="inlineStr"/>
       <c r="L670" t="inlineStr"/>
@@ -38844,7 +39492,11 @@
       <c r="F674" t="inlineStr"/>
       <c r="G674" t="inlineStr"/>
       <c r="H674" t="inlineStr"/>
-      <c r="I674" t="inlineStr"/>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J674" t="inlineStr"/>
       <c r="K674" t="inlineStr"/>
       <c r="L674" t="inlineStr"/>
@@ -39068,7 +39720,11 @@
       <c r="F678" t="inlineStr"/>
       <c r="G678" t="inlineStr"/>
       <c r="H678" t="inlineStr"/>
-      <c r="I678" t="inlineStr"/>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J678" t="inlineStr"/>
       <c r="K678" t="inlineStr"/>
       <c r="L678" t="inlineStr"/>
@@ -39178,7 +39834,11 @@
       <c r="F680" t="inlineStr"/>
       <c r="G680" t="inlineStr"/>
       <c r="H680" t="inlineStr"/>
-      <c r="I680" t="inlineStr"/>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J680" t="inlineStr"/>
       <c r="K680" t="inlineStr"/>
       <c r="L680" t="inlineStr"/>
@@ -39414,7 +40074,11 @@
       <c r="F684" t="inlineStr"/>
       <c r="G684" t="inlineStr"/>
       <c r="H684" t="inlineStr"/>
-      <c r="I684" t="inlineStr"/>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J684" t="inlineStr"/>
       <c r="K684" t="inlineStr"/>
       <c r="L684" t="inlineStr"/>
@@ -39481,7 +40145,11 @@
       <c r="F685" t="inlineStr"/>
       <c r="G685" t="inlineStr"/>
       <c r="H685" t="inlineStr"/>
-      <c r="I685" t="inlineStr"/>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J685" t="inlineStr"/>
       <c r="K685" t="inlineStr"/>
       <c r="L685" t="inlineStr"/>
@@ -39536,7 +40204,11 @@
       <c r="F686" t="inlineStr"/>
       <c r="G686" t="inlineStr"/>
       <c r="H686" t="inlineStr"/>
-      <c r="I686" t="inlineStr"/>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J686" t="inlineStr"/>
       <c r="K686" t="inlineStr"/>
       <c r="L686" t="inlineStr"/>
@@ -39603,7 +40275,11 @@
       <c r="F687" t="inlineStr"/>
       <c r="G687" t="inlineStr"/>
       <c r="H687" t="inlineStr"/>
-      <c r="I687" t="inlineStr"/>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J687" t="inlineStr"/>
       <c r="K687" t="inlineStr"/>
       <c r="L687" t="inlineStr"/>
@@ -39658,7 +40334,11 @@
       <c r="F688" t="inlineStr"/>
       <c r="G688" t="inlineStr"/>
       <c r="H688" t="inlineStr"/>
-      <c r="I688" t="inlineStr"/>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J688" t="inlineStr"/>
       <c r="K688" t="inlineStr"/>
       <c r="L688" t="inlineStr"/>
@@ -39780,7 +40460,11 @@
       <c r="F690" t="inlineStr"/>
       <c r="G690" t="inlineStr"/>
       <c r="H690" t="inlineStr"/>
-      <c r="I690" t="inlineStr"/>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J690" t="inlineStr"/>
       <c r="K690" t="inlineStr"/>
       <c r="L690" t="inlineStr"/>
@@ -40024,7 +40708,11 @@
       <c r="F694" t="inlineStr"/>
       <c r="G694" t="inlineStr"/>
       <c r="H694" t="inlineStr"/>
-      <c r="I694" t="inlineStr"/>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J694" t="inlineStr"/>
       <c r="K694" t="inlineStr"/>
       <c r="L694" t="inlineStr"/>
@@ -40468,7 +41156,11 @@
       <c r="F702" t="inlineStr"/>
       <c r="G702" t="inlineStr"/>
       <c r="H702" t="inlineStr"/>
-      <c r="I702" t="inlineStr"/>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J702" t="inlineStr"/>
       <c r="K702" t="inlineStr"/>
       <c r="L702" t="inlineStr"/>
@@ -40802,7 +41494,11 @@
       <c r="F708" t="inlineStr"/>
       <c r="G708" t="inlineStr"/>
       <c r="H708" t="inlineStr"/>
-      <c r="I708" t="inlineStr"/>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J708" t="inlineStr"/>
       <c r="K708" t="inlineStr"/>
       <c r="L708" t="inlineStr"/>
@@ -40918,7 +41614,7 @@
       <c r="H710" t="inlineStr"/>
       <c r="I710" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J710" t="inlineStr"/>
@@ -41144,7 +41840,11 @@
       <c r="F714" t="inlineStr"/>
       <c r="G714" t="inlineStr"/>
       <c r="H714" t="inlineStr"/>
-      <c r="I714" t="inlineStr"/>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J714" t="inlineStr"/>
       <c r="K714" t="inlineStr"/>
       <c r="L714" t="inlineStr"/>
@@ -41199,7 +41899,11 @@
       <c r="F715" t="inlineStr"/>
       <c r="G715" t="inlineStr"/>
       <c r="H715" t="inlineStr"/>
-      <c r="I715" t="inlineStr"/>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J715" t="inlineStr"/>
       <c r="K715" t="inlineStr"/>
       <c r="L715" t="inlineStr"/>
@@ -41256,7 +41960,7 @@
       <c r="H716" t="inlineStr"/>
       <c r="I716" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="J716" t="inlineStr"/>
@@ -41368,7 +42072,11 @@
       <c r="F718" t="inlineStr"/>
       <c r="G718" t="inlineStr"/>
       <c r="H718" t="inlineStr"/>
-      <c r="I718" t="inlineStr"/>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J718" t="inlineStr"/>
       <c r="K718" t="inlineStr"/>
       <c r="L718" t="inlineStr"/>
@@ -41425,7 +42133,7 @@
       <c r="H719" t="inlineStr"/>
       <c r="I719" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J719" t="inlineStr"/>
@@ -41482,7 +42190,11 @@
       <c r="F720" t="inlineStr"/>
       <c r="G720" t="inlineStr"/>
       <c r="H720" t="inlineStr"/>
-      <c r="I720" t="inlineStr"/>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J720" t="inlineStr"/>
       <c r="K720" t="inlineStr"/>
       <c r="L720" t="inlineStr"/>
@@ -41649,7 +42361,7 @@
       <c r="H723" t="inlineStr"/>
       <c r="I723" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J723" t="inlineStr"/>
@@ -41816,7 +42528,11 @@
       <c r="F726" t="inlineStr"/>
       <c r="G726" t="inlineStr"/>
       <c r="H726" t="inlineStr"/>
-      <c r="I726" t="inlineStr"/>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J726" t="inlineStr"/>
       <c r="K726" t="inlineStr"/>
       <c r="L726" t="inlineStr"/>
@@ -42335,7 +43051,11 @@
       <c r="F735" t="inlineStr"/>
       <c r="G735" t="inlineStr"/>
       <c r="H735" t="inlineStr"/>
-      <c r="I735" t="inlineStr"/>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J735" t="inlineStr"/>
       <c r="K735" t="inlineStr"/>
       <c r="L735" t="inlineStr"/>
@@ -42669,7 +43389,11 @@
       <c r="F741" t="inlineStr"/>
       <c r="G741" t="inlineStr"/>
       <c r="H741" t="inlineStr"/>
-      <c r="I741" t="inlineStr"/>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J741" t="inlineStr"/>
       <c r="K741" t="inlineStr"/>
       <c r="L741" t="inlineStr"/>
@@ -44516,7 +45240,11 @@
       <c r="F774" t="inlineStr"/>
       <c r="G774" t="inlineStr"/>
       <c r="H774" t="inlineStr"/>
-      <c r="I774" t="inlineStr"/>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J774" t="inlineStr"/>
       <c r="K774" t="inlineStr"/>
       <c r="L774" t="inlineStr"/>
@@ -44626,7 +45354,11 @@
       <c r="F776" t="inlineStr"/>
       <c r="G776" t="inlineStr"/>
       <c r="H776" t="inlineStr"/>
-      <c r="I776" t="inlineStr"/>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J776" t="inlineStr"/>
       <c r="K776" t="inlineStr"/>
       <c r="L776" t="inlineStr"/>
@@ -45074,7 +45806,11 @@
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="inlineStr"/>
       <c r="H784" t="inlineStr"/>
-      <c r="I784" t="inlineStr"/>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J784" t="inlineStr"/>
       <c r="K784" t="inlineStr"/>
       <c r="L784" t="inlineStr"/>
@@ -45184,7 +45920,11 @@
       <c r="F786" t="inlineStr"/>
       <c r="G786" t="inlineStr"/>
       <c r="H786" t="inlineStr"/>
-      <c r="I786" t="inlineStr"/>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J786" t="inlineStr"/>
       <c r="K786" t="inlineStr"/>
       <c r="L786" t="inlineStr"/>
@@ -45294,7 +46034,11 @@
       <c r="F788" t="inlineStr"/>
       <c r="G788" t="inlineStr"/>
       <c r="H788" t="inlineStr"/>
-      <c r="I788" t="inlineStr"/>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J788" t="inlineStr"/>
       <c r="K788" t="inlineStr"/>
       <c r="L788" t="inlineStr"/>
@@ -45349,7 +46093,11 @@
       <c r="F789" t="inlineStr"/>
       <c r="G789" t="inlineStr"/>
       <c r="H789" t="inlineStr"/>
-      <c r="I789" t="inlineStr"/>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J789" t="inlineStr"/>
       <c r="K789" t="inlineStr"/>
       <c r="L789" t="inlineStr"/>
@@ -45463,7 +46211,11 @@
       <c r="F791" t="inlineStr"/>
       <c r="G791" t="inlineStr"/>
       <c r="H791" t="inlineStr"/>
-      <c r="I791" t="inlineStr"/>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J791" t="inlineStr"/>
       <c r="K791" t="inlineStr"/>
       <c r="L791" t="inlineStr"/>
@@ -45518,7 +46270,11 @@
       <c r="F792" t="inlineStr"/>
       <c r="G792" t="inlineStr"/>
       <c r="H792" t="inlineStr"/>
-      <c r="I792" t="inlineStr"/>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J792" t="inlineStr"/>
       <c r="K792" t="inlineStr"/>
       <c r="L792" t="inlineStr"/>
@@ -46139,7 +46895,11 @@
       <c r="F803" t="inlineStr"/>
       <c r="G803" t="inlineStr"/>
       <c r="H803" t="inlineStr"/>
-      <c r="I803" t="inlineStr"/>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J803" t="inlineStr"/>
       <c r="K803" t="inlineStr"/>
       <c r="L803" t="inlineStr"/>
@@ -46249,7 +47009,11 @@
       <c r="F805" t="inlineStr"/>
       <c r="G805" t="inlineStr"/>
       <c r="H805" t="inlineStr"/>
-      <c r="I805" t="inlineStr"/>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J805" t="inlineStr"/>
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="inlineStr"/>
@@ -46377,7 +47141,7 @@
       <c r="H807" t="inlineStr"/>
       <c r="I807" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J807" t="inlineStr"/>
@@ -46544,7 +47308,11 @@
       <c r="F810" t="inlineStr"/>
       <c r="G810" t="inlineStr"/>
       <c r="H810" t="inlineStr"/>
-      <c r="I810" t="inlineStr"/>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J810" t="inlineStr"/>
       <c r="K810" t="inlineStr"/>
       <c r="L810" t="inlineStr"/>
@@ -46725,7 +47493,11 @@
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="inlineStr"/>
       <c r="H813" t="inlineStr"/>
-      <c r="I813" t="inlineStr"/>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J813" t="inlineStr"/>
       <c r="K813" t="inlineStr"/>
       <c r="L813" t="inlineStr"/>
@@ -46780,7 +47552,11 @@
       <c r="F814" t="inlineStr"/>
       <c r="G814" t="inlineStr"/>
       <c r="H814" t="inlineStr"/>
-      <c r="I814" t="inlineStr"/>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J814" t="inlineStr"/>
       <c r="K814" t="inlineStr"/>
       <c r="L814" t="inlineStr"/>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -564,7 +564,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -796,7 +800,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1028,7 +1036,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1197,7 +1209,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1370,7 +1386,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1425,7 +1445,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1539,7 +1563,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1653,7 +1681,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1944,7 +1976,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1999,7 +2035,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -2054,7 +2094,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2227,7 +2271,11 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2471,7 +2519,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2526,7 +2578,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2581,7 +2637,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2750,7 +2810,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2805,7 +2869,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2931,7 +2999,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2986,7 +3058,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -3348,7 +3424,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3521,7 +3601,11 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3576,7 +3660,11 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3749,7 +3837,11 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3804,7 +3896,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -4048,7 +4144,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
@@ -4103,7 +4203,11 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
@@ -4158,7 +4262,11 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
@@ -4213,7 +4321,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -4268,7 +4380,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
@@ -4309,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="X66" s="1" t="n">
         <v>46252</v>
@@ -4394,7 +4510,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
@@ -4567,7 +4687,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -4622,7 +4746,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -4795,7 +4923,11 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
@@ -4850,7 +4982,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
@@ -5023,7 +5159,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -5078,7 +5218,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
@@ -5251,7 +5395,11 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
@@ -5424,7 +5572,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
@@ -5479,7 +5631,11 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
@@ -5593,7 +5749,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -5648,7 +5808,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
@@ -5998,7 +6162,11 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
@@ -6053,7 +6221,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
@@ -6226,7 +6398,11 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
@@ -6340,7 +6516,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
@@ -6395,7 +6575,11 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
@@ -6450,7 +6634,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -6517,7 +6705,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
@@ -7162,7 +7354,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
@@ -7453,7 +7649,11 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
@@ -7508,7 +7708,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
@@ -7563,7 +7767,11 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
@@ -7677,7 +7885,11 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
@@ -7791,7 +8003,11 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
@@ -8141,7 +8357,11 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
@@ -8255,7 +8475,11 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
@@ -8440,7 +8664,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
@@ -8511,7 +8739,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>0.41</t>
@@ -8555,7 +8787,7 @@
         </is>
       </c>
       <c r="T139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -8564,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X139" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="Y139" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140">
@@ -8708,7 +8940,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
@@ -8940,7 +9176,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
@@ -9141,7 +9381,11 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
@@ -9491,7 +9735,11 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
@@ -9546,7 +9794,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
@@ -9955,7 +10207,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
@@ -10010,7 +10266,11 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
@@ -10301,7 +10561,11 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
@@ -10356,7 +10620,11 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
@@ -10411,7 +10679,11 @@
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
@@ -10466,7 +10738,11 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
@@ -10580,7 +10856,11 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
@@ -10635,7 +10915,11 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
@@ -11056,7 +11340,11 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
@@ -11170,7 +11458,11 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
@@ -11284,7 +11576,11 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
@@ -11398,7 +11694,11 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
@@ -11512,7 +11812,11 @@
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
@@ -11567,7 +11871,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
@@ -11740,7 +12048,11 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
@@ -11913,7 +12225,11 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
@@ -11968,7 +12284,11 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
@@ -12023,7 +12343,11 @@
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
@@ -12196,7 +12520,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
@@ -12487,7 +12815,11 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
@@ -12660,7 +12992,11 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
@@ -12715,7 +13051,11 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
@@ -13360,7 +13700,11 @@
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
@@ -13474,7 +13818,11 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
@@ -13647,7 +13995,11 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
@@ -13761,7 +14113,11 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
@@ -13934,7 +14290,11 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
@@ -14048,7 +14408,11 @@
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
@@ -14103,7 +14467,11 @@
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
@@ -14194,7 +14562,7 @@
         </is>
       </c>
       <c r="T236" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U236" t="n">
         <v>55.01</v>
@@ -14203,7 +14571,7 @@
         <v>3</v>
       </c>
       <c r="W236" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="X236" s="1" t="n">
         <v>46246</v>
@@ -14347,7 +14715,11 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
@@ -14461,7 +14833,11 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
@@ -14516,7 +14892,11 @@
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
@@ -14571,7 +14951,11 @@
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
@@ -15106,7 +15490,11 @@
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr"/>
@@ -15161,7 +15549,11 @@
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
@@ -15275,7 +15667,11 @@
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
@@ -15330,7 +15726,11 @@
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
@@ -15385,7 +15785,11 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
@@ -15558,7 +15962,11 @@
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
@@ -15708,16 +16116,16 @@
         </is>
       </c>
       <c r="T262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U262" t="n">
-        <v>107.28</v>
+        <v>128.52</v>
       </c>
       <c r="V262" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W262" t="n">
-        <v>68</v>
+        <v>1442</v>
       </c>
       <c r="X262" s="1" t="n">
         <v>46251</v>
@@ -16038,7 +16446,11 @@
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
@@ -16211,7 +16623,11 @@
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
@@ -16266,7 +16682,11 @@
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
@@ -16380,7 +16800,11 @@
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
@@ -16435,7 +16859,11 @@
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
@@ -16490,7 +16918,11 @@
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
@@ -16675,7 +17107,11 @@
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
@@ -16801,7 +17237,11 @@
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
@@ -16868,7 +17308,11 @@
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
-      <c r="I282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr"/>
@@ -16982,7 +17426,11 @@
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
@@ -17037,7 +17485,11 @@
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
@@ -17092,7 +17544,11 @@
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
@@ -17147,7 +17603,11 @@
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
@@ -17202,7 +17662,11 @@
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
@@ -17257,7 +17721,11 @@
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
@@ -17312,7 +17780,11 @@
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
@@ -17367,7 +17839,11 @@
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
@@ -17422,7 +17898,11 @@
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
@@ -17536,7 +18016,11 @@
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
@@ -17650,7 +18134,11 @@
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
@@ -17764,7 +18252,11 @@
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr"/>
@@ -17949,7 +18441,11 @@
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr"/>
@@ -18063,7 +18559,11 @@
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr"/>
@@ -18118,7 +18618,11 @@
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
@@ -18185,7 +18689,11 @@
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr"/>
@@ -18240,7 +18748,11 @@
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
-      <c r="I306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr"/>
@@ -18295,7 +18807,11 @@
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
-      <c r="I307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr"/>
@@ -18468,7 +18984,11 @@
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr"/>
@@ -18582,7 +19102,11 @@
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr"/>
@@ -18755,7 +19279,11 @@
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
@@ -18928,7 +19456,11 @@
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr"/>
@@ -19042,7 +19574,11 @@
       <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr"/>
@@ -19215,7 +19751,11 @@
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr"/>
@@ -19270,7 +19810,11 @@
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr"/>
@@ -19325,7 +19869,11 @@
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr"/>
@@ -19380,7 +19928,11 @@
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr"/>
@@ -19435,7 +19987,11 @@
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
@@ -19903,7 +20459,11 @@
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr"/>
@@ -20135,7 +20695,11 @@
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
@@ -20308,7 +20872,11 @@
       <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr"/>
@@ -20363,7 +20931,11 @@
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
@@ -20607,7 +21179,11 @@
       <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr"/>
@@ -20839,7 +21415,11 @@
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr"/>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr"/>
@@ -21071,7 +21651,11 @@
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr"/>
       <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
@@ -21126,7 +21710,11 @@
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr"/>
@@ -21181,7 +21769,11 @@
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
@@ -21413,7 +22005,11 @@
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr"/>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
@@ -21527,7 +22123,11 @@
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr"/>
@@ -21641,7 +22241,11 @@
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
@@ -21885,7 +22489,11 @@
       <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr"/>
@@ -22058,7 +22666,11 @@
       <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr"/>
@@ -22172,7 +22784,11 @@
       <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr"/>
-      <c r="I374" t="inlineStr"/>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr"/>
@@ -22345,7 +22961,11 @@
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr"/>
-      <c r="I377" t="inlineStr"/>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
@@ -22636,7 +23256,11 @@
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr"/>
-      <c r="I382" t="inlineStr"/>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr"/>
@@ -22691,7 +23315,11 @@
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
-      <c r="I383" t="inlineStr"/>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr"/>
@@ -22864,7 +23492,11 @@
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
-      <c r="I386" t="inlineStr"/>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr"/>
@@ -22919,7 +23551,11 @@
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
-      <c r="I387" t="inlineStr"/>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
@@ -22974,7 +23610,11 @@
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr"/>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
@@ -23147,7 +23787,11 @@
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr"/>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
@@ -23332,7 +23976,11 @@
       <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
-      <c r="I394" t="inlineStr"/>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr"/>
@@ -23505,7 +24153,11 @@
       <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr"/>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr"/>
@@ -23560,7 +24212,11 @@
       <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr"/>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr"/>
@@ -23615,7 +24271,11 @@
       <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
-      <c r="I399" t="inlineStr"/>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr"/>
@@ -23670,7 +24330,11 @@
       <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr"/>
-      <c r="I400" t="inlineStr"/>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr"/>
@@ -23725,7 +24389,11 @@
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr"/>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr"/>
@@ -23780,7 +24448,11 @@
       <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr"/>
@@ -23835,7 +24507,11 @@
       <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr"/>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr"/>
@@ -23890,7 +24566,11 @@
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
-      <c r="I404" t="inlineStr"/>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr"/>
@@ -24004,7 +24684,11 @@
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
-      <c r="I406" t="inlineStr"/>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr"/>
@@ -24130,7 +24814,11 @@
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr"/>
-      <c r="I408" t="inlineStr"/>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr"/>
@@ -24433,7 +25121,11 @@
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr"/>
-      <c r="I413" t="inlineStr"/>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr"/>
@@ -24488,7 +25180,11 @@
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr"/>
-      <c r="I414" t="inlineStr"/>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr"/>
@@ -24543,7 +25239,11 @@
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr"/>
-      <c r="I415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr"/>
@@ -24657,7 +25357,11 @@
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr"/>
-      <c r="I417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr"/>
@@ -24771,7 +25475,11 @@
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr"/>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr"/>
@@ -24885,7 +25593,11 @@
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr"/>
       <c r="H421" t="inlineStr"/>
-      <c r="I421" t="inlineStr"/>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr"/>
@@ -25129,7 +25841,11 @@
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr"/>
-      <c r="I425" t="inlineStr"/>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr"/>
@@ -25184,7 +25900,11 @@
       <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr"/>
-      <c r="I426" t="inlineStr"/>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr"/>
@@ -25239,7 +25959,11 @@
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr"/>
-      <c r="I427" t="inlineStr"/>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr"/>
@@ -25294,7 +26018,11 @@
       <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr"/>
-      <c r="I428" t="inlineStr"/>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr"/>
@@ -25349,7 +26077,11 @@
       <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr"/>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
@@ -25581,7 +26313,11 @@
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr"/>
-      <c r="I433" t="inlineStr"/>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr"/>
@@ -25768,7 +26504,7 @@
         <v>0</v>
       </c>
       <c r="W435" t="n">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="X435" s="1" t="n">
         <v>46252</v>
@@ -25853,7 +26589,11 @@
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
-      <c r="I437" t="inlineStr"/>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr"/>
@@ -26144,7 +26884,11 @@
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr"/>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
@@ -26199,7 +26943,11 @@
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr"/>
-      <c r="I443" t="inlineStr"/>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
@@ -26313,7 +27061,11 @@
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
       <c r="L445" t="inlineStr"/>
@@ -26498,7 +27250,11 @@
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr"/>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr"/>
@@ -26612,7 +27368,11 @@
       <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr"/>
@@ -26726,7 +27486,11 @@
       <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr"/>
-      <c r="I452" t="inlineStr"/>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr"/>
@@ -26840,7 +27604,11 @@
       <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr"/>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr"/>
@@ -26895,7 +27663,11 @@
       <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr"/>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr"/>
@@ -26950,7 +27722,11 @@
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr"/>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr"/>
       <c r="L456" t="inlineStr"/>
@@ -27178,7 +27954,11 @@
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr"/>
-      <c r="I460" t="inlineStr"/>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr"/>
@@ -27304,7 +28084,11 @@
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr"/>
-      <c r="I462" t="inlineStr"/>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr"/>
@@ -27359,7 +28143,11 @@
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="inlineStr"/>
       <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr"/>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr"/>
@@ -27414,7 +28202,11 @@
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr"/>
       <c r="H464" t="inlineStr"/>
-      <c r="I464" t="inlineStr"/>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr"/>
@@ -27528,7 +28320,11 @@
       <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr"/>
       <c r="H466" t="inlineStr"/>
-      <c r="I466" t="inlineStr"/>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr"/>
@@ -27819,7 +28615,11 @@
       <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr"/>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr"/>
@@ -27945,7 +28745,11 @@
       <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr"/>
-      <c r="I473" t="inlineStr"/>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr"/>
@@ -28295,7 +29099,11 @@
       <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr"/>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr"/>
@@ -28350,7 +29158,11 @@
       <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr"/>
-      <c r="I480" t="inlineStr"/>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr"/>
@@ -28405,7 +29217,11 @@
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr"/>
-      <c r="I481" t="inlineStr"/>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr"/>
@@ -28460,7 +29276,11 @@
       <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr"/>
@@ -28940,7 +29760,11 @@
       <c r="F490" t="inlineStr"/>
       <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr"/>
-      <c r="I490" t="inlineStr"/>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr"/>
@@ -29172,7 +29996,11 @@
       <c r="F494" t="inlineStr"/>
       <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr"/>
-      <c r="I494" t="inlineStr"/>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr"/>
@@ -29227,7 +30055,11 @@
       <c r="F495" t="inlineStr"/>
       <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr"/>
-      <c r="I495" t="inlineStr"/>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr"/>
@@ -29455,7 +30287,11 @@
       <c r="F499" t="inlineStr"/>
       <c r="G499" t="inlineStr"/>
       <c r="H499" t="inlineStr"/>
-      <c r="I499" t="inlineStr"/>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr"/>
@@ -29510,7 +30346,11 @@
       <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr"/>
-      <c r="I500" t="inlineStr"/>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr"/>
@@ -29565,7 +30405,11 @@
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr"/>
-      <c r="I501" t="inlineStr"/>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr"/>
@@ -29691,7 +30535,11 @@
       <c r="F503" t="inlineStr"/>
       <c r="G503" t="inlineStr"/>
       <c r="H503" t="inlineStr"/>
-      <c r="I503" t="inlineStr"/>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr"/>
@@ -29746,7 +30594,11 @@
       <c r="F504" t="inlineStr"/>
       <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr"/>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr"/>
@@ -29787,7 +30639,7 @@
         <v>0</v>
       </c>
       <c r="W504" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="X504" s="1" t="n">
         <v>46251</v>
@@ -29813,7 +30665,11 @@
       <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr"/>
       <c r="H505" t="inlineStr"/>
-      <c r="I505" t="inlineStr"/>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr"/>
@@ -29868,7 +30724,11 @@
       <c r="F506" t="inlineStr"/>
       <c r="G506" t="inlineStr"/>
       <c r="H506" t="inlineStr"/>
-      <c r="I506" t="inlineStr"/>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr"/>
@@ -29923,7 +30783,11 @@
       <c r="F507" t="inlineStr"/>
       <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr"/>
-      <c r="I507" t="inlineStr"/>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr"/>
       <c r="L507" t="inlineStr"/>
@@ -29978,7 +30842,11 @@
       <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr"/>
       <c r="H508" t="inlineStr"/>
-      <c r="I508" t="inlineStr"/>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr"/>
@@ -30092,7 +30960,11 @@
       <c r="F510" t="inlineStr"/>
       <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr"/>
-      <c r="I510" t="inlineStr"/>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr"/>
@@ -30147,7 +31019,11 @@
       <c r="F511" t="inlineStr"/>
       <c r="G511" t="inlineStr"/>
       <c r="H511" t="inlineStr"/>
-      <c r="I511" t="inlineStr"/>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr"/>
@@ -30261,7 +31137,11 @@
       <c r="F513" t="inlineStr"/>
       <c r="G513" t="inlineStr"/>
       <c r="H513" t="inlineStr"/>
-      <c r="I513" t="inlineStr"/>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr"/>
@@ -30316,7 +31196,11 @@
       <c r="F514" t="inlineStr"/>
       <c r="G514" t="inlineStr"/>
       <c r="H514" t="inlineStr"/>
-      <c r="I514" t="inlineStr"/>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr"/>
       <c r="L514" t="inlineStr"/>
@@ -30430,7 +31314,11 @@
       <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr"/>
-      <c r="I516" t="inlineStr"/>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr"/>
@@ -30544,7 +31432,11 @@
       <c r="F518" t="inlineStr"/>
       <c r="G518" t="inlineStr"/>
       <c r="H518" t="inlineStr"/>
-      <c r="I518" t="inlineStr"/>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr"/>
@@ -30658,7 +31550,11 @@
       <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr"/>
       <c r="H520" t="inlineStr"/>
-      <c r="I520" t="inlineStr"/>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr"/>
       <c r="L520" t="inlineStr"/>
@@ -30949,7 +31845,11 @@
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="inlineStr"/>
       <c r="H525" t="inlineStr"/>
-      <c r="I525" t="inlineStr"/>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr"/>
       <c r="L525" t="inlineStr"/>
@@ -31063,7 +31963,11 @@
       <c r="F527" t="inlineStr"/>
       <c r="G527" t="inlineStr"/>
       <c r="H527" t="inlineStr"/>
-      <c r="I527" t="inlineStr"/>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr"/>
       <c r="L527" t="inlineStr"/>
@@ -31118,7 +32022,11 @@
       <c r="F528" t="inlineStr"/>
       <c r="G528" t="inlineStr"/>
       <c r="H528" t="inlineStr"/>
-      <c r="I528" t="inlineStr"/>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr"/>
@@ -31291,7 +32199,11 @@
       <c r="F531" t="inlineStr"/>
       <c r="G531" t="inlineStr"/>
       <c r="H531" t="inlineStr"/>
-      <c r="I531" t="inlineStr"/>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr"/>
       <c r="L531" t="inlineStr"/>
@@ -31346,7 +32258,11 @@
       <c r="F532" t="inlineStr"/>
       <c r="G532" t="inlineStr"/>
       <c r="H532" t="inlineStr"/>
-      <c r="I532" t="inlineStr"/>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr"/>
       <c r="L532" t="inlineStr"/>
@@ -31460,7 +32376,11 @@
       <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr"/>
       <c r="H534" t="inlineStr"/>
-      <c r="I534" t="inlineStr"/>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr"/>
       <c r="L534" t="inlineStr"/>
@@ -31574,7 +32494,11 @@
       <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr"/>
       <c r="H536" t="inlineStr"/>
-      <c r="I536" t="inlineStr"/>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr"/>
       <c r="L536" t="inlineStr"/>
@@ -31747,7 +32671,11 @@
       <c r="F539" t="inlineStr"/>
       <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr"/>
-      <c r="I539" t="inlineStr"/>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr"/>
       <c r="L539" t="inlineStr"/>
@@ -31920,7 +32848,11 @@
       <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr"/>
       <c r="H542" t="inlineStr"/>
-      <c r="I542" t="inlineStr"/>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr"/>
       <c r="L542" t="inlineStr"/>
@@ -31975,7 +32907,11 @@
       <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr"/>
       <c r="H543" t="inlineStr"/>
-      <c r="I543" t="inlineStr"/>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr"/>
       <c r="L543" t="inlineStr"/>
@@ -32030,7 +32966,11 @@
       <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr"/>
       <c r="H544" t="inlineStr"/>
-      <c r="I544" t="inlineStr"/>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr"/>
       <c r="L544" t="inlineStr"/>
@@ -32321,7 +33261,11 @@
       <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr"/>
       <c r="H549" t="inlineStr"/>
-      <c r="I549" t="inlineStr"/>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr"/>
       <c r="L549" t="inlineStr"/>
@@ -32435,7 +33379,11 @@
       <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr"/>
       <c r="H551" t="inlineStr"/>
-      <c r="I551" t="inlineStr"/>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr"/>
       <c r="L551" t="inlineStr"/>
@@ -32785,7 +33733,11 @@
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="inlineStr"/>
       <c r="H557" t="inlineStr"/>
-      <c r="I557" t="inlineStr"/>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr"/>
       <c r="L557" t="inlineStr"/>
@@ -33135,7 +34087,11 @@
       <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr"/>
       <c r="H563" t="inlineStr"/>
-      <c r="I563" t="inlineStr"/>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr"/>
       <c r="L563" t="inlineStr"/>
@@ -33308,7 +34264,11 @@
       <c r="F566" t="inlineStr"/>
       <c r="G566" t="inlineStr"/>
       <c r="H566" t="inlineStr"/>
-      <c r="I566" t="inlineStr"/>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr"/>
       <c r="L566" t="inlineStr"/>
@@ -33363,7 +34323,11 @@
       <c r="F567" t="inlineStr"/>
       <c r="G567" t="inlineStr"/>
       <c r="H567" t="inlineStr"/>
-      <c r="I567" t="inlineStr"/>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr"/>
       <c r="L567" t="inlineStr"/>
@@ -33536,7 +34500,11 @@
       <c r="F570" t="inlineStr"/>
       <c r="G570" t="inlineStr"/>
       <c r="H570" t="inlineStr"/>
-      <c r="I570" t="inlineStr"/>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr"/>
       <c r="L570" t="inlineStr"/>
@@ -33591,7 +34559,11 @@
       <c r="F571" t="inlineStr"/>
       <c r="G571" t="inlineStr"/>
       <c r="H571" t="inlineStr"/>
-      <c r="I571" t="inlineStr"/>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr"/>
       <c r="L571" t="inlineStr"/>
@@ -33764,7 +34736,11 @@
       <c r="F574" t="inlineStr"/>
       <c r="G574" t="inlineStr"/>
       <c r="H574" t="inlineStr"/>
-      <c r="I574" t="inlineStr"/>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr"/>
       <c r="L574" t="inlineStr"/>
@@ -33819,7 +34795,11 @@
       <c r="F575" t="inlineStr"/>
       <c r="G575" t="inlineStr"/>
       <c r="H575" t="inlineStr"/>
-      <c r="I575" t="inlineStr"/>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr"/>
       <c r="L575" t="inlineStr"/>
@@ -33874,7 +34854,11 @@
       <c r="F576" t="inlineStr"/>
       <c r="G576" t="inlineStr"/>
       <c r="H576" t="inlineStr"/>
-      <c r="I576" t="inlineStr"/>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr"/>
       <c r="L576" t="inlineStr"/>
@@ -34047,7 +35031,11 @@
       <c r="F579" t="inlineStr"/>
       <c r="G579" t="inlineStr"/>
       <c r="H579" t="inlineStr"/>
-      <c r="I579" t="inlineStr"/>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr"/>
       <c r="L579" t="inlineStr"/>
@@ -34102,7 +35090,11 @@
       <c r="F580" t="inlineStr"/>
       <c r="G580" t="inlineStr"/>
       <c r="H580" t="inlineStr"/>
-      <c r="I580" t="inlineStr"/>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr"/>
       <c r="L580" t="inlineStr"/>
@@ -34157,7 +35149,11 @@
       <c r="F581" t="inlineStr"/>
       <c r="G581" t="inlineStr"/>
       <c r="H581" t="inlineStr"/>
-      <c r="I581" t="inlineStr"/>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr"/>
       <c r="L581" t="inlineStr"/>
@@ -34389,7 +35385,11 @@
       <c r="F585" t="inlineStr"/>
       <c r="G585" t="inlineStr"/>
       <c r="H585" t="inlineStr"/>
-      <c r="I585" t="inlineStr"/>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr"/>
       <c r="L585" t="inlineStr"/>
@@ -34503,7 +35503,11 @@
       <c r="F587" t="inlineStr"/>
       <c r="G587" t="inlineStr"/>
       <c r="H587" t="inlineStr"/>
-      <c r="I587" t="inlineStr"/>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr"/>
       <c r="L587" t="inlineStr"/>
@@ -34558,7 +35562,11 @@
       <c r="F588" t="inlineStr"/>
       <c r="G588" t="inlineStr"/>
       <c r="H588" t="inlineStr"/>
-      <c r="I588" t="inlineStr"/>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr"/>
       <c r="L588" t="inlineStr"/>
@@ -34613,7 +35621,11 @@
       <c r="F589" t="inlineStr"/>
       <c r="G589" t="inlineStr"/>
       <c r="H589" t="inlineStr"/>
-      <c r="I589" t="inlineStr"/>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr"/>
       <c r="L589" t="inlineStr"/>
@@ -34668,7 +35680,11 @@
       <c r="F590" t="inlineStr"/>
       <c r="G590" t="inlineStr"/>
       <c r="H590" t="inlineStr"/>
-      <c r="I590" t="inlineStr"/>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr"/>
       <c r="L590" t="inlineStr"/>
@@ -34723,7 +35739,11 @@
       <c r="F591" t="inlineStr"/>
       <c r="G591" t="inlineStr"/>
       <c r="H591" t="inlineStr"/>
-      <c r="I591" t="inlineStr"/>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr"/>
       <c r="L591" t="inlineStr"/>
@@ -34837,7 +35857,11 @@
       <c r="F593" t="inlineStr"/>
       <c r="G593" t="inlineStr"/>
       <c r="H593" t="inlineStr"/>
-      <c r="I593" t="inlineStr"/>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr"/>
       <c r="L593" t="inlineStr"/>
@@ -34951,7 +35975,11 @@
       <c r="F595" t="inlineStr"/>
       <c r="G595" t="inlineStr"/>
       <c r="H595" t="inlineStr"/>
-      <c r="I595" t="inlineStr"/>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr"/>
       <c r="L595" t="inlineStr"/>
@@ -35006,7 +36034,11 @@
       <c r="F596" t="inlineStr"/>
       <c r="G596" t="inlineStr"/>
       <c r="H596" t="inlineStr"/>
-      <c r="I596" t="inlineStr"/>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr"/>
       <c r="L596" t="inlineStr"/>
@@ -35120,7 +36152,11 @@
       <c r="F598" t="inlineStr"/>
       <c r="G598" t="inlineStr"/>
       <c r="H598" t="inlineStr"/>
-      <c r="I598" t="inlineStr"/>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr"/>
@@ -35234,7 +36270,11 @@
       <c r="F600" t="inlineStr"/>
       <c r="G600" t="inlineStr"/>
       <c r="H600" t="inlineStr"/>
-      <c r="I600" t="inlineStr"/>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr"/>
       <c r="L600" t="inlineStr"/>
@@ -35360,7 +36400,11 @@
       <c r="F602" t="inlineStr"/>
       <c r="G602" t="inlineStr"/>
       <c r="H602" t="inlineStr"/>
-      <c r="I602" t="inlineStr"/>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr"/>
@@ -35415,7 +36459,11 @@
       <c r="F603" t="inlineStr"/>
       <c r="G603" t="inlineStr"/>
       <c r="H603" t="inlineStr"/>
-      <c r="I603" t="inlineStr"/>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr"/>
       <c r="L603" t="inlineStr"/>
@@ -35529,7 +36577,11 @@
       <c r="F605" t="inlineStr"/>
       <c r="G605" t="inlineStr"/>
       <c r="H605" t="inlineStr"/>
-      <c r="I605" t="inlineStr"/>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr"/>
@@ -35643,7 +36695,11 @@
       <c r="F607" t="inlineStr"/>
       <c r="G607" t="inlineStr"/>
       <c r="H607" t="inlineStr"/>
-      <c r="I607" t="inlineStr"/>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr"/>
@@ -35698,7 +36754,11 @@
       <c r="F608" t="inlineStr"/>
       <c r="G608" t="inlineStr"/>
       <c r="H608" t="inlineStr"/>
-      <c r="I608" t="inlineStr"/>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr"/>
       <c r="L608" t="inlineStr"/>
@@ -35753,7 +36813,11 @@
       <c r="F609" t="inlineStr"/>
       <c r="G609" t="inlineStr"/>
       <c r="H609" t="inlineStr"/>
-      <c r="I609" t="inlineStr"/>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr"/>
       <c r="L609" t="inlineStr"/>
@@ -35879,7 +36943,11 @@
       <c r="F611" t="inlineStr"/>
       <c r="G611" t="inlineStr"/>
       <c r="H611" t="inlineStr"/>
-      <c r="I611" t="inlineStr"/>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr"/>
       <c r="L611" t="inlineStr"/>
@@ -35934,7 +37002,11 @@
       <c r="F612" t="inlineStr"/>
       <c r="G612" t="inlineStr"/>
       <c r="H612" t="inlineStr"/>
-      <c r="I612" t="inlineStr"/>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr"/>
       <c r="L612" t="inlineStr"/>
@@ -36107,7 +37179,11 @@
       <c r="F615" t="inlineStr"/>
       <c r="G615" t="inlineStr"/>
       <c r="H615" t="inlineStr"/>
-      <c r="I615" t="inlineStr"/>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr"/>
       <c r="L615" t="inlineStr"/>
@@ -36162,7 +37238,11 @@
       <c r="F616" t="inlineStr"/>
       <c r="G616" t="inlineStr"/>
       <c r="H616" t="inlineStr"/>
-      <c r="I616" t="inlineStr"/>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr"/>
       <c r="L616" t="inlineStr"/>
@@ -36276,7 +37356,11 @@
       <c r="F618" t="inlineStr"/>
       <c r="G618" t="inlineStr"/>
       <c r="H618" t="inlineStr"/>
-      <c r="I618" t="inlineStr"/>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr"/>
       <c r="L618" t="inlineStr"/>
@@ -36390,7 +37474,11 @@
       <c r="F620" t="inlineStr"/>
       <c r="G620" t="inlineStr"/>
       <c r="H620" t="inlineStr"/>
-      <c r="I620" t="inlineStr"/>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr"/>
       <c r="L620" t="inlineStr"/>
@@ -36563,7 +37651,11 @@
       <c r="F623" t="inlineStr"/>
       <c r="G623" t="inlineStr"/>
       <c r="H623" t="inlineStr"/>
-      <c r="I623" t="inlineStr"/>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr"/>
       <c r="L623" t="inlineStr"/>
@@ -36677,7 +37769,11 @@
       <c r="F625" t="inlineStr"/>
       <c r="G625" t="inlineStr"/>
       <c r="H625" t="inlineStr"/>
-      <c r="I625" t="inlineStr"/>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr"/>
@@ -36791,7 +37887,11 @@
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="inlineStr"/>
       <c r="H627" t="inlineStr"/>
-      <c r="I627" t="inlineStr"/>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr"/>
       <c r="L627" t="inlineStr"/>
@@ -36846,7 +37946,11 @@
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="inlineStr"/>
       <c r="H628" t="inlineStr"/>
-      <c r="I628" t="inlineStr"/>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr"/>
       <c r="L628" t="inlineStr"/>
@@ -37015,7 +38119,11 @@
       <c r="F631" t="inlineStr"/>
       <c r="G631" t="inlineStr"/>
       <c r="H631" t="inlineStr"/>
-      <c r="I631" t="inlineStr"/>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr"/>
       <c r="L631" t="inlineStr"/>
@@ -37129,7 +38237,11 @@
       <c r="F633" t="inlineStr"/>
       <c r="G633" t="inlineStr"/>
       <c r="H633" t="inlineStr"/>
-      <c r="I633" t="inlineStr"/>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J633" t="inlineStr"/>
       <c r="K633" t="inlineStr"/>
       <c r="L633" t="inlineStr"/>
@@ -37255,7 +38367,11 @@
       <c r="F635" t="inlineStr"/>
       <c r="G635" t="inlineStr"/>
       <c r="H635" t="inlineStr"/>
-      <c r="I635" t="inlineStr"/>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J635" t="inlineStr"/>
       <c r="K635" t="inlineStr"/>
       <c r="L635" t="inlineStr"/>
@@ -37310,7 +38426,11 @@
       <c r="F636" t="inlineStr"/>
       <c r="G636" t="inlineStr"/>
       <c r="H636" t="inlineStr"/>
-      <c r="I636" t="inlineStr"/>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J636" t="inlineStr"/>
       <c r="K636" t="inlineStr"/>
       <c r="L636" t="inlineStr"/>
@@ -37554,7 +38674,11 @@
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="inlineStr"/>
       <c r="H640" t="inlineStr"/>
-      <c r="I640" t="inlineStr"/>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J640" t="inlineStr"/>
       <c r="K640" t="inlineStr"/>
       <c r="L640" t="inlineStr"/>
@@ -37609,7 +38733,11 @@
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="inlineStr"/>
       <c r="H641" t="inlineStr"/>
-      <c r="I641" t="inlineStr"/>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J641" t="inlineStr"/>
       <c r="K641" t="inlineStr"/>
       <c r="L641" t="inlineStr"/>
@@ -37664,7 +38792,11 @@
       <c r="F642" t="inlineStr"/>
       <c r="G642" t="inlineStr"/>
       <c r="H642" t="inlineStr"/>
-      <c r="I642" t="inlineStr"/>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr"/>
       <c r="L642" t="inlineStr"/>
@@ -37719,7 +38851,11 @@
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="inlineStr"/>
       <c r="H643" t="inlineStr"/>
-      <c r="I643" t="inlineStr"/>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr"/>
       <c r="L643" t="inlineStr"/>
@@ -37774,7 +38910,11 @@
       <c r="F644" t="inlineStr"/>
       <c r="G644" t="inlineStr"/>
       <c r="H644" t="inlineStr"/>
-      <c r="I644" t="inlineStr"/>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J644" t="inlineStr"/>
       <c r="K644" t="inlineStr"/>
       <c r="L644" t="inlineStr"/>
@@ -37829,7 +38969,11 @@
       <c r="F645" t="inlineStr"/>
       <c r="G645" t="inlineStr"/>
       <c r="H645" t="inlineStr"/>
-      <c r="I645" t="inlineStr"/>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J645" t="inlineStr"/>
       <c r="K645" t="inlineStr"/>
       <c r="L645" t="inlineStr"/>
@@ -37943,7 +39087,11 @@
       <c r="F647" t="inlineStr"/>
       <c r="G647" t="inlineStr"/>
       <c r="H647" t="inlineStr"/>
-      <c r="I647" t="inlineStr"/>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J647" t="inlineStr"/>
       <c r="K647" t="inlineStr"/>
       <c r="L647" t="inlineStr"/>
@@ -38057,7 +39205,11 @@
       <c r="F649" t="inlineStr"/>
       <c r="G649" t="inlineStr"/>
       <c r="H649" t="inlineStr"/>
-      <c r="I649" t="inlineStr"/>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J649" t="inlineStr"/>
       <c r="K649" t="inlineStr"/>
       <c r="L649" t="inlineStr"/>
@@ -38348,7 +39500,11 @@
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="inlineStr"/>
       <c r="H654" t="inlineStr"/>
-      <c r="I654" t="inlineStr"/>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J654" t="inlineStr"/>
       <c r="K654" t="inlineStr"/>
       <c r="L654" t="inlineStr"/>
@@ -38462,7 +39618,11 @@
       <c r="F656" t="inlineStr"/>
       <c r="G656" t="inlineStr"/>
       <c r="H656" t="inlineStr"/>
-      <c r="I656" t="inlineStr"/>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J656" t="inlineStr"/>
       <c r="K656" t="inlineStr"/>
       <c r="L656" t="inlineStr"/>
@@ -38576,7 +39736,11 @@
       <c r="F658" t="inlineStr"/>
       <c r="G658" t="inlineStr"/>
       <c r="H658" t="inlineStr"/>
-      <c r="I658" t="inlineStr"/>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J658" t="inlineStr"/>
       <c r="K658" t="inlineStr"/>
       <c r="L658" t="inlineStr"/>
@@ -38631,7 +39795,11 @@
       <c r="F659" t="inlineStr"/>
       <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr"/>
-      <c r="I659" t="inlineStr"/>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J659" t="inlineStr"/>
       <c r="K659" t="inlineStr"/>
       <c r="L659" t="inlineStr"/>
@@ -38922,7 +40090,11 @@
       <c r="F664" t="inlineStr"/>
       <c r="G664" t="inlineStr"/>
       <c r="H664" t="inlineStr"/>
-      <c r="I664" t="inlineStr"/>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J664" t="inlineStr"/>
       <c r="K664" t="inlineStr"/>
       <c r="L664" t="inlineStr"/>
@@ -39095,7 +40267,11 @@
       <c r="F667" t="inlineStr"/>
       <c r="G667" t="inlineStr"/>
       <c r="H667" t="inlineStr"/>
-      <c r="I667" t="inlineStr"/>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J667" t="inlineStr"/>
       <c r="K667" t="inlineStr"/>
       <c r="L667" t="inlineStr"/>
@@ -39209,7 +40385,11 @@
       <c r="F669" t="inlineStr"/>
       <c r="G669" t="inlineStr"/>
       <c r="H669" t="inlineStr"/>
-      <c r="I669" t="inlineStr"/>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J669" t="inlineStr"/>
       <c r="K669" t="inlineStr"/>
       <c r="L669" t="inlineStr"/>
@@ -39323,7 +40503,11 @@
       <c r="F671" t="inlineStr"/>
       <c r="G671" t="inlineStr"/>
       <c r="H671" t="inlineStr"/>
-      <c r="I671" t="inlineStr"/>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J671" t="inlineStr"/>
       <c r="K671" t="inlineStr"/>
       <c r="L671" t="inlineStr"/>
@@ -39378,7 +40562,11 @@
       <c r="F672" t="inlineStr"/>
       <c r="G672" t="inlineStr"/>
       <c r="H672" t="inlineStr"/>
-      <c r="I672" t="inlineStr"/>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J672" t="inlineStr"/>
       <c r="K672" t="inlineStr"/>
       <c r="L672" t="inlineStr"/>
@@ -39433,7 +40621,11 @@
       <c r="F673" t="inlineStr"/>
       <c r="G673" t="inlineStr"/>
       <c r="H673" t="inlineStr"/>
-      <c r="I673" t="inlineStr"/>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J673" t="inlineStr"/>
       <c r="K673" t="inlineStr"/>
       <c r="L673" t="inlineStr"/>
@@ -39606,7 +40798,11 @@
       <c r="F676" t="inlineStr"/>
       <c r="G676" t="inlineStr"/>
       <c r="H676" t="inlineStr"/>
-      <c r="I676" t="inlineStr"/>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J676" t="inlineStr"/>
       <c r="K676" t="inlineStr"/>
       <c r="L676" t="inlineStr"/>
@@ -39661,7 +40857,11 @@
       <c r="F677" t="inlineStr"/>
       <c r="G677" t="inlineStr"/>
       <c r="H677" t="inlineStr"/>
-      <c r="I677" t="inlineStr"/>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J677" t="inlineStr"/>
       <c r="K677" t="inlineStr"/>
       <c r="L677" t="inlineStr"/>
@@ -39716,7 +40916,11 @@
       <c r="F678" t="inlineStr"/>
       <c r="G678" t="inlineStr"/>
       <c r="H678" t="inlineStr"/>
-      <c r="I678" t="inlineStr"/>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J678" t="inlineStr"/>
       <c r="K678" t="inlineStr"/>
       <c r="L678" t="inlineStr"/>
@@ -39968,7 +41172,11 @@
       <c r="F682" t="inlineStr"/>
       <c r="G682" t="inlineStr"/>
       <c r="H682" t="inlineStr"/>
-      <c r="I682" t="inlineStr"/>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J682" t="inlineStr"/>
       <c r="K682" t="inlineStr"/>
       <c r="L682" t="inlineStr"/>
@@ -40023,7 +41231,11 @@
       <c r="F683" t="inlineStr"/>
       <c r="G683" t="inlineStr"/>
       <c r="H683" t="inlineStr"/>
-      <c r="I683" t="inlineStr"/>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J683" t="inlineStr"/>
       <c r="K683" t="inlineStr"/>
       <c r="L683" t="inlineStr"/>
@@ -40137,7 +41349,11 @@
       <c r="F685" t="inlineStr"/>
       <c r="G685" t="inlineStr"/>
       <c r="H685" t="inlineStr"/>
-      <c r="I685" t="inlineStr"/>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J685" t="inlineStr"/>
       <c r="K685" t="inlineStr"/>
       <c r="L685" t="inlineStr"/>
@@ -40192,7 +41408,11 @@
       <c r="F686" t="inlineStr"/>
       <c r="G686" t="inlineStr"/>
       <c r="H686" t="inlineStr"/>
-      <c r="I686" t="inlineStr"/>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J686" t="inlineStr"/>
       <c r="K686" t="inlineStr"/>
       <c r="L686" t="inlineStr"/>
@@ -40365,7 +41585,11 @@
       <c r="F689" t="inlineStr"/>
       <c r="G689" t="inlineStr"/>
       <c r="H689" t="inlineStr"/>
-      <c r="I689" t="inlineStr"/>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J689" t="inlineStr"/>
       <c r="K689" t="inlineStr"/>
       <c r="L689" t="inlineStr"/>
@@ -40479,7 +41703,11 @@
       <c r="F691" t="inlineStr"/>
       <c r="G691" t="inlineStr"/>
       <c r="H691" t="inlineStr"/>
-      <c r="I691" t="inlineStr"/>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J691" t="inlineStr"/>
       <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr"/>
@@ -40534,7 +41762,11 @@
       <c r="F692" t="inlineStr"/>
       <c r="G692" t="inlineStr"/>
       <c r="H692" t="inlineStr"/>
-      <c r="I692" t="inlineStr"/>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J692" t="inlineStr"/>
       <c r="K692" t="inlineStr"/>
       <c r="L692" t="inlineStr"/>
@@ -40829,13 +42061,13 @@
         <v>4</v>
       </c>
       <c r="U696" t="n">
-        <v>353.8</v>
+        <v>383.78</v>
       </c>
       <c r="V696" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W696" t="n">
-        <v>11859</v>
+        <v>12146</v>
       </c>
       <c r="X696" s="1" t="n">
         <v>46244</v>
@@ -40991,7 +42223,11 @@
       <c r="F699" t="inlineStr"/>
       <c r="G699" t="inlineStr"/>
       <c r="H699" t="inlineStr"/>
-      <c r="I699" t="inlineStr"/>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J699" t="inlineStr"/>
       <c r="K699" t="inlineStr"/>
       <c r="L699" t="inlineStr"/>
@@ -41117,7 +42353,11 @@
       <c r="F701" t="inlineStr"/>
       <c r="G701" t="inlineStr"/>
       <c r="H701" t="inlineStr"/>
-      <c r="I701" t="inlineStr"/>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J701" t="inlineStr"/>
       <c r="K701" t="inlineStr"/>
       <c r="L701" t="inlineStr"/>
@@ -41172,7 +42412,11 @@
       <c r="F702" t="inlineStr"/>
       <c r="G702" t="inlineStr"/>
       <c r="H702" t="inlineStr"/>
-      <c r="I702" t="inlineStr"/>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J702" t="inlineStr"/>
       <c r="K702" t="inlineStr"/>
       <c r="L702" t="inlineStr"/>
@@ -41239,7 +42483,11 @@
       <c r="F703" t="inlineStr"/>
       <c r="G703" t="inlineStr"/>
       <c r="H703" t="inlineStr"/>
-      <c r="I703" t="inlineStr"/>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J703" t="inlineStr"/>
       <c r="K703" t="inlineStr"/>
       <c r="L703" t="inlineStr"/>
@@ -41353,7 +42601,11 @@
       <c r="F705" t="inlineStr"/>
       <c r="G705" t="inlineStr"/>
       <c r="H705" t="inlineStr"/>
-      <c r="I705" t="inlineStr"/>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J705" t="inlineStr"/>
       <c r="K705" t="inlineStr"/>
       <c r="L705" t="inlineStr"/>
@@ -41408,7 +42660,11 @@
       <c r="F706" t="inlineStr"/>
       <c r="G706" t="inlineStr"/>
       <c r="H706" t="inlineStr"/>
-      <c r="I706" t="inlineStr"/>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J706" t="inlineStr"/>
       <c r="K706" t="inlineStr"/>
       <c r="L706" t="inlineStr"/>
@@ -41463,7 +42719,11 @@
       <c r="F707" t="inlineStr"/>
       <c r="G707" t="inlineStr"/>
       <c r="H707" t="inlineStr"/>
-      <c r="I707" t="inlineStr"/>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J707" t="inlineStr"/>
       <c r="K707" t="inlineStr"/>
       <c r="L707" t="inlineStr"/>
@@ -41518,7 +42778,11 @@
       <c r="F708" t="inlineStr"/>
       <c r="G708" t="inlineStr"/>
       <c r="H708" t="inlineStr"/>
-      <c r="I708" t="inlineStr"/>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J708" t="inlineStr"/>
       <c r="K708" t="inlineStr"/>
       <c r="L708" t="inlineStr"/>
@@ -41573,7 +42837,11 @@
       <c r="F709" t="inlineStr"/>
       <c r="G709" t="inlineStr"/>
       <c r="H709" t="inlineStr"/>
-      <c r="I709" t="inlineStr"/>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J709" t="inlineStr"/>
       <c r="K709" t="inlineStr"/>
       <c r="L709" t="inlineStr"/>
@@ -41687,7 +42955,11 @@
       <c r="F711" t="inlineStr"/>
       <c r="G711" t="inlineStr"/>
       <c r="H711" t="inlineStr"/>
-      <c r="I711" t="inlineStr"/>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J711" t="inlineStr"/>
       <c r="K711" t="inlineStr"/>
       <c r="L711" t="inlineStr"/>
@@ -41860,7 +43132,11 @@
       <c r="F714" t="inlineStr"/>
       <c r="G714" t="inlineStr"/>
       <c r="H714" t="inlineStr"/>
-      <c r="I714" t="inlineStr"/>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J714" t="inlineStr"/>
       <c r="K714" t="inlineStr"/>
       <c r="L714" t="inlineStr"/>
@@ -41915,7 +43191,11 @@
       <c r="F715" t="inlineStr"/>
       <c r="G715" t="inlineStr"/>
       <c r="H715" t="inlineStr"/>
-      <c r="I715" t="inlineStr"/>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J715" t="inlineStr"/>
       <c r="K715" t="inlineStr"/>
       <c r="L715" t="inlineStr"/>
@@ -41970,7 +43250,11 @@
       <c r="F716" t="inlineStr"/>
       <c r="G716" t="inlineStr"/>
       <c r="H716" t="inlineStr"/>
-      <c r="I716" t="inlineStr"/>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J716" t="inlineStr"/>
       <c r="K716" t="inlineStr"/>
       <c r="L716" t="inlineStr"/>
@@ -42025,7 +43309,11 @@
       <c r="F717" t="inlineStr"/>
       <c r="G717" t="inlineStr"/>
       <c r="H717" t="inlineStr"/>
-      <c r="I717" t="inlineStr"/>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J717" t="inlineStr"/>
       <c r="K717" t="inlineStr"/>
       <c r="L717" t="inlineStr"/>
@@ -42257,7 +43545,11 @@
       <c r="F721" t="inlineStr"/>
       <c r="G721" t="inlineStr"/>
       <c r="H721" t="inlineStr"/>
-      <c r="I721" t="inlineStr"/>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J721" t="inlineStr"/>
       <c r="K721" t="inlineStr"/>
       <c r="L721" t="inlineStr"/>
@@ -42371,7 +43663,11 @@
       <c r="F723" t="inlineStr"/>
       <c r="G723" t="inlineStr"/>
       <c r="H723" t="inlineStr"/>
-      <c r="I723" t="inlineStr"/>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J723" t="inlineStr"/>
       <c r="K723" t="inlineStr"/>
       <c r="L723" t="inlineStr"/>
@@ -42603,7 +43899,11 @@
       <c r="F727" t="inlineStr"/>
       <c r="G727" t="inlineStr"/>
       <c r="H727" t="inlineStr"/>
-      <c r="I727" t="inlineStr"/>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J727" t="inlineStr"/>
       <c r="K727" t="inlineStr"/>
       <c r="L727" t="inlineStr"/>
@@ -42835,7 +44135,11 @@
       <c r="F731" t="inlineStr"/>
       <c r="G731" t="inlineStr"/>
       <c r="H731" t="inlineStr"/>
-      <c r="I731" t="inlineStr"/>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J731" t="inlineStr"/>
       <c r="K731" t="inlineStr"/>
       <c r="L731" t="inlineStr"/>
@@ -42890,7 +44194,11 @@
       <c r="F732" t="inlineStr"/>
       <c r="G732" t="inlineStr"/>
       <c r="H732" t="inlineStr"/>
-      <c r="I732" t="inlineStr"/>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J732" t="inlineStr"/>
       <c r="K732" t="inlineStr"/>
       <c r="L732" t="inlineStr"/>
@@ -43004,7 +44312,11 @@
       <c r="F734" t="inlineStr"/>
       <c r="G734" t="inlineStr"/>
       <c r="H734" t="inlineStr"/>
-      <c r="I734" t="inlineStr"/>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J734" t="inlineStr"/>
       <c r="K734" t="inlineStr"/>
       <c r="L734" t="inlineStr"/>
@@ -43059,7 +44371,11 @@
       <c r="F735" t="inlineStr"/>
       <c r="G735" t="inlineStr"/>
       <c r="H735" t="inlineStr"/>
-      <c r="I735" t="inlineStr"/>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J735" t="inlineStr"/>
       <c r="K735" t="inlineStr"/>
       <c r="L735" t="inlineStr"/>
@@ -43185,7 +44501,11 @@
       <c r="F737" t="inlineStr"/>
       <c r="G737" t="inlineStr"/>
       <c r="H737" t="inlineStr"/>
-      <c r="I737" t="inlineStr"/>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J737" t="inlineStr"/>
       <c r="K737" t="inlineStr"/>
       <c r="L737" t="inlineStr"/>
@@ -43240,7 +44560,11 @@
       <c r="F738" t="inlineStr"/>
       <c r="G738" t="inlineStr"/>
       <c r="H738" t="inlineStr"/>
-      <c r="I738" t="inlineStr"/>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J738" t="inlineStr"/>
       <c r="K738" t="inlineStr"/>
       <c r="L738" t="inlineStr"/>
@@ -43295,7 +44619,11 @@
       <c r="F739" t="inlineStr"/>
       <c r="G739" t="inlineStr"/>
       <c r="H739" t="inlineStr"/>
-      <c r="I739" t="inlineStr"/>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J739" t="inlineStr"/>
       <c r="K739" t="inlineStr"/>
       <c r="L739" t="inlineStr"/>
@@ -43350,7 +44678,11 @@
       <c r="F740" t="inlineStr"/>
       <c r="G740" t="inlineStr"/>
       <c r="H740" t="inlineStr"/>
-      <c r="I740" t="inlineStr"/>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J740" t="inlineStr"/>
       <c r="K740" t="inlineStr"/>
       <c r="L740" t="inlineStr"/>
@@ -43405,7 +44737,11 @@
       <c r="F741" t="inlineStr"/>
       <c r="G741" t="inlineStr"/>
       <c r="H741" t="inlineStr"/>
-      <c r="I741" t="inlineStr"/>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J741" t="inlineStr"/>
       <c r="K741" t="inlineStr"/>
       <c r="L741" t="inlineStr"/>
@@ -43696,7 +45032,11 @@
       <c r="F746" t="inlineStr"/>
       <c r="G746" t="inlineStr"/>
       <c r="H746" t="inlineStr"/>
-      <c r="I746" t="inlineStr"/>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J746" t="inlineStr"/>
       <c r="K746" t="inlineStr"/>
       <c r="L746" t="inlineStr"/>
@@ -43751,7 +45091,11 @@
       <c r="F747" t="inlineStr"/>
       <c r="G747" t="inlineStr"/>
       <c r="H747" t="inlineStr"/>
-      <c r="I747" t="inlineStr"/>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J747" t="inlineStr"/>
       <c r="K747" t="inlineStr"/>
       <c r="L747" t="inlineStr"/>
@@ -43806,7 +45150,11 @@
       <c r="F748" t="inlineStr"/>
       <c r="G748" t="inlineStr"/>
       <c r="H748" t="inlineStr"/>
-      <c r="I748" t="inlineStr"/>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J748" t="inlineStr"/>
       <c r="K748" t="inlineStr"/>
       <c r="L748" t="inlineStr"/>
@@ -43920,7 +45268,11 @@
       <c r="F750" t="inlineStr"/>
       <c r="G750" t="inlineStr"/>
       <c r="H750" t="inlineStr"/>
-      <c r="I750" t="inlineStr"/>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J750" t="inlineStr"/>
       <c r="K750" t="inlineStr"/>
       <c r="L750" t="inlineStr"/>
@@ -44093,7 +45445,11 @@
       <c r="F753" t="inlineStr"/>
       <c r="G753" t="inlineStr"/>
       <c r="H753" t="inlineStr"/>
-      <c r="I753" t="inlineStr"/>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J753" t="inlineStr"/>
       <c r="K753" t="inlineStr"/>
       <c r="L753" t="inlineStr"/>
@@ -44148,7 +45504,11 @@
       <c r="F754" t="inlineStr"/>
       <c r="G754" t="inlineStr"/>
       <c r="H754" t="inlineStr"/>
-      <c r="I754" t="inlineStr"/>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J754" t="inlineStr"/>
       <c r="K754" t="inlineStr"/>
       <c r="L754" t="inlineStr"/>
@@ -44203,7 +45563,11 @@
       <c r="F755" t="inlineStr"/>
       <c r="G755" t="inlineStr"/>
       <c r="H755" t="inlineStr"/>
-      <c r="I755" t="inlineStr"/>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J755" t="inlineStr"/>
       <c r="K755" t="inlineStr"/>
       <c r="L755" t="inlineStr"/>
@@ -44258,7 +45622,11 @@
       <c r="F756" t="inlineStr"/>
       <c r="G756" t="inlineStr"/>
       <c r="H756" t="inlineStr"/>
-      <c r="I756" t="inlineStr"/>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J756" t="inlineStr"/>
       <c r="K756" t="inlineStr"/>
       <c r="L756" t="inlineStr"/>
@@ -44313,7 +45681,11 @@
       <c r="F757" t="inlineStr"/>
       <c r="G757" t="inlineStr"/>
       <c r="H757" t="inlineStr"/>
-      <c r="I757" t="inlineStr"/>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J757" t="inlineStr"/>
       <c r="K757" t="inlineStr"/>
       <c r="L757" t="inlineStr"/>
@@ -44368,7 +45740,11 @@
       <c r="F758" t="inlineStr"/>
       <c r="G758" t="inlineStr"/>
       <c r="H758" t="inlineStr"/>
-      <c r="I758" t="inlineStr"/>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J758" t="inlineStr"/>
       <c r="K758" t="inlineStr"/>
       <c r="L758" t="inlineStr"/>
@@ -44423,7 +45799,11 @@
       <c r="F759" t="inlineStr"/>
       <c r="G759" t="inlineStr"/>
       <c r="H759" t="inlineStr"/>
-      <c r="I759" t="inlineStr"/>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J759" t="inlineStr"/>
       <c r="K759" t="inlineStr"/>
       <c r="L759" t="inlineStr"/>
@@ -44478,7 +45858,11 @@
       <c r="F760" t="inlineStr"/>
       <c r="G760" t="inlineStr"/>
       <c r="H760" t="inlineStr"/>
-      <c r="I760" t="inlineStr"/>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J760" t="inlineStr"/>
       <c r="K760" t="inlineStr"/>
       <c r="L760" t="inlineStr"/>
@@ -44533,7 +45917,11 @@
       <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr"/>
       <c r="H761" t="inlineStr"/>
-      <c r="I761" t="inlineStr"/>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J761" t="inlineStr"/>
       <c r="K761" t="inlineStr"/>
       <c r="L761" t="inlineStr"/>
@@ -44588,7 +45976,11 @@
       <c r="F762" t="inlineStr"/>
       <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr"/>
-      <c r="I762" t="inlineStr"/>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J762" t="inlineStr"/>
       <c r="K762" t="inlineStr"/>
       <c r="L762" t="inlineStr"/>
@@ -44643,7 +46035,11 @@
       <c r="F763" t="inlineStr"/>
       <c r="G763" t="inlineStr"/>
       <c r="H763" t="inlineStr"/>
-      <c r="I763" t="inlineStr"/>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J763" t="inlineStr"/>
       <c r="K763" t="inlineStr"/>
       <c r="L763" t="inlineStr"/>
@@ -44698,7 +46094,11 @@
       <c r="F764" t="inlineStr"/>
       <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr"/>
-      <c r="I764" t="inlineStr"/>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J764" t="inlineStr"/>
       <c r="K764" t="inlineStr"/>
       <c r="L764" t="inlineStr"/>
@@ -44753,7 +46153,11 @@
       <c r="F765" t="inlineStr"/>
       <c r="G765" t="inlineStr"/>
       <c r="H765" t="inlineStr"/>
-      <c r="I765" t="inlineStr"/>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J765" t="inlineStr"/>
       <c r="K765" t="inlineStr"/>
       <c r="L765" t="inlineStr"/>
@@ -44867,7 +46271,11 @@
       <c r="F767" t="inlineStr"/>
       <c r="G767" t="inlineStr"/>
       <c r="H767" t="inlineStr"/>
-      <c r="I767" t="inlineStr"/>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J767" t="inlineStr"/>
       <c r="K767" t="inlineStr"/>
       <c r="L767" t="inlineStr"/>
@@ -44922,7 +46330,11 @@
       <c r="F768" t="inlineStr"/>
       <c r="G768" t="inlineStr"/>
       <c r="H768" t="inlineStr"/>
-      <c r="I768" t="inlineStr"/>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J768" t="inlineStr"/>
       <c r="K768" t="inlineStr"/>
       <c r="L768" t="inlineStr"/>
@@ -44977,7 +46389,11 @@
       <c r="F769" t="inlineStr"/>
       <c r="G769" t="inlineStr"/>
       <c r="H769" t="inlineStr"/>
-      <c r="I769" t="inlineStr"/>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J769" t="inlineStr"/>
       <c r="K769" t="inlineStr"/>
       <c r="L769" t="inlineStr"/>
@@ -45032,7 +46448,11 @@
       <c r="F770" t="inlineStr"/>
       <c r="G770" t="inlineStr"/>
       <c r="H770" t="inlineStr"/>
-      <c r="I770" t="inlineStr"/>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J770" t="inlineStr"/>
       <c r="K770" t="inlineStr"/>
       <c r="L770" t="inlineStr"/>
@@ -45087,7 +46507,11 @@
       <c r="F771" t="inlineStr"/>
       <c r="G771" t="inlineStr"/>
       <c r="H771" t="inlineStr"/>
-      <c r="I771" t="inlineStr"/>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J771" t="inlineStr"/>
       <c r="K771" t="inlineStr"/>
       <c r="L771" t="inlineStr"/>
@@ -45142,7 +46566,11 @@
       <c r="F772" t="inlineStr"/>
       <c r="G772" t="inlineStr"/>
       <c r="H772" t="inlineStr"/>
-      <c r="I772" t="inlineStr"/>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J772" t="inlineStr"/>
       <c r="K772" t="inlineStr"/>
       <c r="L772" t="inlineStr"/>
@@ -45197,7 +46625,11 @@
       <c r="F773" t="inlineStr"/>
       <c r="G773" t="inlineStr"/>
       <c r="H773" t="inlineStr"/>
-      <c r="I773" t="inlineStr"/>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J773" t="inlineStr"/>
       <c r="K773" t="inlineStr"/>
       <c r="L773" t="inlineStr"/>
@@ -45252,7 +46684,11 @@
       <c r="F774" t="inlineStr"/>
       <c r="G774" t="inlineStr"/>
       <c r="H774" t="inlineStr"/>
-      <c r="I774" t="inlineStr"/>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J774" t="inlineStr"/>
       <c r="K774" t="inlineStr"/>
       <c r="L774" t="inlineStr"/>
@@ -45307,7 +46743,11 @@
       <c r="F775" t="inlineStr"/>
       <c r="G775" t="inlineStr"/>
       <c r="H775" t="inlineStr"/>
-      <c r="I775" t="inlineStr"/>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J775" t="inlineStr"/>
       <c r="K775" t="inlineStr"/>
       <c r="L775" t="inlineStr"/>
@@ -45362,7 +46802,11 @@
       <c r="F776" t="inlineStr"/>
       <c r="G776" t="inlineStr"/>
       <c r="H776" t="inlineStr"/>
-      <c r="I776" t="inlineStr"/>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J776" t="inlineStr"/>
       <c r="K776" t="inlineStr"/>
       <c r="L776" t="inlineStr"/>
@@ -45476,7 +46920,11 @@
       <c r="F778" t="inlineStr"/>
       <c r="G778" t="inlineStr"/>
       <c r="H778" t="inlineStr"/>
-      <c r="I778" t="inlineStr"/>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J778" t="inlineStr"/>
       <c r="K778" t="inlineStr"/>
       <c r="L778" t="inlineStr"/>
@@ -45940,7 +47388,11 @@
       <c r="F786" t="inlineStr"/>
       <c r="G786" t="inlineStr"/>
       <c r="H786" t="inlineStr"/>
-      <c r="I786" t="inlineStr"/>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J786" t="inlineStr"/>
       <c r="K786" t="inlineStr"/>
       <c r="L786" t="inlineStr"/>
@@ -46054,7 +47506,11 @@
       <c r="F788" t="inlineStr"/>
       <c r="G788" t="inlineStr"/>
       <c r="H788" t="inlineStr"/>
-      <c r="I788" t="inlineStr"/>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J788" t="inlineStr"/>
       <c r="K788" t="inlineStr"/>
       <c r="L788" t="inlineStr"/>
@@ -46227,7 +47683,11 @@
       <c r="F791" t="inlineStr"/>
       <c r="G791" t="inlineStr"/>
       <c r="H791" t="inlineStr"/>
-      <c r="I791" t="inlineStr"/>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J791" t="inlineStr"/>
       <c r="K791" t="inlineStr"/>
       <c r="L791" t="inlineStr"/>
@@ -46282,7 +47742,11 @@
       <c r="F792" t="inlineStr"/>
       <c r="G792" t="inlineStr"/>
       <c r="H792" t="inlineStr"/>
-      <c r="I792" t="inlineStr"/>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J792" t="inlineStr"/>
       <c r="K792" t="inlineStr"/>
       <c r="L792" t="inlineStr"/>
@@ -46337,7 +47801,11 @@
       <c r="F793" t="inlineStr"/>
       <c r="G793" t="inlineStr"/>
       <c r="H793" t="inlineStr"/>
-      <c r="I793" t="inlineStr"/>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J793" t="inlineStr"/>
       <c r="K793" t="inlineStr"/>
       <c r="L793" t="inlineStr"/>
@@ -46392,7 +47860,11 @@
       <c r="F794" t="inlineStr"/>
       <c r="G794" t="inlineStr"/>
       <c r="H794" t="inlineStr"/>
-      <c r="I794" t="inlineStr"/>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J794" t="inlineStr"/>
       <c r="K794" t="inlineStr"/>
       <c r="L794" t="inlineStr"/>
@@ -46506,7 +47978,11 @@
       <c r="F796" t="inlineStr"/>
       <c r="G796" t="inlineStr"/>
       <c r="H796" t="inlineStr"/>
-      <c r="I796" t="inlineStr"/>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J796" t="inlineStr"/>
       <c r="K796" t="inlineStr"/>
       <c r="L796" t="inlineStr"/>
@@ -46620,7 +48096,11 @@
       <c r="F798" t="inlineStr"/>
       <c r="G798" t="inlineStr"/>
       <c r="H798" t="inlineStr"/>
-      <c r="I798" t="inlineStr"/>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J798" t="inlineStr"/>
       <c r="K798" t="inlineStr"/>
       <c r="L798" t="inlineStr"/>
@@ -47084,7 +48564,11 @@
       <c r="F806" t="inlineStr"/>
       <c r="G806" t="inlineStr"/>
       <c r="H806" t="inlineStr"/>
-      <c r="I806" t="inlineStr"/>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J806" t="inlineStr"/>
       <c r="K806" t="inlineStr"/>
       <c r="L806" t="inlineStr"/>
@@ -47139,7 +48623,11 @@
       <c r="F807" t="inlineStr"/>
       <c r="G807" t="inlineStr"/>
       <c r="H807" t="inlineStr"/>
-      <c r="I807" t="inlineStr"/>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J807" t="inlineStr"/>
       <c r="K807" t="inlineStr"/>
       <c r="L807" t="inlineStr"/>
@@ -47194,7 +48682,11 @@
       <c r="F808" t="inlineStr"/>
       <c r="G808" t="inlineStr"/>
       <c r="H808" t="inlineStr"/>
-      <c r="I808" t="inlineStr"/>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J808" t="inlineStr"/>
       <c r="K808" t="inlineStr"/>
       <c r="L808" t="inlineStr"/>
@@ -47308,7 +48800,11 @@
       <c r="F810" t="inlineStr"/>
       <c r="G810" t="inlineStr"/>
       <c r="H810" t="inlineStr"/>
-      <c r="I810" t="inlineStr"/>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J810" t="inlineStr"/>
       <c r="K810" t="inlineStr"/>
       <c r="L810" t="inlineStr"/>
@@ -47363,7 +48859,11 @@
       <c r="F811" t="inlineStr"/>
       <c r="G811" t="inlineStr"/>
       <c r="H811" t="inlineStr"/>
-      <c r="I811" t="inlineStr"/>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J811" t="inlineStr"/>
       <c r="K811" t="inlineStr"/>
       <c r="L811" t="inlineStr"/>
@@ -47477,7 +48977,11 @@
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="inlineStr"/>
       <c r="H813" t="inlineStr"/>
-      <c r="I813" t="inlineStr"/>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J813" t="inlineStr"/>
       <c r="K813" t="inlineStr"/>
       <c r="L813" t="inlineStr"/>
@@ -47650,7 +49154,11 @@
       <c r="F816" t="inlineStr"/>
       <c r="G816" t="inlineStr"/>
       <c r="H816" t="inlineStr"/>
-      <c r="I816" t="inlineStr"/>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J816" t="inlineStr"/>
       <c r="K816" t="inlineStr"/>
       <c r="L816" t="inlineStr"/>
@@ -47894,7 +49402,11 @@
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="inlineStr"/>
       <c r="H820" t="inlineStr"/>
-      <c r="I820" t="inlineStr"/>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J820" t="inlineStr"/>
       <c r="K820" t="inlineStr"/>
       <c r="L820" t="inlineStr"/>
@@ -47949,7 +49461,11 @@
       <c r="F821" t="inlineStr"/>
       <c r="G821" t="inlineStr"/>
       <c r="H821" t="inlineStr"/>
-      <c r="I821" t="inlineStr"/>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J821" t="inlineStr"/>
       <c r="K821" t="inlineStr"/>
       <c r="L821" t="inlineStr"/>
@@ -48075,7 +49591,11 @@
       <c r="F823" t="inlineStr"/>
       <c r="G823" t="inlineStr"/>
       <c r="H823" t="inlineStr"/>
-      <c r="I823" t="inlineStr"/>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J823" t="inlineStr"/>
       <c r="K823" t="inlineStr"/>
       <c r="L823" t="inlineStr"/>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="X28" s="1" t="n">
         <v>46255</v>
@@ -6630,15 +6630,27 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T104" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="V104" t="n">
+        <v>2</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9731,13 +9743,13 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="X156" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="Y156" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157">
@@ -9861,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="X158" s="1" t="n">
         <v>46255</v>
@@ -16776,7 +16788,7 @@
         <v>0</v>
       </c>
       <c r="W275" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="X275" s="1" t="n">
         <v>46254</v>
@@ -17593,7 +17605,7 @@
         </is>
       </c>
       <c r="T289" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U289" t="n">
         <v>0</v>
@@ -17602,7 +17614,7 @@
         <v>0</v>
       </c>
       <c r="W289" t="n">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="X289" s="1" t="n">
         <v>46254</v>
@@ -17909,13 +17921,13 @@
         <v>0</v>
       </c>
       <c r="W294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X294" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="Y294" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295">
@@ -18620,16 +18632,16 @@
         </is>
       </c>
       <c r="T306" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U306" t="n">
-        <v>261.38</v>
+        <v>276.3</v>
       </c>
       <c r="V306" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W306" t="n">
-        <v>4276</v>
+        <v>4380</v>
       </c>
       <c r="X306" s="1" t="n">
         <v>46251</v>
@@ -19568,7 +19580,7 @@
         </is>
       </c>
       <c r="T322" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U322" t="n">
         <v>0</v>
@@ -19577,7 +19589,7 @@
         <v>0</v>
       </c>
       <c r="W322" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X322" s="1" t="n">
         <v>46215</v>
@@ -19883,7 +19895,7 @@
         </is>
       </c>
       <c r="T327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U327" t="n">
         <v>0</v>
@@ -19892,13 +19904,13 @@
         <v>0</v>
       </c>
       <c r="W327" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X327" s="1" t="n">
-        <v>46200</v>
+        <v>46218</v>
       </c>
       <c r="Y327" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="328">
@@ -21476,7 +21488,7 @@
         </is>
       </c>
       <c r="T354" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U354" t="n">
         <v>0</v>
@@ -21485,7 +21497,7 @@
         <v>0</v>
       </c>
       <c r="W354" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="X354" s="1" t="n">
         <v>46213</v>
@@ -27557,15 +27569,27 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T457" t="inlineStr"/>
-      <c r="U457" t="inlineStr"/>
-      <c r="V457" t="inlineStr"/>
-      <c r="W457" t="inlineStr"/>
-      <c r="X457" t="inlineStr"/>
-      <c r="Y457" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T457" t="n">
+        <v>1</v>
+      </c>
+      <c r="U457" t="n">
+        <v>0</v>
+      </c>
+      <c r="V457" t="n">
+        <v>0</v>
+      </c>
+      <c r="W457" t="n">
+        <v>1</v>
+      </c>
+      <c r="X457" s="1" t="n">
+        <v>46264</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -30678,7 +30702,7 @@
         <v>1</v>
       </c>
       <c r="W509" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="X509" s="1" t="n">
         <v>46252</v>
@@ -41758,13 +41782,13 @@
         <v>0</v>
       </c>
       <c r="W697" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="X697" s="1" t="n">
-        <v>46199</v>
+        <v>46205</v>
       </c>
       <c r="Y697" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="698">
@@ -46119,15 +46143,27 @@
       </c>
       <c r="S771" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T771" t="inlineStr"/>
-      <c r="U771" t="inlineStr"/>
-      <c r="V771" t="inlineStr"/>
-      <c r="W771" t="inlineStr"/>
-      <c r="X771" t="inlineStr"/>
-      <c r="Y771" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T771" t="n">
+        <v>2</v>
+      </c>
+      <c r="U771" t="n">
+        <v>0</v>
+      </c>
+      <c r="V771" t="n">
+        <v>0</v>
+      </c>
+      <c r="W771" t="n">
+        <v>444</v>
+      </c>
+      <c r="X771" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="Y771" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -48613,27 +48649,15 @@
       </c>
       <c r="S813" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T813" t="n">
-        <v>1</v>
-      </c>
-      <c r="U813" t="n">
-        <v>0</v>
-      </c>
-      <c r="V813" t="n">
-        <v>0</v>
-      </c>
-      <c r="W813" t="n">
-        <v>3</v>
-      </c>
-      <c r="X813" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="Y813" t="n">
-        <v>6</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T813" t="inlineStr"/>
+      <c r="U813" t="inlineStr"/>
+      <c r="V813" t="inlineStr"/>
+      <c r="W813" t="inlineStr"/>
+      <c r="X813" t="inlineStr"/>
+      <c r="Y813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -48743,7 +48767,7 @@
         </is>
       </c>
       <c r="T815" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U815" t="n">
         <v>0</v>
@@ -48752,7 +48776,7 @@
         <v>0</v>
       </c>
       <c r="W815" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="X815" s="1" t="n">
         <v>46248</v>
@@ -48941,13 +48965,13 @@
         <v>0</v>
       </c>
       <c r="W818" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X818" s="1" t="n">
-        <v>46200</v>
+        <v>46205</v>
       </c>
       <c r="Y818" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="819">
@@ -56512,7 +56536,7 @@
         <v>0</v>
       </c>
       <c r="W947" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X947" s="1" t="n">
         <v>46254</v>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y974"/>
+  <dimension ref="A1:Y975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47954,12 +47954,12 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>teemama329</t>
+          <t>tee_y.x</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teemama329</t>
+          <t>https://www.tiktok.com/@tee_y.x</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
@@ -47968,11 +47968,7 @@
       <c r="F802" t="inlineStr"/>
       <c r="G802" t="inlineStr"/>
       <c r="H802" t="inlineStr"/>
-      <c r="I802" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+      <c r="I802" t="inlineStr"/>
       <c r="J802" t="inlineStr"/>
       <c r="K802" t="inlineStr"/>
       <c r="L802" t="inlineStr"/>
@@ -47981,22 +47977,22 @@
       </c>
       <c r="N802" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O802" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P802" s="1" t="n">
-        <v>46207.83660879629</v>
+        <v>46265.0228125</v>
       </c>
       <c r="Q802" s="1" t="n">
-        <v>46207.83660879629</v>
+        <v>46265.0228125</v>
       </c>
       <c r="R802" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S802" t="inlineStr">
         <is>
@@ -48013,12 +48009,12 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>teeto2021</t>
+          <t>teemama329</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teeto2021</t>
+          <t>https://www.tiktok.com/@teemama329</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
@@ -48029,7 +48025,7 @@
       <c r="H803" t="inlineStr"/>
       <c r="I803" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J803" t="inlineStr"/>
@@ -48049,10 +48045,10 @@
         </is>
       </c>
       <c r="P803" s="1" t="n">
-        <v>46209.51795138889</v>
+        <v>46207.83660879629</v>
       </c>
       <c r="Q803" s="1" t="n">
-        <v>46209.51795138889</v>
+        <v>46207.83660879629</v>
       </c>
       <c r="R803" t="n">
         <v>4.8</v>
@@ -48072,12 +48068,12 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>teewhyj31</t>
+          <t>teeto2021</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teewhyj31</t>
+          <t>https://www.tiktok.com/@teeto2021</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -48108,10 +48104,10 @@
         </is>
       </c>
       <c r="P804" s="1" t="n">
-        <v>46234.72247685185</v>
+        <v>46209.51795138889</v>
       </c>
       <c r="Q804" s="1" t="n">
-        <v>46234.72247685185</v>
+        <v>46209.51795138889</v>
       </c>
       <c r="R804" t="n">
         <v>4.8</v>
@@ -48131,12 +48127,12 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>teexvnn</t>
+          <t>teewhyj31</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teexvnn</t>
+          <t>https://www.tiktok.com/@teewhyj31</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
@@ -48167,10 +48163,10 @@
         </is>
       </c>
       <c r="P805" s="1" t="n">
-        <v>46240.94375</v>
+        <v>46234.72247685185</v>
       </c>
       <c r="Q805" s="1" t="n">
-        <v>46240.94375</v>
+        <v>46234.72247685185</v>
       </c>
       <c r="R805" t="n">
         <v>4.8</v>
@@ -48190,12 +48186,12 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>temidiresholagbad</t>
+          <t>teexvnn</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temidiresholagbad</t>
+          <t>https://www.tiktok.com/@teexvnn</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
@@ -48226,10 +48222,10 @@
         </is>
       </c>
       <c r="P806" s="1" t="n">
-        <v>46210.48326388889</v>
+        <v>46240.94375</v>
       </c>
       <c r="Q806" s="1" t="n">
-        <v>46210.48326388889</v>
+        <v>46240.94375</v>
       </c>
       <c r="R806" t="n">
         <v>4.8</v>
@@ -48249,12 +48245,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>temitayo0835</t>
+          <t>temidiresholagbad</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temitayo0835</t>
+          <t>https://www.tiktok.com/@temidiresholagbad</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
@@ -48276,7 +48272,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O807" t="inlineStr">
@@ -48285,13 +48281,13 @@
         </is>
       </c>
       <c r="P807" s="1" t="n">
-        <v>46246.62105324074</v>
+        <v>46210.48326388889</v>
       </c>
       <c r="Q807" s="1" t="n">
-        <v>46246.62105324074</v>
+        <v>46210.48326388889</v>
       </c>
       <c r="R807" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S807" t="inlineStr">
         <is>
@@ -48308,12 +48304,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>temmiedee68</t>
+          <t>temitayo0835</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temmiedee68</t>
+          <t>https://www.tiktok.com/@temitayo0835</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
@@ -48344,10 +48340,10 @@
         </is>
       </c>
       <c r="P808" s="1" t="n">
-        <v>46248.75665509259</v>
+        <v>46246.62105324074</v>
       </c>
       <c r="Q808" s="1" t="n">
-        <v>46248.75665509259</v>
+        <v>46246.62105324074</v>
       </c>
       <c r="R808" t="n">
         <v>6</v>
@@ -48367,12 +48363,12 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>temmit7</t>
+          <t>temmiedee68</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temmit7</t>
+          <t>https://www.tiktok.com/@temmiedee68</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
@@ -48383,7 +48379,7 @@
       <c r="H809" t="inlineStr"/>
       <c r="I809" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J809" t="inlineStr"/>
@@ -48394,7 +48390,7 @@
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O809" t="inlineStr">
@@ -48403,13 +48399,13 @@
         </is>
       </c>
       <c r="P809" s="1" t="n">
-        <v>46236.455625</v>
+        <v>46248.75665509259</v>
       </c>
       <c r="Q809" s="1" t="n">
-        <v>46236.455625</v>
+        <v>46248.75665509259</v>
       </c>
       <c r="R809" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S809" t="inlineStr">
         <is>
@@ -48426,12 +48422,12 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>teresa_plugs</t>
+          <t>temmit7</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teresa_plugs</t>
+          <t>https://www.tiktok.com/@temmit7</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
@@ -48462,10 +48458,10 @@
         </is>
       </c>
       <c r="P810" s="1" t="n">
-        <v>46237.60640046297</v>
+        <v>46236.455625</v>
       </c>
       <c r="Q810" s="1" t="n">
-        <v>46237.60640046297</v>
+        <v>46236.455625</v>
       </c>
       <c r="R810" t="n">
         <v>4.8</v>
@@ -48485,12 +48481,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>thaminanoore</t>
+          <t>teresa_plugs</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thaminanoore</t>
+          <t>https://www.tiktok.com/@teresa_plugs</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
@@ -48521,10 +48517,10 @@
         </is>
       </c>
       <c r="P811" s="1" t="n">
-        <v>46212.65239583333</v>
+        <v>46237.60640046297</v>
       </c>
       <c r="Q811" s="1" t="n">
-        <v>46212.65239583333</v>
+        <v>46237.60640046297</v>
       </c>
       <c r="R811" t="n">
         <v>4.8</v>
@@ -48544,12 +48540,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>the.love.of.god36</t>
+          <t>thaminanoore</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the.love.of.god36</t>
+          <t>https://www.tiktok.com/@thaminanoore</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
@@ -48560,7 +48556,7 @@
       <c r="H812" t="inlineStr"/>
       <c r="I812" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J812" t="inlineStr"/>
@@ -48571,22 +48567,22 @@
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O812" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P812" s="1" t="n">
-        <v>46246.60049768518</v>
+        <v>46212.65239583333</v>
       </c>
       <c r="Q812" s="1" t="n">
-        <v>46246.60049768518</v>
+        <v>46212.65239583333</v>
       </c>
       <c r="R812" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S812" t="inlineStr">
         <is>
@@ -48603,12 +48599,12 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>the.witchy.wander</t>
+          <t>the.love.of.god36</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the.witchy.wander</t>
+          <t>https://www.tiktok.com/@the.love.of.god36</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
@@ -48619,7 +48615,7 @@
       <c r="H813" t="inlineStr"/>
       <c r="I813" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J813" t="inlineStr"/>
@@ -48630,7 +48626,7 @@
       </c>
       <c r="N813" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O813" t="inlineStr">
@@ -48639,13 +48635,13 @@
         </is>
       </c>
       <c r="P813" s="1" t="n">
-        <v>46196.76916666667</v>
+        <v>46246.60049768518</v>
       </c>
       <c r="Q813" s="1" t="n">
-        <v>46196.76916666667</v>
+        <v>46246.60049768518</v>
       </c>
       <c r="R813" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="S813" t="inlineStr">
         <is>
@@ -48662,12 +48658,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>the_akins2</t>
+          <t>the.witchy.wander</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_akins2</t>
+          <t>https://www.tiktok.com/@the.witchy.wander</t>
         </is>
       </c>
       <c r="C814" t="inlineStr"/>
@@ -48678,7 +48674,7 @@
       <c r="H814" t="inlineStr"/>
       <c r="I814" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J814" t="inlineStr"/>
@@ -48689,22 +48685,22 @@
       </c>
       <c r="N814" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O814" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P814" s="1" t="n">
-        <v>46222.77729166667</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="Q814" s="1" t="n">
-        <v>46222.77729166667</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="R814" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S814" t="inlineStr">
         <is>
@@ -48721,12 +48717,12 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>thefindspace</t>
+          <t>the_akins2</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thefindspace</t>
+          <t>https://www.tiktok.com/@the_akins2</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
@@ -48735,65 +48731,57 @@
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="inlineStr"/>
       <c r="H815" t="inlineStr"/>
-      <c r="I815" t="inlineStr"/>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J815" t="inlineStr"/>
       <c r="K815" t="inlineStr"/>
       <c r="L815" t="inlineStr"/>
       <c r="M815" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O815" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT), seller</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P815" s="1" t="n">
-        <v>46260.44456018518</v>
+        <v>46222.77729166667</v>
       </c>
       <c r="Q815" s="1" t="n">
-        <v>46260.44456018518</v>
+        <v>46222.77729166667</v>
       </c>
       <c r="R815" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="S815" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T815" t="n">
-        <v>2</v>
-      </c>
-      <c r="U815" t="n">
-        <v>0</v>
-      </c>
-      <c r="V815" t="n">
-        <v>0</v>
-      </c>
-      <c r="W815" t="n">
-        <v>96</v>
-      </c>
-      <c r="X815" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="Y815" t="n">
-        <v>-13</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T815" t="inlineStr"/>
+      <c r="U815" t="inlineStr"/>
+      <c r="V815" t="inlineStr"/>
+      <c r="W815" t="inlineStr"/>
+      <c r="X815" t="inlineStr"/>
+      <c r="Y815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>themyturpe4</t>
+          <t>thefindspace</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themyturpe4</t>
+          <t>https://www.tiktok.com/@thefindspace</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
@@ -48802,57 +48790,65 @@
       <c r="F816" t="inlineStr"/>
       <c r="G816" t="inlineStr"/>
       <c r="H816" t="inlineStr"/>
-      <c r="I816" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I816" t="inlineStr"/>
       <c r="J816" t="inlineStr"/>
       <c r="K816" t="inlineStr"/>
       <c r="L816" t="inlineStr"/>
       <c r="M816" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O816" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P816" s="1" t="n">
-        <v>46239.55702546296</v>
+        <v>46260.44456018518</v>
       </c>
       <c r="Q816" s="1" t="n">
-        <v>46239.55702546296</v>
+        <v>46260.44456018518</v>
       </c>
       <c r="R816" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="S816" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T816" t="inlineStr"/>
-      <c r="U816" t="inlineStr"/>
-      <c r="V816" t="inlineStr"/>
-      <c r="W816" t="inlineStr"/>
-      <c r="X816" t="inlineStr"/>
-      <c r="Y816" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T816" t="n">
+        <v>2</v>
+      </c>
+      <c r="U816" t="n">
+        <v>0</v>
+      </c>
+      <c r="V816" t="n">
+        <v>0</v>
+      </c>
+      <c r="W816" t="n">
+        <v>96</v>
+      </c>
+      <c r="X816" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="Y816" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>theresaboakye74</t>
+          <t>themyturpe4</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theresaboakye74</t>
+          <t>https://www.tiktok.com/@themyturpe4</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -48883,10 +48879,10 @@
         </is>
       </c>
       <c r="P817" s="1" t="n">
-        <v>46230.67072916667</v>
+        <v>46239.55702546296</v>
       </c>
       <c r="Q817" s="1" t="n">
-        <v>46230.67072916667</v>
+        <v>46239.55702546296</v>
       </c>
       <c r="R817" t="n">
         <v>4.8</v>
@@ -48906,12 +48902,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>thetripleteez</t>
+          <t>theresaboakye74</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thetripleteez</t>
+          <t>https://www.tiktok.com/@theresaboakye74</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
@@ -48922,7 +48918,7 @@
       <c r="H818" t="inlineStr"/>
       <c r="I818" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J818" t="inlineStr"/>
@@ -48933,56 +48929,44 @@
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O818" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P818" s="1" t="n">
-        <v>46198.62644675926</v>
+        <v>46230.67072916667</v>
       </c>
       <c r="Q818" s="1" t="n">
-        <v>46198.62644675926</v>
+        <v>46230.67072916667</v>
       </c>
       <c r="R818" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S818" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T818" t="n">
-        <v>1</v>
-      </c>
-      <c r="U818" t="n">
-        <v>0</v>
-      </c>
-      <c r="V818" t="n">
-        <v>0</v>
-      </c>
-      <c r="W818" t="n">
-        <v>2</v>
-      </c>
-      <c r="X818" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="Y818" t="n">
-        <v>6</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T818" t="inlineStr"/>
+      <c r="U818" t="inlineStr"/>
+      <c r="V818" t="inlineStr"/>
+      <c r="W818" t="inlineStr"/>
+      <c r="X818" t="inlineStr"/>
+      <c r="Y818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>thumandpea123</t>
+          <t>thetripleteez</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thumandpea123</t>
+          <t>https://www.tiktok.com/@thetripleteez</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
@@ -48993,7 +48977,7 @@
       <c r="H819" t="inlineStr"/>
       <c r="I819" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J819" t="inlineStr"/>
@@ -49004,44 +48988,56 @@
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O819" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P819" s="1" t="n">
-        <v>46219.8472800926</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="Q819" s="1" t="n">
-        <v>46219.8472800926</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="R819" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S819" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T819" t="inlineStr"/>
-      <c r="U819" t="inlineStr"/>
-      <c r="V819" t="inlineStr"/>
-      <c r="W819" t="inlineStr"/>
-      <c r="X819" t="inlineStr"/>
-      <c r="Y819" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T819" t="n">
+        <v>1</v>
+      </c>
+      <c r="U819" t="n">
+        <v>0</v>
+      </c>
+      <c r="V819" t="n">
+        <v>0</v>
+      </c>
+      <c r="W819" t="n">
+        <v>2</v>
+      </c>
+      <c r="X819" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="Y819" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>tifeyhslash</t>
+          <t>thumandpea123</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tifeyhslash</t>
+          <t>https://www.tiktok.com/@thumandpea123</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
@@ -49052,7 +49048,7 @@
       <c r="H820" t="inlineStr"/>
       <c r="I820" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J820" t="inlineStr"/>
@@ -49063,56 +49059,44 @@
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O820" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P820" s="1" t="n">
-        <v>46220.44594907408</v>
+        <v>46219.8472800926</v>
       </c>
       <c r="Q820" s="1" t="n">
-        <v>46220.44594907408</v>
+        <v>46219.8472800926</v>
       </c>
       <c r="R820" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S820" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T820" t="n">
-        <v>1</v>
-      </c>
-      <c r="U820" t="n">
-        <v>0</v>
-      </c>
-      <c r="V820" t="n">
-        <v>0</v>
-      </c>
-      <c r="W820" t="n">
-        <v>7</v>
-      </c>
-      <c r="X820" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="Y820" t="n">
-        <v>5</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T820" t="inlineStr"/>
+      <c r="U820" t="inlineStr"/>
+      <c r="V820" t="inlineStr"/>
+      <c r="W820" t="inlineStr"/>
+      <c r="X820" t="inlineStr"/>
+      <c r="Y820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>tiktok.comusershaza</t>
+          <t>tifeyhslash</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktok.comusershaza</t>
+          <t>https://www.tiktok.com/@tifeyhslash</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -49123,7 +49107,7 @@
       <c r="H821" t="inlineStr"/>
       <c r="I821" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J821" t="inlineStr"/>
@@ -49134,44 +49118,56 @@
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O821" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P821" s="1" t="n">
-        <v>46234.01479166667</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="Q821" s="1" t="n">
-        <v>46234.01479166667</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="R821" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S821" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T821" t="inlineStr"/>
-      <c r="U821" t="inlineStr"/>
-      <c r="V821" t="inlineStr"/>
-      <c r="W821" t="inlineStr"/>
-      <c r="X821" t="inlineStr"/>
-      <c r="Y821" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T821" t="n">
+        <v>1</v>
+      </c>
+      <c r="U821" t="n">
+        <v>0</v>
+      </c>
+      <c r="V821" t="n">
+        <v>0</v>
+      </c>
+      <c r="W821" t="n">
+        <v>7</v>
+      </c>
+      <c r="X821" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Y821" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>tiktokuserssssssww</t>
+          <t>tiktok.comusershaza</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktokuserssssssww</t>
+          <t>https://www.tiktok.com/@tiktok.comusershaza</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
@@ -49193,7 +49189,7 @@
       </c>
       <c r="N822" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O822" t="inlineStr">
@@ -49202,13 +49198,13 @@
         </is>
       </c>
       <c r="P822" s="1" t="n">
-        <v>46201.06403935186</v>
+        <v>46234.01479166667</v>
       </c>
       <c r="Q822" s="1" t="n">
-        <v>46201.06403935186</v>
+        <v>46234.01479166667</v>
       </c>
       <c r="R822" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S822" t="inlineStr">
         <is>
@@ -49225,12 +49221,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>tinash1330</t>
+          <t>tiktokuserssssssww</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinash1330</t>
+          <t>https://www.tiktok.com/@tiktokuserssssssww</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -49252,7 +49248,7 @@
       </c>
       <c r="N823" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O823" t="inlineStr">
@@ -49261,13 +49257,13 @@
         </is>
       </c>
       <c r="P823" s="1" t="n">
-        <v>46221.52363425926</v>
+        <v>46201.06403935186</v>
       </c>
       <c r="Q823" s="1" t="n">
-        <v>46221.52363425926</v>
+        <v>46201.06403935186</v>
       </c>
       <c r="R823" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S823" t="inlineStr">
         <is>
@@ -49284,12 +49280,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>tinashairandbeauty</t>
+          <t>tinash1330</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinashairandbeauty</t>
+          <t>https://www.tiktok.com/@tinash1330</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
@@ -49311,7 +49307,7 @@
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O824" t="inlineStr">
@@ -49320,13 +49316,13 @@
         </is>
       </c>
       <c r="P824" s="1" t="n">
-        <v>46153.36642361111</v>
+        <v>46221.52363425926</v>
       </c>
       <c r="Q824" s="1" t="n">
-        <v>46153.36642361111</v>
+        <v>46221.52363425926</v>
       </c>
       <c r="R824" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S824" t="inlineStr">
         <is>
@@ -49343,12 +49339,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>tinu.ola</t>
+          <t>tinashairandbeauty</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinu.ola</t>
+          <t>https://www.tiktok.com/@tinashairandbeauty</t>
         </is>
       </c>
       <c r="C825" t="inlineStr"/>
@@ -49359,7 +49355,7 @@
       <c r="H825" t="inlineStr"/>
       <c r="I825" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J825" t="inlineStr"/>
@@ -49370,22 +49366,22 @@
       </c>
       <c r="N825" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O825" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P825" s="1" t="n">
-        <v>46246.69505787037</v>
+        <v>46153.36642361111</v>
       </c>
       <c r="Q825" s="1" t="n">
-        <v>46246.69505787037</v>
+        <v>46153.36642361111</v>
       </c>
       <c r="R825" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="S825" t="inlineStr">
         <is>
@@ -49402,12 +49398,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>tinugold123</t>
+          <t>tinu.ola</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinugold123</t>
+          <t>https://www.tiktok.com/@tinu.ola</t>
         </is>
       </c>
       <c r="C826" t="inlineStr"/>
@@ -49429,22 +49425,22 @@
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O826" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P826" s="1" t="n">
-        <v>46238.029375</v>
+        <v>46246.69505787037</v>
       </c>
       <c r="Q826" s="1" t="n">
-        <v>46238.029375</v>
+        <v>46246.69505787037</v>
       </c>
       <c r="R826" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="S826" t="inlineStr">
         <is>
@@ -49461,12 +49457,12 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>tirzahbyoneal</t>
+          <t>tinugold123</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tirzahbyoneal</t>
+          <t>https://www.tiktok.com/@tinugold123</t>
         </is>
       </c>
       <c r="C827" t="inlineStr"/>
@@ -49477,7 +49473,7 @@
       <c r="H827" t="inlineStr"/>
       <c r="I827" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J827" t="inlineStr"/>
@@ -49497,10 +49493,10 @@
         </is>
       </c>
       <c r="P827" s="1" t="n">
-        <v>46201.90878472223</v>
+        <v>46238.029375</v>
       </c>
       <c r="Q827" s="1" t="n">
-        <v>46201.90878472223</v>
+        <v>46238.029375</v>
       </c>
       <c r="R827" t="n">
         <v>6</v>
@@ -49520,12 +49516,12 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>titiagboola</t>
+          <t>tirzahbyoneal</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@titiagboola</t>
+          <t>https://www.tiktok.com/@tirzahbyoneal</t>
         </is>
       </c>
       <c r="C828" t="inlineStr"/>
@@ -49536,7 +49532,7 @@
       <c r="H828" t="inlineStr"/>
       <c r="I828" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J828" t="inlineStr"/>
@@ -49547,7 +49543,7 @@
       </c>
       <c r="N828" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O828" t="inlineStr">
@@ -49556,13 +49552,13 @@
         </is>
       </c>
       <c r="P828" s="1" t="n">
-        <v>46209.72179398148</v>
+        <v>46201.90878472223</v>
       </c>
       <c r="Q828" s="1" t="n">
-        <v>46209.72179398148</v>
+        <v>46201.90878472223</v>
       </c>
       <c r="R828" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S828" t="inlineStr">
         <is>
@@ -49579,12 +49575,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>titilayosanusi</t>
+          <t>titiagboola</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@titilayosanusi</t>
+          <t>https://www.tiktok.com/@titiagboola</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -49615,10 +49611,10 @@
         </is>
       </c>
       <c r="P829" s="1" t="n">
-        <v>46217.10659722222</v>
+        <v>46209.72179398148</v>
       </c>
       <c r="Q829" s="1" t="n">
-        <v>46217.10659722222</v>
+        <v>46209.72179398148</v>
       </c>
       <c r="R829" t="n">
         <v>4.8</v>
@@ -49638,12 +49634,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>titty.titty8</t>
+          <t>titilayosanusi</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@titty.titty8</t>
+          <t>https://www.tiktok.com/@titilayosanusi</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -49654,7 +49650,7 @@
       <c r="H830" t="inlineStr"/>
       <c r="I830" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J830" t="inlineStr"/>
@@ -49674,10 +49670,10 @@
         </is>
       </c>
       <c r="P830" s="1" t="n">
-        <v>46218.68445601852</v>
+        <v>46217.10659722222</v>
       </c>
       <c r="Q830" s="1" t="n">
-        <v>46218.68445601852</v>
+        <v>46217.10659722222</v>
       </c>
       <c r="R830" t="n">
         <v>4.8</v>
@@ -49697,12 +49693,12 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>to_biiiii1</t>
+          <t>titty.titty8</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@to_biiiii1</t>
+          <t>https://www.tiktok.com/@titty.titty8</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -49713,7 +49709,7 @@
       <c r="H831" t="inlineStr"/>
       <c r="I831" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J831" t="inlineStr"/>
@@ -49724,7 +49720,7 @@
       </c>
       <c r="N831" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O831" t="inlineStr">
@@ -49733,13 +49729,13 @@
         </is>
       </c>
       <c r="P831" s="1" t="n">
-        <v>46250.35457175926</v>
+        <v>46218.68445601852</v>
       </c>
       <c r="Q831" s="1" t="n">
-        <v>46250.35457175926</v>
+        <v>46218.68445601852</v>
       </c>
       <c r="R831" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S831" t="inlineStr">
         <is>
@@ -49756,12 +49752,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>tolaniogunlesi998</t>
+          <t>to_biiiii1</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tolaniogunlesi998</t>
+          <t>https://www.tiktok.com/@to_biiiii1</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -49783,7 +49779,7 @@
       </c>
       <c r="N832" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O832" t="inlineStr">
@@ -49792,13 +49788,13 @@
         </is>
       </c>
       <c r="P832" s="1" t="n">
-        <v>46216.5428587963</v>
+        <v>46250.35457175926</v>
       </c>
       <c r="Q832" s="1" t="n">
-        <v>46216.5428587963</v>
+        <v>46250.35457175926</v>
       </c>
       <c r="R832" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S832" t="inlineStr">
         <is>
@@ -49815,12 +49811,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>tomo.265</t>
+          <t>tolaniogunlesi998</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tomo.265</t>
+          <t>https://www.tiktok.com/@tolaniogunlesi998</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -49831,7 +49827,7 @@
       <c r="H833" t="inlineStr"/>
       <c r="I833" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J833" t="inlineStr"/>
@@ -49851,10 +49847,10 @@
         </is>
       </c>
       <c r="P833" s="1" t="n">
-        <v>46227.50211805556</v>
+        <v>46216.5428587963</v>
       </c>
       <c r="Q833" s="1" t="n">
-        <v>46227.50211805556</v>
+        <v>46216.5428587963</v>
       </c>
       <c r="R833" t="n">
         <v>4.8</v>
@@ -49874,12 +49870,12 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>tony03672</t>
+          <t>tomo.265</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tony03672</t>
+          <t>https://www.tiktok.com/@tomo.265</t>
         </is>
       </c>
       <c r="C834" t="inlineStr"/>
@@ -49901,22 +49897,22 @@
       </c>
       <c r="N834" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O834" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P834" s="1" t="n">
-        <v>45993.6759375</v>
+        <v>46227.50211805556</v>
       </c>
       <c r="Q834" s="1" t="n">
-        <v>45993.6759375</v>
+        <v>46227.50211805556</v>
       </c>
       <c r="R834" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="S834" t="inlineStr">
         <is>
@@ -49933,12 +49929,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>topinsonjoe</t>
+          <t>tony03672</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topinsonjoe</t>
+          <t>https://www.tiktok.com/@tony03672</t>
         </is>
       </c>
       <c r="C835" t="inlineStr"/>
@@ -49949,7 +49945,7 @@
       <c r="H835" t="inlineStr"/>
       <c r="I835" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J835" t="inlineStr"/>
@@ -49960,22 +49956,22 @@
       </c>
       <c r="N835" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O835" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P835" s="1" t="n">
-        <v>46219.29</v>
+        <v>45993.6759375</v>
       </c>
       <c r="Q835" s="1" t="n">
-        <v>46219.29</v>
+        <v>45993.6759375</v>
       </c>
       <c r="R835" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S835" t="inlineStr">
         <is>
@@ -49992,12 +49988,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>toyin.georgetaylo</t>
+          <t>topinsonjoe</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toyin.georgetaylo</t>
+          <t>https://www.tiktok.com/@topinsonjoe</t>
         </is>
       </c>
       <c r="C836" t="inlineStr"/>
@@ -50008,7 +50004,7 @@
       <c r="H836" t="inlineStr"/>
       <c r="I836" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J836" t="inlineStr"/>
@@ -50028,10 +50024,10 @@
         </is>
       </c>
       <c r="P836" s="1" t="n">
-        <v>46220.63767361111</v>
+        <v>46219.29</v>
       </c>
       <c r="Q836" s="1" t="n">
-        <v>46220.63767361111</v>
+        <v>46219.29</v>
       </c>
       <c r="R836" t="n">
         <v>4.8</v>
@@ -50051,12 +50047,12 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>toyinedos</t>
+          <t>toyin.georgetaylo</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toyinedos</t>
+          <t>https://www.tiktok.com/@toyin.georgetaylo</t>
         </is>
       </c>
       <c r="C837" t="inlineStr"/>
@@ -50067,7 +50063,7 @@
       <c r="H837" t="inlineStr"/>
       <c r="I837" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J837" t="inlineStr"/>
@@ -50087,10 +50083,10 @@
         </is>
       </c>
       <c r="P837" s="1" t="n">
-        <v>46238.3083912037</v>
+        <v>46220.63767361111</v>
       </c>
       <c r="Q837" s="1" t="n">
-        <v>46238.3083912037</v>
+        <v>46220.63767361111</v>
       </c>
       <c r="R837" t="n">
         <v>4.8</v>
@@ -50110,12 +50106,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>traetari1</t>
+          <t>toyinedos</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@traetari1</t>
+          <t>https://www.tiktok.com/@toyinedos</t>
         </is>
       </c>
       <c r="C838" t="inlineStr"/>
@@ -50146,10 +50142,10 @@
         </is>
       </c>
       <c r="P838" s="1" t="n">
-        <v>46238.87353009259</v>
+        <v>46238.3083912037</v>
       </c>
       <c r="Q838" s="1" t="n">
-        <v>46238.87353009259</v>
+        <v>46238.3083912037</v>
       </c>
       <c r="R838" t="n">
         <v>4.8</v>
@@ -50169,12 +50165,12 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>tran.le455</t>
+          <t>traetari1</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tran.le455</t>
+          <t>https://www.tiktok.com/@traetari1</t>
         </is>
       </c>
       <c r="C839" t="inlineStr"/>
@@ -50183,7 +50179,11 @@
       <c r="F839" t="inlineStr"/>
       <c r="G839" t="inlineStr"/>
       <c r="H839" t="inlineStr"/>
-      <c r="I839" t="inlineStr"/>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J839" t="inlineStr"/>
       <c r="K839" t="inlineStr"/>
       <c r="L839" t="inlineStr"/>
@@ -50192,22 +50192,22 @@
       </c>
       <c r="N839" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O839" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P839" s="1" t="n">
-        <v>46262.61487268518</v>
+        <v>46238.87353009259</v>
       </c>
       <c r="Q839" s="1" t="n">
-        <v>46262.61487268518</v>
+        <v>46238.87353009259</v>
       </c>
       <c r="R839" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S839" t="inlineStr">
         <is>
@@ -50224,12 +50224,12 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>treasure.lope</t>
+          <t>tran.le455</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@treasure.lope</t>
+          <t>https://www.tiktok.com/@tran.le455</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
@@ -50238,11 +50238,7 @@
       <c r="F840" t="inlineStr"/>
       <c r="G840" t="inlineStr"/>
       <c r="H840" t="inlineStr"/>
-      <c r="I840" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I840" t="inlineStr"/>
       <c r="J840" t="inlineStr"/>
       <c r="K840" t="inlineStr"/>
       <c r="L840" t="inlineStr"/>
@@ -50251,22 +50247,22 @@
       </c>
       <c r="N840" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O840" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P840" s="1" t="n">
-        <v>46207.89181712963</v>
+        <v>46262.61487268518</v>
       </c>
       <c r="Q840" s="1" t="n">
-        <v>46207.89181712963</v>
+        <v>46262.61487268518</v>
       </c>
       <c r="R840" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S840" t="inlineStr">
         <is>
@@ -50283,12 +50279,12 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>treasurerealm64</t>
+          <t>treasure.lope</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@treasurerealm64</t>
+          <t>https://www.tiktok.com/@treasure.lope</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
@@ -50299,7 +50295,7 @@
       <c r="H841" t="inlineStr"/>
       <c r="I841" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J841" t="inlineStr"/>
@@ -50319,10 +50315,10 @@
         </is>
       </c>
       <c r="P841" s="1" t="n">
-        <v>46230.82032407408</v>
+        <v>46207.89181712963</v>
       </c>
       <c r="Q841" s="1" t="n">
-        <v>46230.82032407408</v>
+        <v>46207.89181712963</v>
       </c>
       <c r="R841" t="n">
         <v>4.8</v>
@@ -50342,12 +50338,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>trending_gists_omoola</t>
+          <t>treasurerealm64</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trending_gists_omoola</t>
+          <t>https://www.tiktok.com/@treasurerealm64</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
@@ -50356,7 +50352,11 @@
       <c r="F842" t="inlineStr"/>
       <c r="G842" t="inlineStr"/>
       <c r="H842" t="inlineStr"/>
-      <c r="I842" t="inlineStr"/>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J842" t="inlineStr"/>
       <c r="K842" t="inlineStr"/>
       <c r="L842" t="inlineStr"/>
@@ -50365,22 +50365,22 @@
       </c>
       <c r="N842" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O842" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P842" s="1" t="n">
-        <v>46264.89782407408</v>
+        <v>46230.82032407408</v>
       </c>
       <c r="Q842" s="1" t="n">
-        <v>46264.89782407408</v>
+        <v>46230.82032407408</v>
       </c>
       <c r="R842" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S842" t="inlineStr">
         <is>
@@ -50397,12 +50397,12 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>tricia.xo1</t>
+          <t>trending_gists_omoola</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tricia.xo1</t>
+          <t>https://www.tiktok.com/@trending_gists_omoola</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
@@ -50411,11 +50411,7 @@
       <c r="F843" t="inlineStr"/>
       <c r="G843" t="inlineStr"/>
       <c r="H843" t="inlineStr"/>
-      <c r="I843" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I843" t="inlineStr"/>
       <c r="J843" t="inlineStr"/>
       <c r="K843" t="inlineStr"/>
       <c r="L843" t="inlineStr"/>
@@ -50424,22 +50420,22 @@
       </c>
       <c r="N843" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O843" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P843" s="1" t="n">
-        <v>46209.36672453704</v>
+        <v>46264.89782407408</v>
       </c>
       <c r="Q843" s="1" t="n">
-        <v>46209.36672453704</v>
+        <v>46264.89782407408</v>
       </c>
       <c r="R843" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S843" t="inlineStr">
         <is>
@@ -50456,12 +50452,12 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>triplehoney8</t>
+          <t>tricia.xo1</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triplehoney8</t>
+          <t>https://www.tiktok.com/@tricia.xo1</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -50472,7 +50468,7 @@
       <c r="H844" t="inlineStr"/>
       <c r="I844" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J844" t="inlineStr"/>
@@ -50492,10 +50488,10 @@
         </is>
       </c>
       <c r="P844" s="1" t="n">
-        <v>46239.38399305556</v>
+        <v>46209.36672453704</v>
       </c>
       <c r="Q844" s="1" t="n">
-        <v>46239.38399305556</v>
+        <v>46209.36672453704</v>
       </c>
       <c r="R844" t="n">
         <v>4.8</v>
@@ -50515,12 +50511,12 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>tuturasdumitru</t>
+          <t>triplehoney8</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tuturasdumitru</t>
+          <t>https://www.tiktok.com/@triplehoney8</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -50531,7 +50527,7 @@
       <c r="H845" t="inlineStr"/>
       <c r="I845" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J845" t="inlineStr"/>
@@ -50551,10 +50547,10 @@
         </is>
       </c>
       <c r="P845" s="1" t="n">
-        <v>46208.76107638889</v>
+        <v>46239.38399305556</v>
       </c>
       <c r="Q845" s="1" t="n">
-        <v>46208.76107638889</v>
+        <v>46239.38399305556</v>
       </c>
       <c r="R845" t="n">
         <v>4.8</v>
@@ -50574,12 +50570,12 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>twasjael</t>
+          <t>tuturasdumitru</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@twasjael</t>
+          <t>https://www.tiktok.com/@tuturasdumitru</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -50590,7 +50586,7 @@
       <c r="H846" t="inlineStr"/>
       <c r="I846" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J846" t="inlineStr"/>
@@ -50610,10 +50606,10 @@
         </is>
       </c>
       <c r="P846" s="1" t="n">
-        <v>46232.34398148148</v>
+        <v>46208.76107638889</v>
       </c>
       <c r="Q846" s="1" t="n">
-        <v>46232.34398148148</v>
+        <v>46208.76107638889</v>
       </c>
       <c r="R846" t="n">
         <v>4.8</v>
@@ -50633,12 +50629,12 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>uh.numnumnum</t>
+          <t>twasjael</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uh.numnumnum</t>
+          <t>https://www.tiktok.com/@twasjael</t>
         </is>
       </c>
       <c r="C847" t="inlineStr"/>
@@ -50649,7 +50645,7 @@
       <c r="H847" t="inlineStr"/>
       <c r="I847" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="J847" t="inlineStr"/>
@@ -50669,10 +50665,10 @@
         </is>
       </c>
       <c r="P847" s="1" t="n">
-        <v>46226.59572916666</v>
+        <v>46232.34398148148</v>
       </c>
       <c r="Q847" s="1" t="n">
-        <v>46226.59572916666</v>
+        <v>46232.34398148148</v>
       </c>
       <c r="R847" t="n">
         <v>4.8</v>
@@ -50692,12 +50688,12 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>ukhtimuslima21</t>
+          <t>uh.numnumnum</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ukhtimuslima21</t>
+          <t>https://www.tiktok.com/@uh.numnumnum</t>
         </is>
       </c>
       <c r="C848" t="inlineStr"/>
@@ -50708,7 +50704,7 @@
       <c r="H848" t="inlineStr"/>
       <c r="I848" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J848" t="inlineStr"/>
@@ -50728,10 +50724,10 @@
         </is>
       </c>
       <c r="P848" s="1" t="n">
-        <v>46224.76721064815</v>
+        <v>46226.59572916666</v>
       </c>
       <c r="Q848" s="1" t="n">
-        <v>46224.76721064815</v>
+        <v>46226.59572916666</v>
       </c>
       <c r="R848" t="n">
         <v>4.8</v>
@@ -50751,12 +50747,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>uky1090</t>
+          <t>ukhtimuslima21</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uky1090</t>
+          <t>https://www.tiktok.com/@ukhtimuslima21</t>
         </is>
       </c>
       <c r="C849" t="inlineStr"/>
@@ -50765,7 +50761,11 @@
       <c r="F849" t="inlineStr"/>
       <c r="G849" t="inlineStr"/>
       <c r="H849" t="inlineStr"/>
-      <c r="I849" t="inlineStr"/>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J849" t="inlineStr"/>
       <c r="K849" t="inlineStr"/>
       <c r="L849" t="inlineStr"/>
@@ -50774,22 +50774,22 @@
       </c>
       <c r="N849" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O849" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P849" s="1" t="n">
-        <v>46262.06763888889</v>
+        <v>46224.76721064815</v>
       </c>
       <c r="Q849" s="1" t="n">
-        <v>46262.06763888889</v>
+        <v>46224.76721064815</v>
       </c>
       <c r="R849" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S849" t="inlineStr">
         <is>
@@ -50806,12 +50806,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>umaadhussain</t>
+          <t>uky1090</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@umaadhussain</t>
+          <t>https://www.tiktok.com/@uky1090</t>
         </is>
       </c>
       <c r="C850" t="inlineStr"/>
@@ -50820,11 +50820,7 @@
       <c r="F850" t="inlineStr"/>
       <c r="G850" t="inlineStr"/>
       <c r="H850" t="inlineStr"/>
-      <c r="I850" t="inlineStr">
-        <is>
-          <t>South Asian</t>
-        </is>
-      </c>
+      <c r="I850" t="inlineStr"/>
       <c r="J850" t="inlineStr"/>
       <c r="K850" t="inlineStr"/>
       <c r="L850" t="inlineStr"/>
@@ -50833,22 +50829,22 @@
       </c>
       <c r="N850" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O850" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P850" s="1" t="n">
-        <v>46209.50694444445</v>
+        <v>46262.06763888889</v>
       </c>
       <c r="Q850" s="1" t="n">
-        <v>46209.50694444445</v>
+        <v>46262.06763888889</v>
       </c>
       <c r="R850" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S850" t="inlineStr">
         <is>
@@ -50865,12 +50861,12 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>urlovemakisedits2</t>
+          <t>umaadhussain</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@urlovemakisedits2</t>
+          <t>https://www.tiktok.com/@umaadhussain</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
@@ -50881,7 +50877,7 @@
       <c r="H851" t="inlineStr"/>
       <c r="I851" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J851" t="inlineStr"/>
@@ -50901,10 +50897,10 @@
         </is>
       </c>
       <c r="P851" s="1" t="n">
-        <v>46223.48380787037</v>
+        <v>46209.50694444445</v>
       </c>
       <c r="Q851" s="1" t="n">
-        <v>46223.48380787037</v>
+        <v>46209.50694444445</v>
       </c>
       <c r="R851" t="n">
         <v>4.8</v>
@@ -50924,12 +50920,12 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>user.okikiwealth</t>
+          <t>urlovemakisedits2</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user.okikiwealth</t>
+          <t>https://www.tiktok.com/@urlovemakisedits2</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
@@ -50960,10 +50956,10 @@
         </is>
       </c>
       <c r="P852" s="1" t="n">
-        <v>46235.55792824074</v>
+        <v>46223.48380787037</v>
       </c>
       <c r="Q852" s="1" t="n">
-        <v>46235.55792824074</v>
+        <v>46223.48380787037</v>
       </c>
       <c r="R852" t="n">
         <v>4.8</v>
@@ -50983,12 +50979,12 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>user003204305</t>
+          <t>user.okikiwealth</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user003204305</t>
+          <t>https://www.tiktok.com/@user.okikiwealth</t>
         </is>
       </c>
       <c r="C853" t="inlineStr"/>
@@ -50999,7 +50995,7 @@
       <c r="H853" t="inlineStr"/>
       <c r="I853" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J853" t="inlineStr"/>
@@ -51019,10 +51015,10 @@
         </is>
       </c>
       <c r="P853" s="1" t="n">
-        <v>46207.6971412037</v>
+        <v>46235.55792824074</v>
       </c>
       <c r="Q853" s="1" t="n">
-        <v>46207.6971412037</v>
+        <v>46235.55792824074</v>
       </c>
       <c r="R853" t="n">
         <v>4.8</v>
@@ -51042,12 +51038,12 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>user13822840075788</t>
+          <t>user003204305</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user13822840075788</t>
+          <t>https://www.tiktok.com/@user003204305</t>
         </is>
       </c>
       <c r="C854" t="inlineStr"/>
@@ -51078,10 +51074,10 @@
         </is>
       </c>
       <c r="P854" s="1" t="n">
-        <v>46210.92520833333</v>
+        <v>46207.6971412037</v>
       </c>
       <c r="Q854" s="1" t="n">
-        <v>46210.92520833333</v>
+        <v>46207.6971412037</v>
       </c>
       <c r="R854" t="n">
         <v>4.8</v>
@@ -51101,12 +51097,12 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>user1466702213394</t>
+          <t>user13822840075788</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user1466702213394</t>
+          <t>https://www.tiktok.com/@user13822840075788</t>
         </is>
       </c>
       <c r="C855" t="inlineStr"/>
@@ -51117,7 +51113,7 @@
       <c r="H855" t="inlineStr"/>
       <c r="I855" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J855" t="inlineStr"/>
@@ -51137,10 +51133,10 @@
         </is>
       </c>
       <c r="P855" s="1" t="n">
-        <v>46234.47584490741</v>
+        <v>46210.92520833333</v>
       </c>
       <c r="Q855" s="1" t="n">
-        <v>46234.47584490741</v>
+        <v>46210.92520833333</v>
       </c>
       <c r="R855" t="n">
         <v>4.8</v>
@@ -51160,12 +51156,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>user1524873803257</t>
+          <t>user1466702213394</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user1524873803257</t>
+          <t>https://www.tiktok.com/@user1466702213394</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
@@ -51176,7 +51172,7 @@
       <c r="H856" t="inlineStr"/>
       <c r="I856" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J856" t="inlineStr"/>
@@ -51196,10 +51192,10 @@
         </is>
       </c>
       <c r="P856" s="1" t="n">
-        <v>46227.23572916666</v>
+        <v>46234.47584490741</v>
       </c>
       <c r="Q856" s="1" t="n">
-        <v>46227.23572916666</v>
+        <v>46234.47584490741</v>
       </c>
       <c r="R856" t="n">
         <v>4.8</v>
@@ -51219,12 +51215,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>user15510211574576</t>
+          <t>user1524873803257</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user15510211574576</t>
+          <t>https://www.tiktok.com/@user1524873803257</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -51255,10 +51251,10 @@
         </is>
       </c>
       <c r="P857" s="1" t="n">
-        <v>46210.85340277778</v>
+        <v>46227.23572916666</v>
       </c>
       <c r="Q857" s="1" t="n">
-        <v>46210.85340277778</v>
+        <v>46227.23572916666</v>
       </c>
       <c r="R857" t="n">
         <v>4.8</v>
@@ -51278,12 +51274,12 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>user1660073803243</t>
+          <t>user15510211574576</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user1660073803243</t>
+          <t>https://www.tiktok.com/@user15510211574576</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -51292,7 +51288,11 @@
       <c r="F858" t="inlineStr"/>
       <c r="G858" t="inlineStr"/>
       <c r="H858" t="inlineStr"/>
-      <c r="I858" t="inlineStr"/>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J858" t="inlineStr"/>
       <c r="K858" t="inlineStr"/>
       <c r="L858" t="inlineStr"/>
@@ -51301,22 +51301,22 @@
       </c>
       <c r="N858" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O858" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P858" s="1" t="n">
-        <v>46252.50942129629</v>
+        <v>46210.85340277778</v>
       </c>
       <c r="Q858" s="1" t="n">
-        <v>46252.50942129629</v>
+        <v>46210.85340277778</v>
       </c>
       <c r="R858" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S858" t="inlineStr">
         <is>
@@ -51333,12 +51333,12 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>user1849538441054</t>
+          <t>user1660073803243</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user1849538441054</t>
+          <t>https://www.tiktok.com/@user1660073803243</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
@@ -51347,35 +51347,31 @@
       <c r="F859" t="inlineStr"/>
       <c r="G859" t="inlineStr"/>
       <c r="H859" t="inlineStr"/>
-      <c r="I859" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+      <c r="I859" t="inlineStr"/>
       <c r="J859" t="inlineStr"/>
       <c r="K859" t="inlineStr"/>
       <c r="L859" t="inlineStr"/>
       <c r="M859" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N859" t="inlineStr">
         <is>
-          <t>Green Burner, Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O859" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT), seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P859" s="1" t="n">
-        <v>46234.65694444445</v>
+        <v>46252.50942129629</v>
       </c>
       <c r="Q859" s="1" t="n">
-        <v>46259.8296412037</v>
+        <v>46252.50942129629</v>
       </c>
       <c r="R859" t="n">
-        <v>10.7</v>
+        <v>5.9</v>
       </c>
       <c r="S859" t="inlineStr">
         <is>
@@ -51392,12 +51388,12 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>user18539263935775</t>
+          <t>user1849538441054</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user18539263935775</t>
+          <t>https://www.tiktok.com/@user1849538441054</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -51415,26 +51411,26 @@
       <c r="K860" t="inlineStr"/>
       <c r="L860" t="inlineStr"/>
       <c r="M860" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N860" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner, Lemon Ginger</t>
         </is>
       </c>
       <c r="O860" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P860" s="1" t="n">
-        <v>46240.15883101852</v>
+        <v>46234.65694444445</v>
       </c>
       <c r="Q860" s="1" t="n">
-        <v>46240.15883101852</v>
+        <v>46259.8296412037</v>
       </c>
       <c r="R860" t="n">
-        <v>4.8</v>
+        <v>10.7</v>
       </c>
       <c r="S860" t="inlineStr">
         <is>
@@ -51451,12 +51447,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>user2067381855385</t>
+          <t>user18539263935775</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2067381855385</t>
+          <t>https://www.tiktok.com/@user18539263935775</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -51487,10 +51483,10 @@
         </is>
       </c>
       <c r="P861" s="1" t="n">
-        <v>46215.89106481482</v>
+        <v>46240.15883101852</v>
       </c>
       <c r="Q861" s="1" t="n">
-        <v>46215.89106481482</v>
+        <v>46240.15883101852</v>
       </c>
       <c r="R861" t="n">
         <v>4.8</v>
@@ -51510,12 +51506,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>user2133928667610</t>
+          <t>user2067381855385</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2133928667610</t>
+          <t>https://www.tiktok.com/@user2067381855385</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
@@ -51546,10 +51542,10 @@
         </is>
       </c>
       <c r="P862" s="1" t="n">
-        <v>46238.9434837963</v>
+        <v>46215.89106481482</v>
       </c>
       <c r="Q862" s="1" t="n">
-        <v>46238.9434837963</v>
+        <v>46215.89106481482</v>
       </c>
       <c r="R862" t="n">
         <v>4.8</v>
@@ -51569,12 +51565,12 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>user22378493319474</t>
+          <t>user2133928667610</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user22378493319474</t>
+          <t>https://www.tiktok.com/@user2133928667610</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
@@ -51585,7 +51581,7 @@
       <c r="H863" t="inlineStr"/>
       <c r="I863" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J863" t="inlineStr"/>
@@ -51605,10 +51601,10 @@
         </is>
       </c>
       <c r="P863" s="1" t="n">
-        <v>46240.35208333333</v>
+        <v>46238.9434837963</v>
       </c>
       <c r="Q863" s="1" t="n">
-        <v>46240.35208333333</v>
+        <v>46238.9434837963</v>
       </c>
       <c r="R863" t="n">
         <v>4.8</v>
@@ -51628,12 +51624,12 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>user24484259047033</t>
+          <t>user22378493319474</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user24484259047033</t>
+          <t>https://www.tiktok.com/@user22378493319474</t>
         </is>
       </c>
       <c r="C864" t="inlineStr"/>
@@ -51644,7 +51640,7 @@
       <c r="H864" t="inlineStr"/>
       <c r="I864" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J864" t="inlineStr"/>
@@ -51655,7 +51651,7 @@
       </c>
       <c r="N864" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O864" t="inlineStr">
@@ -51664,13 +51660,13 @@
         </is>
       </c>
       <c r="P864" s="1" t="n">
-        <v>46178.61515046296</v>
+        <v>46240.35208333333</v>
       </c>
       <c r="Q864" s="1" t="n">
-        <v>46178.61515046296</v>
+        <v>46240.35208333333</v>
       </c>
       <c r="R864" t="n">
-        <v>12.4</v>
+        <v>4.8</v>
       </c>
       <c r="S864" t="inlineStr">
         <is>
@@ -51687,12 +51683,12 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>user2499773111198</t>
+          <t>user24484259047033</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2499773111198</t>
+          <t>https://www.tiktok.com/@user24484259047033</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
@@ -51714,7 +51710,7 @@
       </c>
       <c r="N865" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O865" t="inlineStr">
@@ -51723,13 +51719,13 @@
         </is>
       </c>
       <c r="P865" s="1" t="n">
-        <v>46225.03729166667</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="Q865" s="1" t="n">
-        <v>46225.03729166667</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="R865" t="n">
-        <v>4.8</v>
+        <v>12.4</v>
       </c>
       <c r="S865" t="inlineStr">
         <is>
@@ -51746,12 +51742,12 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>user2509825076594</t>
+          <t>user2499773111198</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2509825076594</t>
+          <t>https://www.tiktok.com/@user2499773111198</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -51762,7 +51758,7 @@
       <c r="H866" t="inlineStr"/>
       <c r="I866" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J866" t="inlineStr"/>
@@ -51782,10 +51778,10 @@
         </is>
       </c>
       <c r="P866" s="1" t="n">
-        <v>46231.6984837963</v>
+        <v>46225.03729166667</v>
       </c>
       <c r="Q866" s="1" t="n">
-        <v>46231.6984837963</v>
+        <v>46225.03729166667</v>
       </c>
       <c r="R866" t="n">
         <v>4.8</v>
@@ -51805,12 +51801,12 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>user2611154757676</t>
+          <t>user2509825076594</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2611154757676</t>
+          <t>https://www.tiktok.com/@user2509825076594</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -51841,10 +51837,10 @@
         </is>
       </c>
       <c r="P867" s="1" t="n">
-        <v>46231.88670138889</v>
+        <v>46231.6984837963</v>
       </c>
       <c r="Q867" s="1" t="n">
-        <v>46231.88670138889</v>
+        <v>46231.6984837963</v>
       </c>
       <c r="R867" t="n">
         <v>4.8</v>
@@ -51864,12 +51860,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>user26963863682186</t>
+          <t>user2611154757676</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user26963863682186</t>
+          <t>https://www.tiktok.com/@user2611154757676</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
@@ -51878,7 +51874,11 @@
       <c r="F868" t="inlineStr"/>
       <c r="G868" t="inlineStr"/>
       <c r="H868" t="inlineStr"/>
-      <c r="I868" t="inlineStr"/>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J868" t="inlineStr"/>
       <c r="K868" t="inlineStr"/>
       <c r="L868" t="inlineStr"/>
@@ -51887,22 +51887,22 @@
       </c>
       <c r="N868" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O868" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P868" s="1" t="n">
-        <v>46261.68694444445</v>
+        <v>46231.88670138889</v>
       </c>
       <c r="Q868" s="1" t="n">
-        <v>46261.68694444445</v>
+        <v>46231.88670138889</v>
       </c>
       <c r="R868" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S868" t="inlineStr">
         <is>
@@ -51919,12 +51919,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>user2940653632458</t>
+          <t>user26963863682186</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2940653632458</t>
+          <t>https://www.tiktok.com/@user26963863682186</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
@@ -51933,11 +51933,7 @@
       <c r="F869" t="inlineStr"/>
       <c r="G869" t="inlineStr"/>
       <c r="H869" t="inlineStr"/>
-      <c r="I869" t="inlineStr">
-        <is>
-          <t>Faceless</t>
-        </is>
-      </c>
+      <c r="I869" t="inlineStr"/>
       <c r="J869" t="inlineStr"/>
       <c r="K869" t="inlineStr"/>
       <c r="L869" t="inlineStr"/>
@@ -51946,22 +51942,22 @@
       </c>
       <c r="N869" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O869" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P869" s="1" t="n">
-        <v>46236.3840625</v>
+        <v>46261.68694444445</v>
       </c>
       <c r="Q869" s="1" t="n">
-        <v>46236.3840625</v>
+        <v>46261.68694444445</v>
       </c>
       <c r="R869" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S869" t="inlineStr">
         <is>
@@ -51978,12 +51974,12 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>user2997965690229</t>
+          <t>user2940653632458</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2997965690229</t>
+          <t>https://www.tiktok.com/@user2940653632458</t>
         </is>
       </c>
       <c r="C870" t="inlineStr"/>
@@ -51994,7 +51990,7 @@
       <c r="H870" t="inlineStr"/>
       <c r="I870" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J870" t="inlineStr"/>
@@ -52005,22 +52001,22 @@
       </c>
       <c r="N870" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O870" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P870" s="1" t="n">
-        <v>46248.79699074074</v>
+        <v>46236.3840625</v>
       </c>
       <c r="Q870" s="1" t="n">
-        <v>46248.79699074074</v>
+        <v>46236.3840625</v>
       </c>
       <c r="R870" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S870" t="inlineStr">
         <is>
@@ -52037,12 +52033,12 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>user3002455420</t>
+          <t>user2997965690229</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3002455420</t>
+          <t>https://www.tiktok.com/@user2997965690229</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
@@ -52064,22 +52060,22 @@
       </c>
       <c r="N871" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O871" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P871" s="1" t="n">
-        <v>46225.82162037037</v>
+        <v>46248.79699074074</v>
       </c>
       <c r="Q871" s="1" t="n">
-        <v>46225.82162037037</v>
+        <v>46248.79699074074</v>
       </c>
       <c r="R871" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S871" t="inlineStr">
         <is>
@@ -52096,12 +52092,12 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>user307169220</t>
+          <t>user3002455420</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user307169220</t>
+          <t>https://www.tiktok.com/@user3002455420</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
@@ -52112,7 +52108,7 @@
       <c r="H872" t="inlineStr"/>
       <c r="I872" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J872" t="inlineStr"/>
@@ -52132,10 +52128,10 @@
         </is>
       </c>
       <c r="P872" s="1" t="n">
-        <v>46222.65678240741</v>
+        <v>46225.82162037037</v>
       </c>
       <c r="Q872" s="1" t="n">
-        <v>46222.65678240741</v>
+        <v>46225.82162037037</v>
       </c>
       <c r="R872" t="n">
         <v>4.8</v>
@@ -52155,12 +52151,12 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>user3242536109635</t>
+          <t>user307169220</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3242536109635</t>
+          <t>https://www.tiktok.com/@user307169220</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
@@ -52191,10 +52187,10 @@
         </is>
       </c>
       <c r="P873" s="1" t="n">
-        <v>46237.86270833333</v>
+        <v>46222.65678240741</v>
       </c>
       <c r="Q873" s="1" t="n">
-        <v>46237.86270833333</v>
+        <v>46222.65678240741</v>
       </c>
       <c r="R873" t="n">
         <v>4.8</v>
@@ -52214,12 +52210,12 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>user336789764</t>
+          <t>user3242536109635</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user336789764</t>
+          <t>https://www.tiktok.com/@user3242536109635</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
@@ -52230,7 +52226,7 @@
       <c r="H874" t="inlineStr"/>
       <c r="I874" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J874" t="inlineStr"/>
@@ -52250,10 +52246,10 @@
         </is>
       </c>
       <c r="P874" s="1" t="n">
-        <v>46232.82585648148</v>
+        <v>46237.86270833333</v>
       </c>
       <c r="Q874" s="1" t="n">
-        <v>46232.82585648148</v>
+        <v>46237.86270833333</v>
       </c>
       <c r="R874" t="n">
         <v>4.8</v>
@@ -52273,12 +52269,12 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>user3606227777348</t>
+          <t>user336789764</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3606227777348</t>
+          <t>https://www.tiktok.com/@user336789764</t>
         </is>
       </c>
       <c r="C875" t="inlineStr"/>
@@ -52289,7 +52285,7 @@
       <c r="H875" t="inlineStr"/>
       <c r="I875" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J875" t="inlineStr"/>
@@ -52300,7 +52296,7 @@
       </c>
       <c r="N875" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O875" t="inlineStr">
@@ -52309,13 +52305,13 @@
         </is>
       </c>
       <c r="P875" s="1" t="n">
-        <v>46185.40584490741</v>
+        <v>46232.82585648148</v>
       </c>
       <c r="Q875" s="1" t="n">
-        <v>46185.40584490741</v>
+        <v>46232.82585648148</v>
       </c>
       <c r="R875" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S875" t="inlineStr">
         <is>
@@ -52332,12 +52328,12 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>user3955918607485</t>
+          <t>user3606227777348</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3955918607485</t>
+          <t>https://www.tiktok.com/@user3606227777348</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
@@ -52348,7 +52344,7 @@
       <c r="H876" t="inlineStr"/>
       <c r="I876" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J876" t="inlineStr"/>
@@ -52359,7 +52355,7 @@
       </c>
       <c r="N876" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O876" t="inlineStr">
@@ -52368,13 +52364,13 @@
         </is>
       </c>
       <c r="P876" s="1" t="n">
-        <v>46221.53251157407</v>
+        <v>46185.40584490741</v>
       </c>
       <c r="Q876" s="1" t="n">
-        <v>46221.53251157407</v>
+        <v>46185.40584490741</v>
       </c>
       <c r="R876" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S876" t="inlineStr">
         <is>
@@ -52391,12 +52387,12 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>user411982221</t>
+          <t>user3955918607485</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user411982221</t>
+          <t>https://www.tiktok.com/@user3955918607485</t>
         </is>
       </c>
       <c r="C877" t="inlineStr"/>
@@ -52427,10 +52423,10 @@
         </is>
       </c>
       <c r="P877" s="1" t="n">
-        <v>46216.60361111111</v>
+        <v>46221.53251157407</v>
       </c>
       <c r="Q877" s="1" t="n">
-        <v>46216.60361111111</v>
+        <v>46221.53251157407</v>
       </c>
       <c r="R877" t="n">
         <v>4.8</v>
@@ -52450,12 +52446,12 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>user42180953</t>
+          <t>user411982221</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user42180953</t>
+          <t>https://www.tiktok.com/@user411982221</t>
         </is>
       </c>
       <c r="C878" t="inlineStr"/>
@@ -52466,7 +52462,7 @@
       <c r="H878" t="inlineStr"/>
       <c r="I878" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J878" t="inlineStr"/>
@@ -52486,10 +52482,10 @@
         </is>
       </c>
       <c r="P878" s="1" t="n">
-        <v>46215.97638888889</v>
+        <v>46216.60361111111</v>
       </c>
       <c r="Q878" s="1" t="n">
-        <v>46215.97638888889</v>
+        <v>46216.60361111111</v>
       </c>
       <c r="R878" t="n">
         <v>4.8</v>
@@ -52509,12 +52505,12 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>user4423713561101</t>
+          <t>user42180953</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4423713561101</t>
+          <t>https://www.tiktok.com/@user42180953</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
@@ -52523,7 +52519,11 @@
       <c r="F879" t="inlineStr"/>
       <c r="G879" t="inlineStr"/>
       <c r="H879" t="inlineStr"/>
-      <c r="I879" t="inlineStr"/>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J879" t="inlineStr"/>
       <c r="K879" t="inlineStr"/>
       <c r="L879" t="inlineStr"/>
@@ -52532,22 +52532,22 @@
       </c>
       <c r="N879" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O879" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P879" s="1" t="n">
-        <v>46262.45489583333</v>
+        <v>46215.97638888889</v>
       </c>
       <c r="Q879" s="1" t="n">
-        <v>46262.45489583333</v>
+        <v>46215.97638888889</v>
       </c>
       <c r="R879" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S879" t="inlineStr">
         <is>
@@ -52564,12 +52564,12 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>user450470676288</t>
+          <t>user4423713561101</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user450470676288</t>
+          <t>https://www.tiktok.com/@user4423713561101</t>
         </is>
       </c>
       <c r="C880" t="inlineStr"/>
@@ -52578,11 +52578,7 @@
       <c r="F880" t="inlineStr"/>
       <c r="G880" t="inlineStr"/>
       <c r="H880" t="inlineStr"/>
-      <c r="I880" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I880" t="inlineStr"/>
       <c r="J880" t="inlineStr"/>
       <c r="K880" t="inlineStr"/>
       <c r="L880" t="inlineStr"/>
@@ -52591,22 +52587,22 @@
       </c>
       <c r="N880" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O880" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P880" s="1" t="n">
-        <v>46225.3074537037</v>
+        <v>46262.45489583333</v>
       </c>
       <c r="Q880" s="1" t="n">
-        <v>46225.3074537037</v>
+        <v>46262.45489583333</v>
       </c>
       <c r="R880" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S880" t="inlineStr">
         <is>
@@ -52623,12 +52619,12 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>user458118102612</t>
+          <t>user450470676288</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user458118102612</t>
+          <t>https://www.tiktok.com/@user450470676288</t>
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
@@ -52659,10 +52655,10 @@
         </is>
       </c>
       <c r="P881" s="1" t="n">
-        <v>46217.40354166667</v>
+        <v>46225.3074537037</v>
       </c>
       <c r="Q881" s="1" t="n">
-        <v>46217.40354166667</v>
+        <v>46225.3074537037</v>
       </c>
       <c r="R881" t="n">
         <v>4.8</v>
@@ -52682,12 +52678,12 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>user467542615061</t>
+          <t>user458118102612</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user467542615061</t>
+          <t>https://www.tiktok.com/@user458118102612</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -52698,7 +52694,7 @@
       <c r="H882" t="inlineStr"/>
       <c r="I882" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J882" t="inlineStr"/>
@@ -52718,10 +52714,10 @@
         </is>
       </c>
       <c r="P882" s="1" t="n">
-        <v>46212.24355324074</v>
+        <v>46217.40354166667</v>
       </c>
       <c r="Q882" s="1" t="n">
-        <v>46212.24355324074</v>
+        <v>46217.40354166667</v>
       </c>
       <c r="R882" t="n">
         <v>4.8</v>
@@ -52741,12 +52737,12 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>user4688052396059</t>
+          <t>user467542615061</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4688052396059</t>
+          <t>https://www.tiktok.com/@user467542615061</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>
@@ -52777,10 +52773,10 @@
         </is>
       </c>
       <c r="P883" s="1" t="n">
-        <v>46207.57041666667</v>
+        <v>46212.24355324074</v>
       </c>
       <c r="Q883" s="1" t="n">
-        <v>46207.57041666667</v>
+        <v>46212.24355324074</v>
       </c>
       <c r="R883" t="n">
         <v>4.8</v>
@@ -52800,12 +52796,12 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>user4961074980381</t>
+          <t>user4688052396059</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4961074980381</t>
+          <t>https://www.tiktok.com/@user4688052396059</t>
         </is>
       </c>
       <c r="C884" t="inlineStr"/>
@@ -52814,7 +52810,11 @@
       <c r="F884" t="inlineStr"/>
       <c r="G884" t="inlineStr"/>
       <c r="H884" t="inlineStr"/>
-      <c r="I884" t="inlineStr"/>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J884" t="inlineStr"/>
       <c r="K884" t="inlineStr"/>
       <c r="L884" t="inlineStr"/>
@@ -52823,22 +52823,22 @@
       </c>
       <c r="N884" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O884" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P884" s="1" t="n">
-        <v>46262.91384259259</v>
+        <v>46207.57041666667</v>
       </c>
       <c r="Q884" s="1" t="n">
-        <v>46262.91384259259</v>
+        <v>46207.57041666667</v>
       </c>
       <c r="R884" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S884" t="inlineStr">
         <is>
@@ -52855,12 +52855,12 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>user5007976343248</t>
+          <t>user4961074980381</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5007976343248</t>
+          <t>https://www.tiktok.com/@user4961074980381</t>
         </is>
       </c>
       <c r="C885" t="inlineStr"/>
@@ -52869,11 +52869,7 @@
       <c r="F885" t="inlineStr"/>
       <c r="G885" t="inlineStr"/>
       <c r="H885" t="inlineStr"/>
-      <c r="I885" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+      <c r="I885" t="inlineStr"/>
       <c r="J885" t="inlineStr"/>
       <c r="K885" t="inlineStr"/>
       <c r="L885" t="inlineStr"/>
@@ -52882,22 +52878,22 @@
       </c>
       <c r="N885" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O885" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P885" s="1" t="n">
-        <v>46232.6764699074</v>
+        <v>46262.91384259259</v>
       </c>
       <c r="Q885" s="1" t="n">
-        <v>46232.6764699074</v>
+        <v>46262.91384259259</v>
       </c>
       <c r="R885" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S885" t="inlineStr">
         <is>
@@ -52914,12 +52910,12 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>user50112483538821</t>
+          <t>user5007976343248</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user50112483538821</t>
+          <t>https://www.tiktok.com/@user5007976343248</t>
         </is>
       </c>
       <c r="C886" t="inlineStr"/>
@@ -52950,10 +52946,10 @@
         </is>
       </c>
       <c r="P886" s="1" t="n">
-        <v>46225.41709490741</v>
+        <v>46232.6764699074</v>
       </c>
       <c r="Q886" s="1" t="n">
-        <v>46225.41709490741</v>
+        <v>46232.6764699074</v>
       </c>
       <c r="R886" t="n">
         <v>4.8</v>
@@ -52973,12 +52969,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>user5167483848722</t>
+          <t>user50112483538821</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5167483848722</t>
+          <t>https://www.tiktok.com/@user50112483538821</t>
         </is>
       </c>
       <c r="C887" t="inlineStr"/>
@@ -53009,10 +53005,10 @@
         </is>
       </c>
       <c r="P887" s="1" t="n">
-        <v>46216.00447916667</v>
+        <v>46225.41709490741</v>
       </c>
       <c r="Q887" s="1" t="n">
-        <v>46216.00447916667</v>
+        <v>46225.41709490741</v>
       </c>
       <c r="R887" t="n">
         <v>4.8</v>
@@ -53032,12 +53028,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>user5366244810788</t>
+          <t>user5167483848722</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5366244810788</t>
+          <t>https://www.tiktok.com/@user5167483848722</t>
         </is>
       </c>
       <c r="C888" t="inlineStr"/>
@@ -53048,7 +53044,7 @@
       <c r="H888" t="inlineStr"/>
       <c r="I888" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J888" t="inlineStr"/>
@@ -53068,10 +53064,10 @@
         </is>
       </c>
       <c r="P888" s="1" t="n">
-        <v>46220.09133101852</v>
+        <v>46216.00447916667</v>
       </c>
       <c r="Q888" s="1" t="n">
-        <v>46220.09133101852</v>
+        <v>46216.00447916667</v>
       </c>
       <c r="R888" t="n">
         <v>4.8</v>
@@ -53091,12 +53087,12 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>user5724531303785</t>
+          <t>user5366244810788</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5724531303785</t>
+          <t>https://www.tiktok.com/@user5366244810788</t>
         </is>
       </c>
       <c r="C889" t="inlineStr"/>
@@ -53107,7 +53103,7 @@
       <c r="H889" t="inlineStr"/>
       <c r="I889" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J889" t="inlineStr"/>
@@ -53127,10 +53123,10 @@
         </is>
       </c>
       <c r="P889" s="1" t="n">
-        <v>46240.27773148148</v>
+        <v>46220.09133101852</v>
       </c>
       <c r="Q889" s="1" t="n">
-        <v>46240.27773148148</v>
+        <v>46220.09133101852</v>
       </c>
       <c r="R889" t="n">
         <v>4.8</v>
@@ -53150,12 +53146,12 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>user596114145414</t>
+          <t>user5724531303785</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user596114145414</t>
+          <t>https://www.tiktok.com/@user5724531303785</t>
         </is>
       </c>
       <c r="C890" t="inlineStr"/>
@@ -53164,7 +53160,11 @@
       <c r="F890" t="inlineStr"/>
       <c r="G890" t="inlineStr"/>
       <c r="H890" t="inlineStr"/>
-      <c r="I890" t="inlineStr"/>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J890" t="inlineStr"/>
       <c r="K890" t="inlineStr"/>
       <c r="L890" t="inlineStr"/>
@@ -53173,22 +53173,22 @@
       </c>
       <c r="N890" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O890" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P890" s="1" t="n">
-        <v>46262.78965277778</v>
+        <v>46240.27773148148</v>
       </c>
       <c r="Q890" s="1" t="n">
-        <v>46262.78965277778</v>
+        <v>46240.27773148148</v>
       </c>
       <c r="R890" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S890" t="inlineStr">
         <is>
@@ -53205,12 +53205,12 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>user59838594031894</t>
+          <t>user596114145414</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user59838594031894</t>
+          <t>https://www.tiktok.com/@user596114145414</t>
         </is>
       </c>
       <c r="C891" t="inlineStr"/>
@@ -53219,11 +53219,7 @@
       <c r="F891" t="inlineStr"/>
       <c r="G891" t="inlineStr"/>
       <c r="H891" t="inlineStr"/>
-      <c r="I891" t="inlineStr">
-        <is>
-          <t>Faceless</t>
-        </is>
-      </c>
+      <c r="I891" t="inlineStr"/>
       <c r="J891" t="inlineStr"/>
       <c r="K891" t="inlineStr"/>
       <c r="L891" t="inlineStr"/>
@@ -53232,22 +53228,22 @@
       </c>
       <c r="N891" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O891" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P891" s="1" t="n">
-        <v>46238.55344907408</v>
+        <v>46262.78965277778</v>
       </c>
       <c r="Q891" s="1" t="n">
-        <v>46238.55344907408</v>
+        <v>46262.78965277778</v>
       </c>
       <c r="R891" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="S891" t="inlineStr">
         <is>
@@ -53264,12 +53260,12 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>user6166966793526</t>
+          <t>user59838594031894</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6166966793526</t>
+          <t>https://www.tiktok.com/@user59838594031894</t>
         </is>
       </c>
       <c r="C892" t="inlineStr"/>
@@ -53278,7 +53274,11 @@
       <c r="F892" t="inlineStr"/>
       <c r="G892" t="inlineStr"/>
       <c r="H892" t="inlineStr"/>
-      <c r="I892" t="inlineStr"/>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
       <c r="J892" t="inlineStr"/>
       <c r="K892" t="inlineStr"/>
       <c r="L892" t="inlineStr"/>
@@ -53287,22 +53287,22 @@
       </c>
       <c r="N892" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O892" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P892" s="1" t="n">
-        <v>46253.35270833333</v>
+        <v>46238.55344907408</v>
       </c>
       <c r="Q892" s="1" t="n">
-        <v>46253.35270833333</v>
+        <v>46238.55344907408</v>
       </c>
       <c r="R892" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="S892" t="inlineStr">
         <is>
@@ -53319,12 +53319,12 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>user62832717591475</t>
+          <t>user6166966793526</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user62832717591475</t>
+          <t>https://www.tiktok.com/@user6166966793526</t>
         </is>
       </c>
       <c r="C893" t="inlineStr"/>
@@ -53351,10 +53351,10 @@
         </is>
       </c>
       <c r="P893" s="1" t="n">
-        <v>46253.30351851852</v>
+        <v>46253.35270833333</v>
       </c>
       <c r="Q893" s="1" t="n">
-        <v>46253.30351851852</v>
+        <v>46253.35270833333</v>
       </c>
       <c r="R893" t="n">
         <v>5.9</v>
@@ -53374,12 +53374,12 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>user630548237</t>
+          <t>user62832717591475</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user630548237</t>
+          <t>https://www.tiktok.com/@user62832717591475</t>
         </is>
       </c>
       <c r="C894" t="inlineStr"/>
@@ -53388,11 +53388,7 @@
       <c r="F894" t="inlineStr"/>
       <c r="G894" t="inlineStr"/>
       <c r="H894" t="inlineStr"/>
-      <c r="I894" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+      <c r="I894" t="inlineStr"/>
       <c r="J894" t="inlineStr"/>
       <c r="K894" t="inlineStr"/>
       <c r="L894" t="inlineStr"/>
@@ -53401,22 +53397,22 @@
       </c>
       <c r="N894" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O894" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P894" s="1" t="n">
-        <v>46212.98568287037</v>
+        <v>46253.30351851852</v>
       </c>
       <c r="Q894" s="1" t="n">
-        <v>46212.98568287037</v>
+        <v>46253.30351851852</v>
       </c>
       <c r="R894" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S894" t="inlineStr">
         <is>
@@ -53433,12 +53429,12 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>user6333787981304</t>
+          <t>user630548237</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6333787981304</t>
+          <t>https://www.tiktok.com/@user630548237</t>
         </is>
       </c>
       <c r="C895" t="inlineStr"/>
@@ -53460,7 +53456,7 @@
       </c>
       <c r="N895" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O895" t="inlineStr">
@@ -53469,13 +53465,13 @@
         </is>
       </c>
       <c r="P895" s="1" t="n">
-        <v>46218.50613425926</v>
+        <v>46212.98568287037</v>
       </c>
       <c r="Q895" s="1" t="n">
-        <v>46218.50613425926</v>
+        <v>46212.98568287037</v>
       </c>
       <c r="R895" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S895" t="inlineStr">
         <is>
@@ -53492,12 +53488,12 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>user6651682812259</t>
+          <t>user6333787981304</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6651682812259</t>
+          <t>https://www.tiktok.com/@user6333787981304</t>
         </is>
       </c>
       <c r="C896" t="inlineStr"/>
@@ -53506,7 +53502,11 @@
       <c r="F896" t="inlineStr"/>
       <c r="G896" t="inlineStr"/>
       <c r="H896" t="inlineStr"/>
-      <c r="I896" t="inlineStr"/>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J896" t="inlineStr"/>
       <c r="K896" t="inlineStr"/>
       <c r="L896" t="inlineStr"/>
@@ -53515,22 +53515,22 @@
       </c>
       <c r="N896" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O896" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P896" s="1" t="n">
-        <v>46262.01202546297</v>
+        <v>46218.50613425926</v>
       </c>
       <c r="Q896" s="1" t="n">
-        <v>46262.01202546297</v>
+        <v>46218.50613425926</v>
       </c>
       <c r="R896" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="S896" t="inlineStr">
         <is>
@@ -53547,12 +53547,12 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>user6678773820675</t>
+          <t>user6651682812259</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6678773820675</t>
+          <t>https://www.tiktok.com/@user6651682812259</t>
         </is>
       </c>
       <c r="C897" t="inlineStr"/>
@@ -53561,11 +53561,7 @@
       <c r="F897" t="inlineStr"/>
       <c r="G897" t="inlineStr"/>
       <c r="H897" t="inlineStr"/>
-      <c r="I897" t="inlineStr">
-        <is>
-          <t>Faceless</t>
-        </is>
-      </c>
+      <c r="I897" t="inlineStr"/>
       <c r="J897" t="inlineStr"/>
       <c r="K897" t="inlineStr"/>
       <c r="L897" t="inlineStr"/>
@@ -53574,22 +53570,22 @@
       </c>
       <c r="N897" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O897" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P897" s="1" t="n">
-        <v>46218.53957175926</v>
+        <v>46262.01202546297</v>
       </c>
       <c r="Q897" s="1" t="n">
-        <v>46218.53957175926</v>
+        <v>46262.01202546297</v>
       </c>
       <c r="R897" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S897" t="inlineStr">
         <is>
@@ -53606,12 +53602,12 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>user67333378229996</t>
+          <t>user6678773820675</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user67333378229996</t>
+          <t>https://www.tiktok.com/@user6678773820675</t>
         </is>
       </c>
       <c r="C898" t="inlineStr"/>
@@ -53642,10 +53638,10 @@
         </is>
       </c>
       <c r="P898" s="1" t="n">
-        <v>46234.39538194444</v>
+        <v>46218.53957175926</v>
       </c>
       <c r="Q898" s="1" t="n">
-        <v>46234.39538194444</v>
+        <v>46218.53957175926</v>
       </c>
       <c r="R898" t="n">
         <v>4.8</v>
@@ -53665,12 +53661,12 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>user6737190678194</t>
+          <t>user67333378229996</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6737190678194</t>
+          <t>https://www.tiktok.com/@user67333378229996</t>
         </is>
       </c>
       <c r="C899" t="inlineStr"/>
@@ -53681,7 +53677,7 @@
       <c r="H899" t="inlineStr"/>
       <c r="I899" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J899" t="inlineStr"/>
@@ -53701,10 +53697,10 @@
         </is>
       </c>
       <c r="P899" s="1" t="n">
-        <v>46222.63238425926</v>
+        <v>46234.39538194444</v>
       </c>
       <c r="Q899" s="1" t="n">
-        <v>46222.63238425926</v>
+        <v>46234.39538194444</v>
       </c>
       <c r="R899" t="n">
         <v>4.8</v>
@@ -53724,12 +53720,12 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>user6878452250754</t>
+          <t>user6737190678194</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6878452250754</t>
+          <t>https://www.tiktok.com/@user6737190678194</t>
         </is>
       </c>
       <c r="C900" t="inlineStr"/>
@@ -53738,7 +53734,11 @@
       <c r="F900" t="inlineStr"/>
       <c r="G900" t="inlineStr"/>
       <c r="H900" t="inlineStr"/>
-      <c r="I900" t="inlineStr"/>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J900" t="inlineStr"/>
       <c r="K900" t="inlineStr"/>
       <c r="L900" t="inlineStr"/>
@@ -53747,22 +53747,22 @@
       </c>
       <c r="N900" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O900" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P900" s="1" t="n">
-        <v>46255.7966087963</v>
+        <v>46222.63238425926</v>
       </c>
       <c r="Q900" s="1" t="n">
-        <v>46255.7966087963</v>
+        <v>46222.63238425926</v>
       </c>
       <c r="R900" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S900" t="inlineStr">
         <is>
@@ -53779,12 +53779,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>user6892760169821</t>
+          <t>user6878452250754</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6892760169821</t>
+          <t>https://www.tiktok.com/@user6878452250754</t>
         </is>
       </c>
       <c r="C901" t="inlineStr"/>
@@ -53793,11 +53793,7 @@
       <c r="F901" t="inlineStr"/>
       <c r="G901" t="inlineStr"/>
       <c r="H901" t="inlineStr"/>
-      <c r="I901" t="inlineStr">
-        <is>
-          <t>South Asian</t>
-        </is>
-      </c>
+      <c r="I901" t="inlineStr"/>
       <c r="J901" t="inlineStr"/>
       <c r="K901" t="inlineStr"/>
       <c r="L901" t="inlineStr"/>
@@ -53806,22 +53802,22 @@
       </c>
       <c r="N901" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O901" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P901" s="1" t="n">
-        <v>46208.68979166666</v>
+        <v>46255.7966087963</v>
       </c>
       <c r="Q901" s="1" t="n">
-        <v>46208.68979166666</v>
+        <v>46255.7966087963</v>
       </c>
       <c r="R901" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S901" t="inlineStr">
         <is>
@@ -53838,12 +53834,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>user6962927106649</t>
+          <t>user6892760169821</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6962927106649</t>
+          <t>https://www.tiktok.com/@user6892760169821</t>
         </is>
       </c>
       <c r="C902" t="inlineStr"/>
@@ -53854,7 +53850,7 @@
       <c r="H902" t="inlineStr"/>
       <c r="I902" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J902" t="inlineStr"/>
@@ -53874,10 +53870,10 @@
         </is>
       </c>
       <c r="P902" s="1" t="n">
-        <v>46220.98945601852</v>
+        <v>46208.68979166666</v>
       </c>
       <c r="Q902" s="1" t="n">
-        <v>46220.98945601852</v>
+        <v>46208.68979166666</v>
       </c>
       <c r="R902" t="n">
         <v>4.8</v>
@@ -53897,12 +53893,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>user7232137600814</t>
+          <t>user6962927106649</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7232137600814</t>
+          <t>https://www.tiktok.com/@user6962927106649</t>
         </is>
       </c>
       <c r="C903" t="inlineStr"/>
@@ -53913,7 +53909,7 @@
       <c r="H903" t="inlineStr"/>
       <c r="I903" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J903" t="inlineStr"/>
@@ -53933,10 +53929,10 @@
         </is>
       </c>
       <c r="P903" s="1" t="n">
-        <v>46216.11149305556</v>
+        <v>46220.98945601852</v>
       </c>
       <c r="Q903" s="1" t="n">
-        <v>46216.11149305556</v>
+        <v>46220.98945601852</v>
       </c>
       <c r="R903" t="n">
         <v>4.8</v>
@@ -53956,12 +53952,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>user7411816032779</t>
+          <t>user7232137600814</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7411816032779</t>
+          <t>https://www.tiktok.com/@user7232137600814</t>
         </is>
       </c>
       <c r="C904" t="inlineStr"/>
@@ -53972,7 +53968,7 @@
       <c r="H904" t="inlineStr"/>
       <c r="I904" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J904" t="inlineStr"/>
@@ -53992,10 +53988,10 @@
         </is>
       </c>
       <c r="P904" s="1" t="n">
-        <v>46231.93748842592</v>
+        <v>46216.11149305556</v>
       </c>
       <c r="Q904" s="1" t="n">
-        <v>46231.93748842592</v>
+        <v>46216.11149305556</v>
       </c>
       <c r="R904" t="n">
         <v>4.8</v>
@@ -54015,12 +54011,12 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>user7888882185294</t>
+          <t>user7411816032779</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7888882185294</t>
+          <t>https://www.tiktok.com/@user7411816032779</t>
         </is>
       </c>
       <c r="C905" t="inlineStr"/>
@@ -54051,10 +54047,10 @@
         </is>
       </c>
       <c r="P905" s="1" t="n">
-        <v>46217.0528587963</v>
+        <v>46231.93748842592</v>
       </c>
       <c r="Q905" s="1" t="n">
-        <v>46217.0528587963</v>
+        <v>46231.93748842592</v>
       </c>
       <c r="R905" t="n">
         <v>4.8</v>
@@ -54074,12 +54070,12 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>user8008669545474</t>
+          <t>user7888882185294</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8008669545474</t>
+          <t>https://www.tiktok.com/@user7888882185294</t>
         </is>
       </c>
       <c r="C906" t="inlineStr"/>
@@ -54101,22 +54097,22 @@
       </c>
       <c r="N906" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O906" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P906" s="1" t="n">
-        <v>45981.84152777777</v>
+        <v>46217.0528587963</v>
       </c>
       <c r="Q906" s="1" t="n">
-        <v>45981.84152777777</v>
+        <v>46217.0528587963</v>
       </c>
       <c r="R906" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="S906" t="inlineStr">
         <is>
@@ -54133,12 +54129,12 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>user8134650348013</t>
+          <t>user8008669545474</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8134650348013</t>
+          <t>https://www.tiktok.com/@user8008669545474</t>
         </is>
       </c>
       <c r="C907" t="inlineStr"/>
@@ -54160,22 +54156,22 @@
       </c>
       <c r="N907" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O907" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P907" s="1" t="n">
-        <v>46217.49246527778</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="Q907" s="1" t="n">
-        <v>46217.49246527778</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="R907" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S907" t="inlineStr">
         <is>
@@ -54192,12 +54188,12 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>user8234558006158</t>
+          <t>user8134650348013</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8234558006158</t>
+          <t>https://www.tiktok.com/@user8134650348013</t>
         </is>
       </c>
       <c r="C908" t="inlineStr"/>
@@ -54208,7 +54204,7 @@
       <c r="H908" t="inlineStr"/>
       <c r="I908" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J908" t="inlineStr"/>
@@ -54219,22 +54215,22 @@
       </c>
       <c r="N908" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O908" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P908" s="1" t="n">
-        <v>46246.30070601852</v>
+        <v>46217.49246527778</v>
       </c>
       <c r="Q908" s="1" t="n">
-        <v>46246.30070601852</v>
+        <v>46217.49246527778</v>
       </c>
       <c r="R908" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S908" t="inlineStr">
         <is>
@@ -54251,12 +54247,12 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>user8376211816358</t>
+          <t>user8234558006158</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8376211816358</t>
+          <t>https://www.tiktok.com/@user8234558006158</t>
         </is>
       </c>
       <c r="C909" t="inlineStr"/>
@@ -54278,22 +54274,22 @@
       </c>
       <c r="N909" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O909" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P909" s="1" t="n">
-        <v>46219.42800925926</v>
+        <v>46246.30070601852</v>
       </c>
       <c r="Q909" s="1" t="n">
-        <v>46219.42800925926</v>
+        <v>46246.30070601852</v>
       </c>
       <c r="R909" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S909" t="inlineStr">
         <is>
@@ -54310,12 +54306,12 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>user8387816340732</t>
+          <t>user8376211816358</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8387816340732</t>
+          <t>https://www.tiktok.com/@user8376211816358</t>
         </is>
       </c>
       <c r="C910" t="inlineStr"/>
@@ -54346,10 +54342,10 @@
         </is>
       </c>
       <c r="P910" s="1" t="n">
-        <v>46231.80520833333</v>
+        <v>46219.42800925926</v>
       </c>
       <c r="Q910" s="1" t="n">
-        <v>46231.80520833333</v>
+        <v>46219.42800925926</v>
       </c>
       <c r="R910" t="n">
         <v>4.8</v>
@@ -54369,12 +54365,12 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>user866w5p9rl9</t>
+          <t>user8387816340732</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user866w5p9rl9</t>
+          <t>https://www.tiktok.com/@user8387816340732</t>
         </is>
       </c>
       <c r="C911" t="inlineStr"/>
@@ -54385,7 +54381,7 @@
       <c r="H911" t="inlineStr"/>
       <c r="I911" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J911" t="inlineStr"/>
@@ -54396,22 +54392,22 @@
       </c>
       <c r="N911" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O911" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P911" s="1" t="n">
-        <v>46053.63612268519</v>
+        <v>46231.80520833333</v>
       </c>
       <c r="Q911" s="1" t="n">
-        <v>46053.63612268519</v>
+        <v>46231.80520833333</v>
       </c>
       <c r="R911" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S911" t="inlineStr">
         <is>
@@ -54428,12 +54424,12 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>user88181884284463</t>
+          <t>user866w5p9rl9</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user88181884284463</t>
+          <t>https://www.tiktok.com/@user866w5p9rl9</t>
         </is>
       </c>
       <c r="C912" t="inlineStr"/>
@@ -54455,22 +54451,22 @@
       </c>
       <c r="N912" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O912" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P912" s="1" t="n">
-        <v>46210.45086805556</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="Q912" s="1" t="n">
-        <v>46210.45086805556</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="R912" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S912" t="inlineStr">
         <is>
@@ -54487,12 +54483,12 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>user9090397839153</t>
+          <t>user88181884284463</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9090397839153</t>
+          <t>https://www.tiktok.com/@user88181884284463</t>
         </is>
       </c>
       <c r="C913" t="inlineStr"/>
@@ -54523,10 +54519,10 @@
         </is>
       </c>
       <c r="P913" s="1" t="n">
-        <v>46208.69571759259</v>
+        <v>46210.45086805556</v>
       </c>
       <c r="Q913" s="1" t="n">
-        <v>46208.69571759259</v>
+        <v>46210.45086805556</v>
       </c>
       <c r="R913" t="n">
         <v>4.8</v>
@@ -54546,12 +54542,12 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>user9578635552261</t>
+          <t>user9090397839153</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9578635552261</t>
+          <t>https://www.tiktok.com/@user9090397839153</t>
         </is>
       </c>
       <c r="C914" t="inlineStr"/>
@@ -54560,7 +54556,11 @@
       <c r="F914" t="inlineStr"/>
       <c r="G914" t="inlineStr"/>
       <c r="H914" t="inlineStr"/>
-      <c r="I914" t="inlineStr"/>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J914" t="inlineStr"/>
       <c r="K914" t="inlineStr"/>
       <c r="L914" t="inlineStr"/>
@@ -54569,22 +54569,22 @@
       </c>
       <c r="N914" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O914" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P914" s="1" t="n">
-        <v>46253.96681712963</v>
+        <v>46208.69571759259</v>
       </c>
       <c r="Q914" s="1" t="n">
-        <v>46253.96681712963</v>
+        <v>46208.69571759259</v>
       </c>
       <c r="R914" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S914" t="inlineStr">
         <is>
@@ -54601,12 +54601,12 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>user9760096301617</t>
+          <t>user9578635552261</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9760096301617</t>
+          <t>https://www.tiktok.com/@user9578635552261</t>
         </is>
       </c>
       <c r="C915" t="inlineStr"/>
@@ -54615,11 +54615,7 @@
       <c r="F915" t="inlineStr"/>
       <c r="G915" t="inlineStr"/>
       <c r="H915" t="inlineStr"/>
-      <c r="I915" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
+      <c r="I915" t="inlineStr"/>
       <c r="J915" t="inlineStr"/>
       <c r="K915" t="inlineStr"/>
       <c r="L915" t="inlineStr"/>
@@ -54628,22 +54624,22 @@
       </c>
       <c r="N915" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O915" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P915" s="1" t="n">
-        <v>46227.566875</v>
+        <v>46253.96681712963</v>
       </c>
       <c r="Q915" s="1" t="n">
-        <v>46227.566875</v>
+        <v>46253.96681712963</v>
       </c>
       <c r="R915" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S915" t="inlineStr">
         <is>
@@ -54660,12 +54656,12 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>user9813841001322</t>
+          <t>user9760096301617</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9813841001322</t>
+          <t>https://www.tiktok.com/@user9760096301617</t>
         </is>
       </c>
       <c r="C916" t="inlineStr"/>
@@ -54676,7 +54672,7 @@
       <c r="H916" t="inlineStr"/>
       <c r="I916" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J916" t="inlineStr"/>
@@ -54696,10 +54692,10 @@
         </is>
       </c>
       <c r="P916" s="1" t="n">
-        <v>46236.99202546296</v>
+        <v>46227.566875</v>
       </c>
       <c r="Q916" s="1" t="n">
-        <v>46236.99202546296</v>
+        <v>46227.566875</v>
       </c>
       <c r="R916" t="n">
         <v>4.8</v>
@@ -54719,12 +54715,12 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>user_steeze</t>
+          <t>user9813841001322</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_steeze</t>
+          <t>https://www.tiktok.com/@user9813841001322</t>
         </is>
       </c>
       <c r="C917" t="inlineStr"/>
@@ -54733,7 +54729,11 @@
       <c r="F917" t="inlineStr"/>
       <c r="G917" t="inlineStr"/>
       <c r="H917" t="inlineStr"/>
-      <c r="I917" t="inlineStr"/>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J917" t="inlineStr"/>
       <c r="K917" t="inlineStr"/>
       <c r="L917" t="inlineStr"/>
@@ -54742,7 +54742,7 @@
       </c>
       <c r="N917" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O917" t="inlineStr">
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="P917" s="1" t="n">
-        <v>46264.74940972222</v>
+        <v>46236.99202546296</v>
       </c>
       <c r="Q917" s="1" t="n">
-        <v>46264.74940972222</v>
+        <v>46236.99202546296</v>
       </c>
       <c r="R917" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S917" t="inlineStr">
         <is>
@@ -54774,12 +54774,12 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>usernamelarchinoo</t>
+          <t>user_steeze</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@usernamelarchinoo</t>
+          <t>https://www.tiktok.com/@user_steeze</t>
         </is>
       </c>
       <c r="C918" t="inlineStr"/>
@@ -54788,11 +54788,7 @@
       <c r="F918" t="inlineStr"/>
       <c r="G918" t="inlineStr"/>
       <c r="H918" t="inlineStr"/>
-      <c r="I918" t="inlineStr">
-        <is>
-          <t>Middle Eastern/Arab</t>
-        </is>
-      </c>
+      <c r="I918" t="inlineStr"/>
       <c r="J918" t="inlineStr"/>
       <c r="K918" t="inlineStr"/>
       <c r="L918" t="inlineStr"/>
@@ -54801,7 +54797,7 @@
       </c>
       <c r="N918" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O918" t="inlineStr">
@@ -54810,13 +54806,13 @@
         </is>
       </c>
       <c r="P918" s="1" t="n">
-        <v>46209.84040509259</v>
+        <v>46264.74940972222</v>
       </c>
       <c r="Q918" s="1" t="n">
-        <v>46209.84040509259</v>
+        <v>46264.74940972222</v>
       </c>
       <c r="R918" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S918" t="inlineStr">
         <is>
@@ -54833,12 +54829,12 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>userparidil008</t>
+          <t>usernamelarchinoo</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@userparidil008</t>
+          <t>https://www.tiktok.com/@usernamelarchinoo</t>
         </is>
       </c>
       <c r="C919" t="inlineStr"/>
@@ -54847,7 +54843,11 @@
       <c r="F919" t="inlineStr"/>
       <c r="G919" t="inlineStr"/>
       <c r="H919" t="inlineStr"/>
-      <c r="I919" t="inlineStr"/>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J919" t="inlineStr"/>
       <c r="K919" t="inlineStr"/>
       <c r="L919" t="inlineStr"/>
@@ -54856,22 +54856,22 @@
       </c>
       <c r="N919" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O919" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P919" s="1" t="n">
-        <v>46252.75293981482</v>
+        <v>46209.84040509259</v>
       </c>
       <c r="Q919" s="1" t="n">
-        <v>46252.75293981482</v>
+        <v>46209.84040509259</v>
       </c>
       <c r="R919" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S919" t="inlineStr">
         <is>
@@ -54888,12 +54888,12 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>uyi_guobadia1976</t>
+          <t>userparidil008</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uyi_guobadia1976</t>
+          <t>https://www.tiktok.com/@userparidil008</t>
         </is>
       </c>
       <c r="C920" t="inlineStr"/>
@@ -54902,11 +54902,7 @@
       <c r="F920" t="inlineStr"/>
       <c r="G920" t="inlineStr"/>
       <c r="H920" t="inlineStr"/>
-      <c r="I920" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I920" t="inlineStr"/>
       <c r="J920" t="inlineStr"/>
       <c r="K920" t="inlineStr"/>
       <c r="L920" t="inlineStr"/>
@@ -54915,22 +54911,22 @@
       </c>
       <c r="N920" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O920" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P920" s="1" t="n">
-        <v>46229.67628472222</v>
+        <v>46252.75293981482</v>
       </c>
       <c r="Q920" s="1" t="n">
-        <v>46229.67628472222</v>
+        <v>46252.75293981482</v>
       </c>
       <c r="R920" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S920" t="inlineStr">
         <is>
@@ -54947,12 +54943,12 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>vanfoxhamah</t>
+          <t>uyi_guobadia1976</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vanfoxhamah</t>
+          <t>https://www.tiktok.com/@uyi_guobadia1976</t>
         </is>
       </c>
       <c r="C921" t="inlineStr"/>
@@ -54983,10 +54979,10 @@
         </is>
       </c>
       <c r="P921" s="1" t="n">
-        <v>46223.24950231481</v>
+        <v>46229.67628472222</v>
       </c>
       <c r="Q921" s="1" t="n">
-        <v>46223.24950231481</v>
+        <v>46229.67628472222</v>
       </c>
       <c r="R921" t="n">
         <v>4.8</v>
@@ -55006,12 +55002,12 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>vickyvickss3</t>
+          <t>vanfoxhamah</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vickyvickss3</t>
+          <t>https://www.tiktok.com/@vanfoxhamah</t>
         </is>
       </c>
       <c r="C922" t="inlineStr"/>
@@ -55033,22 +55029,22 @@
       </c>
       <c r="N922" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O922" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P922" s="1" t="n">
-        <v>46245.73690972223</v>
+        <v>46223.24950231481</v>
       </c>
       <c r="Q922" s="1" t="n">
-        <v>46245.73690972223</v>
+        <v>46223.24950231481</v>
       </c>
       <c r="R922" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S922" t="inlineStr">
         <is>
@@ -55065,12 +55061,12 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>victoriaookoro</t>
+          <t>vickyvickss3</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@victoriaookoro</t>
+          <t>https://www.tiktok.com/@vickyvickss3</t>
         </is>
       </c>
       <c r="C923" t="inlineStr"/>
@@ -55092,22 +55088,22 @@
       </c>
       <c r="N923" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O923" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P923" s="1" t="n">
-        <v>46235.32452546297</v>
+        <v>46245.73690972223</v>
       </c>
       <c r="Q923" s="1" t="n">
-        <v>46235.32452546297</v>
+        <v>46245.73690972223</v>
       </c>
       <c r="R923" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S923" t="inlineStr">
         <is>
@@ -55124,12 +55120,12 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>virginglo</t>
+          <t>victoriaookoro</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@virginglo</t>
+          <t>https://www.tiktok.com/@victoriaookoro</t>
         </is>
       </c>
       <c r="C924" t="inlineStr"/>
@@ -55160,10 +55156,10 @@
         </is>
       </c>
       <c r="P924" s="1" t="n">
-        <v>46209.88831018518</v>
+        <v>46235.32452546297</v>
       </c>
       <c r="Q924" s="1" t="n">
-        <v>46209.88831018518</v>
+        <v>46235.32452546297</v>
       </c>
       <c r="R924" t="n">
         <v>4.8</v>
@@ -55183,12 +55179,12 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>vision.rift</t>
+          <t>virginglo</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vision.rift</t>
+          <t>https://www.tiktok.com/@virginglo</t>
         </is>
       </c>
       <c r="C925" t="inlineStr"/>
@@ -55210,22 +55206,22 @@
       </c>
       <c r="N925" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O925" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P925" s="1" t="n">
-        <v>45965.5908449074</v>
+        <v>46209.88831018518</v>
       </c>
       <c r="Q925" s="1" t="n">
-        <v>45965.5908449074</v>
+        <v>46209.88831018518</v>
       </c>
       <c r="R925" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S925" t="inlineStr">
         <is>
@@ -55242,12 +55238,12 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>vivian.shobogun.backup</t>
+          <t>vision.rift</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vivian.shobogun.backup</t>
+          <t>https://www.tiktok.com/@vision.rift</t>
         </is>
       </c>
       <c r="C926" t="inlineStr"/>
@@ -55269,22 +55265,22 @@
       </c>
       <c r="N926" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O926" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P926" s="1" t="n">
-        <v>46222.26184027778</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="Q926" s="1" t="n">
-        <v>46222.26184027778</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="R926" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S926" t="inlineStr">
         <is>
@@ -55301,12 +55297,12 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>vivianokeke98</t>
+          <t>vivian.shobogun.backup</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vivianokeke98</t>
+          <t>https://www.tiktok.com/@vivian.shobogun.backup</t>
         </is>
       </c>
       <c r="C927" t="inlineStr"/>
@@ -55337,10 +55333,10 @@
         </is>
       </c>
       <c r="P927" s="1" t="n">
-        <v>46232.40989583333</v>
+        <v>46222.26184027778</v>
       </c>
       <c r="Q927" s="1" t="n">
-        <v>46232.40989583333</v>
+        <v>46222.26184027778</v>
       </c>
       <c r="R927" t="n">
         <v>4.8</v>
@@ -55360,12 +55356,12 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>vytyglrl</t>
+          <t>vivianokeke98</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vytyglrl</t>
+          <t>https://www.tiktok.com/@vivianokeke98</t>
         </is>
       </c>
       <c r="C928" t="inlineStr"/>
@@ -55376,7 +55372,7 @@
       <c r="H928" t="inlineStr"/>
       <c r="I928" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J928" t="inlineStr"/>
@@ -55387,7 +55383,7 @@
       </c>
       <c r="N928" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O928" t="inlineStr">
@@ -55396,13 +55392,13 @@
         </is>
       </c>
       <c r="P928" s="1" t="n">
-        <v>46235.07810185185</v>
+        <v>46232.40989583333</v>
       </c>
       <c r="Q928" s="1" t="n">
-        <v>46235.07810185185</v>
+        <v>46232.40989583333</v>
       </c>
       <c r="R928" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S928" t="inlineStr">
         <is>
@@ -55419,12 +55415,12 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>waletreasure</t>
+          <t>vytyglrl</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waletreasure</t>
+          <t>https://www.tiktok.com/@vytyglrl</t>
         </is>
       </c>
       <c r="C929" t="inlineStr"/>
@@ -55435,7 +55431,7 @@
       <c r="H929" t="inlineStr"/>
       <c r="I929" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J929" t="inlineStr"/>
@@ -55446,7 +55442,7 @@
       </c>
       <c r="N929" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O929" t="inlineStr">
@@ -55455,13 +55451,13 @@
         </is>
       </c>
       <c r="P929" s="1" t="n">
-        <v>46245.54293981481</v>
+        <v>46235.07810185185</v>
       </c>
       <c r="Q929" s="1" t="n">
-        <v>46245.54293981481</v>
+        <v>46235.07810185185</v>
       </c>
       <c r="R929" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="S929" t="inlineStr">
         <is>
@@ -55478,12 +55474,12 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>walex0880</t>
+          <t>waletreasure</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@walex0880</t>
+          <t>https://www.tiktok.com/@waletreasure</t>
         </is>
       </c>
       <c r="C930" t="inlineStr"/>
@@ -55505,7 +55501,7 @@
       </c>
       <c r="N930" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O930" t="inlineStr">
@@ -55514,13 +55510,13 @@
         </is>
       </c>
       <c r="P930" s="1" t="n">
-        <v>46238.89991898148</v>
+        <v>46245.54293981481</v>
       </c>
       <c r="Q930" s="1" t="n">
-        <v>46238.89991898148</v>
+        <v>46245.54293981481</v>
       </c>
       <c r="R930" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S930" t="inlineStr">
         <is>
@@ -55537,12 +55533,12 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>wankycandle</t>
+          <t>walex0880</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wankycandle</t>
+          <t>https://www.tiktok.com/@walex0880</t>
         </is>
       </c>
       <c r="C931" t="inlineStr"/>
@@ -55553,7 +55549,7 @@
       <c r="H931" t="inlineStr"/>
       <c r="I931" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J931" t="inlineStr"/>
@@ -55564,22 +55560,22 @@
       </c>
       <c r="N931" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O931" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P931" s="1" t="n">
-        <v>46206.37778935185</v>
+        <v>46238.89991898148</v>
       </c>
       <c r="Q931" s="1" t="n">
-        <v>46206.37778935185</v>
+        <v>46238.89991898148</v>
       </c>
       <c r="R931" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S931" t="inlineStr">
         <is>
@@ -55596,12 +55592,12 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>waq78690</t>
+          <t>wankycandle</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waq78690</t>
+          <t>https://www.tiktok.com/@wankycandle</t>
         </is>
       </c>
       <c r="C932" t="inlineStr"/>
@@ -55612,7 +55608,7 @@
       <c r="H932" t="inlineStr"/>
       <c r="I932" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J932" t="inlineStr"/>
@@ -55632,10 +55628,10 @@
         </is>
       </c>
       <c r="P932" s="1" t="n">
-        <v>46220.91548611111</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="Q932" s="1" t="n">
-        <v>46220.91548611111</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="R932" t="n">
         <v>6</v>
@@ -55655,12 +55651,12 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>wassava4</t>
+          <t>waq78690</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wassava4</t>
+          <t>https://www.tiktok.com/@waq78690</t>
         </is>
       </c>
       <c r="C933" t="inlineStr"/>
@@ -55671,7 +55667,7 @@
       <c r="H933" t="inlineStr"/>
       <c r="I933" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J933" t="inlineStr"/>
@@ -55682,22 +55678,22 @@
       </c>
       <c r="N933" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O933" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P933" s="1" t="n">
-        <v>46221.72733796296</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="Q933" s="1" t="n">
-        <v>46221.72733796296</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="R933" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S933" t="inlineStr">
         <is>
@@ -55714,12 +55710,12 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>waxtee0</t>
+          <t>wassava4</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waxtee0</t>
+          <t>https://www.tiktok.com/@wassava4</t>
         </is>
       </c>
       <c r="C934" t="inlineStr"/>
@@ -55730,7 +55726,7 @@
       <c r="H934" t="inlineStr"/>
       <c r="I934" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J934" t="inlineStr"/>
@@ -55750,10 +55746,10 @@
         </is>
       </c>
       <c r="P934" s="1" t="n">
-        <v>46230.38460648148</v>
+        <v>46221.72733796296</v>
       </c>
       <c r="Q934" s="1" t="n">
-        <v>46230.38460648148</v>
+        <v>46221.72733796296</v>
       </c>
       <c r="R934" t="n">
         <v>4.8</v>
@@ -55773,12 +55769,12 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>wealth2869</t>
+          <t>waxtee0</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wealth2869</t>
+          <t>https://www.tiktok.com/@waxtee0</t>
         </is>
       </c>
       <c r="C935" t="inlineStr"/>
@@ -55789,7 +55785,7 @@
       <c r="H935" t="inlineStr"/>
       <c r="I935" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J935" t="inlineStr"/>
@@ -55809,10 +55805,10 @@
         </is>
       </c>
       <c r="P935" s="1" t="n">
-        <v>46222.32829861111</v>
+        <v>46230.38460648148</v>
       </c>
       <c r="Q935" s="1" t="n">
-        <v>46222.32829861111</v>
+        <v>46230.38460648148</v>
       </c>
       <c r="R935" t="n">
         <v>4.8</v>
@@ -55832,12 +55828,12 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>wellnesswithuzo</t>
+          <t>wealth2869</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wellnesswithuzo</t>
+          <t>https://www.tiktok.com/@wealth2869</t>
         </is>
       </c>
       <c r="C936" t="inlineStr"/>
@@ -55859,22 +55855,22 @@
       </c>
       <c r="N936" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O936" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P936" s="1" t="n">
-        <v>46258.28196759259</v>
+        <v>46222.32829861111</v>
       </c>
       <c r="Q936" s="1" t="n">
-        <v>46258.28196759259</v>
+        <v>46222.32829861111</v>
       </c>
       <c r="R936" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S936" t="inlineStr">
         <is>
@@ -55891,12 +55887,12 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>wendykhan19</t>
+          <t>wellnesswithuzo</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wendykhan19</t>
+          <t>https://www.tiktok.com/@wellnesswithuzo</t>
         </is>
       </c>
       <c r="C937" t="inlineStr"/>
@@ -55907,7 +55903,7 @@
       <c r="H937" t="inlineStr"/>
       <c r="I937" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J937" t="inlineStr"/>
@@ -55918,22 +55914,22 @@
       </c>
       <c r="N937" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O937" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P937" s="1" t="n">
-        <v>46213.43940972222</v>
+        <v>46258.28196759259</v>
       </c>
       <c r="Q937" s="1" t="n">
-        <v>46213.43940972222</v>
+        <v>46258.28196759259</v>
       </c>
       <c r="R937" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S937" t="inlineStr">
         <is>
@@ -55950,12 +55946,12 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>whatdoes09</t>
+          <t>wendykhan19</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@whatdoes09</t>
+          <t>https://www.tiktok.com/@wendykhan19</t>
         </is>
       </c>
       <c r="C938" t="inlineStr"/>
@@ -55966,7 +55962,7 @@
       <c r="H938" t="inlineStr"/>
       <c r="I938" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J938" t="inlineStr"/>
@@ -55986,10 +55982,10 @@
         </is>
       </c>
       <c r="P938" s="1" t="n">
-        <v>46224.32761574074</v>
+        <v>46213.43940972222</v>
       </c>
       <c r="Q938" s="1" t="n">
-        <v>46224.32761574074</v>
+        <v>46213.43940972222</v>
       </c>
       <c r="R938" t="n">
         <v>4.8</v>
@@ -56009,12 +56005,12 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>whoisedwina.x</t>
+          <t>whatdoes09</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@whoisedwina.x</t>
+          <t>https://www.tiktok.com/@whatdoes09</t>
         </is>
       </c>
       <c r="C939" t="inlineStr"/>
@@ -56025,7 +56021,7 @@
       <c r="H939" t="inlineStr"/>
       <c r="I939" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J939" t="inlineStr"/>
@@ -56045,10 +56041,10 @@
         </is>
       </c>
       <c r="P939" s="1" t="n">
-        <v>46238.83828703704</v>
+        <v>46224.32761574074</v>
       </c>
       <c r="Q939" s="1" t="n">
-        <v>46238.83828703704</v>
+        <v>46224.32761574074</v>
       </c>
       <c r="R939" t="n">
         <v>4.8</v>
@@ -56068,12 +56064,12 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>williams.olumide5</t>
+          <t>whoisedwina.x</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@williams.olumide5</t>
+          <t>https://www.tiktok.com/@whoisedwina.x</t>
         </is>
       </c>
       <c r="C940" t="inlineStr"/>
@@ -56104,10 +56100,10 @@
         </is>
       </c>
       <c r="P940" s="1" t="n">
-        <v>46208.69674768519</v>
+        <v>46238.83828703704</v>
       </c>
       <c r="Q940" s="1" t="n">
-        <v>46208.69674768519</v>
+        <v>46238.83828703704</v>
       </c>
       <c r="R940" t="n">
         <v>4.8</v>
@@ -56127,12 +56123,12 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>willow_mama23</t>
+          <t>williams.olumide5</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@willow_mama23</t>
+          <t>https://www.tiktok.com/@williams.olumide5</t>
         </is>
       </c>
       <c r="C941" t="inlineStr"/>
@@ -56143,7 +56139,7 @@
       <c r="H941" t="inlineStr"/>
       <c r="I941" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J941" t="inlineStr"/>
@@ -56154,7 +56150,7 @@
       </c>
       <c r="N941" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O941" t="inlineStr">
@@ -56163,13 +56159,13 @@
         </is>
       </c>
       <c r="P941" s="1" t="n">
-        <v>46250.84450231482</v>
+        <v>46208.69674768519</v>
       </c>
       <c r="Q941" s="1" t="n">
-        <v>46250.84450231482</v>
+        <v>46208.69674768519</v>
       </c>
       <c r="R941" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S941" t="inlineStr">
         <is>
@@ -56186,12 +56182,12 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>womeninspiration5</t>
+          <t>willow_mama23</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@womeninspiration5</t>
+          <t>https://www.tiktok.com/@willow_mama23</t>
         </is>
       </c>
       <c r="C942" t="inlineStr"/>
@@ -56202,7 +56198,7 @@
       <c r="H942" t="inlineStr"/>
       <c r="I942" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J942" t="inlineStr"/>
@@ -56218,17 +56214,17 @@
       </c>
       <c r="O942" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P942" s="1" t="n">
-        <v>45939.98240740741</v>
+        <v>46250.84450231482</v>
       </c>
       <c r="Q942" s="1" t="n">
-        <v>45939.98240740741</v>
+        <v>46250.84450231482</v>
       </c>
       <c r="R942" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="S942" t="inlineStr">
         <is>
@@ -56245,12 +56241,12 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>worldbestkaffy</t>
+          <t>womeninspiration5</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@worldbestkaffy</t>
+          <t>https://www.tiktok.com/@womeninspiration5</t>
         </is>
       </c>
       <c r="C943" t="inlineStr"/>
@@ -56259,7 +56255,11 @@
       <c r="F943" t="inlineStr"/>
       <c r="G943" t="inlineStr"/>
       <c r="H943" t="inlineStr"/>
-      <c r="I943" t="inlineStr"/>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J943" t="inlineStr"/>
       <c r="K943" t="inlineStr"/>
       <c r="L943" t="inlineStr"/>
@@ -56268,7 +56268,7 @@
       </c>
       <c r="N943" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O943" t="inlineStr">
@@ -56277,13 +56277,13 @@
         </is>
       </c>
       <c r="P943" s="1" t="n">
-        <v>46253.76657407408</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="Q943" s="1" t="n">
-        <v>46253.76657407408</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="R943" t="n">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S943" t="inlineStr">
         <is>
@@ -56300,12 +56300,12 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>xheyitsbeccax</t>
+          <t>worldbestkaffy</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xheyitsbeccax</t>
+          <t>https://www.tiktok.com/@worldbestkaffy</t>
         </is>
       </c>
       <c r="C944" t="inlineStr"/>
@@ -56314,35 +56314,31 @@
       <c r="F944" t="inlineStr"/>
       <c r="G944" t="inlineStr"/>
       <c r="H944" t="inlineStr"/>
-      <c r="I944" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
+      <c r="I944" t="inlineStr"/>
       <c r="J944" t="inlineStr"/>
       <c r="K944" t="inlineStr"/>
       <c r="L944" t="inlineStr"/>
       <c r="M944" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N944" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Other</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O944" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT), seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P944" s="1" t="n">
-        <v>46250.04033564815</v>
+        <v>46253.76657407408</v>
       </c>
       <c r="Q944" s="1" t="n">
-        <v>46250.04033564815</v>
+        <v>46253.76657407408</v>
       </c>
       <c r="R944" t="n">
-        <v>11.9</v>
+        <v>5.9</v>
       </c>
       <c r="S944" t="inlineStr">
         <is>
@@ -56359,12 +56355,12 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>xhollycolhounx</t>
+          <t>xheyitsbeccax</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xhollycolhounx</t>
+          <t>https://www.tiktok.com/@xheyitsbeccax</t>
         </is>
       </c>
       <c r="C945" t="inlineStr"/>
@@ -56382,26 +56378,26 @@
       <c r="K945" t="inlineStr"/>
       <c r="L945" t="inlineStr"/>
       <c r="M945" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N945" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O945" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P945" s="1" t="n">
-        <v>46198.62712962963</v>
+        <v>46250.04033564815</v>
       </c>
       <c r="Q945" s="1" t="n">
-        <v>46198.62712962963</v>
+        <v>46250.04033564815</v>
       </c>
       <c r="R945" t="n">
-        <v>6</v>
+        <v>11.9</v>
       </c>
       <c r="S945" t="inlineStr">
         <is>
@@ -56418,12 +56414,12 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>xstarharry</t>
+          <t>xhollycolhounx</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xstarharry</t>
+          <t>https://www.tiktok.com/@xhollycolhounx</t>
         </is>
       </c>
       <c r="C946" t="inlineStr"/>
@@ -56434,7 +56430,7 @@
       <c r="H946" t="inlineStr"/>
       <c r="I946" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J946" t="inlineStr"/>
@@ -56445,22 +56441,22 @@
       </c>
       <c r="N946" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O946" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P946" s="1" t="n">
-        <v>46219.35070601852</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q946" s="1" t="n">
-        <v>46219.35070601852</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R946" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S946" t="inlineStr">
         <is>
@@ -56477,12 +56473,12 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>y_ddraig69</t>
+          <t>xstarharry</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@y_ddraig69</t>
+          <t>https://www.tiktok.com/@xstarharry</t>
         </is>
       </c>
       <c r="C947" t="inlineStr"/>
@@ -56493,67 +56489,55 @@
       <c r="H947" t="inlineStr"/>
       <c r="I947" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J947" t="inlineStr"/>
       <c r="K947" t="inlineStr"/>
       <c r="L947" t="inlineStr"/>
       <c r="M947" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N947" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O947" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT), seller</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P947" s="1" t="n">
-        <v>46249.74936342592</v>
+        <v>46219.35070601852</v>
       </c>
       <c r="Q947" s="1" t="n">
-        <v>46249.749375</v>
+        <v>46219.35070601852</v>
       </c>
       <c r="R947" t="n">
-        <v>11.9</v>
+        <v>4.8</v>
       </c>
       <c r="S947" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T947" t="n">
-        <v>2</v>
-      </c>
-      <c r="U947" t="n">
-        <v>0</v>
-      </c>
-      <c r="V947" t="n">
-        <v>0</v>
-      </c>
-      <c r="W947" t="n">
-        <v>7</v>
-      </c>
-      <c r="X947" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="Y947" t="n">
-        <v>4</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T947" t="inlineStr"/>
+      <c r="U947" t="inlineStr"/>
+      <c r="V947" t="inlineStr"/>
+      <c r="W947" t="inlineStr"/>
+      <c r="X947" t="inlineStr"/>
+      <c r="Y947" t="inlineStr"/>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>yahwehshaven</t>
+          <t>y_ddraig69</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yahwehshaven</t>
+          <t>https://www.tiktok.com/@y_ddraig69</t>
         </is>
       </c>
       <c r="C948" t="inlineStr"/>
@@ -56564,55 +56548,67 @@
       <c r="H948" t="inlineStr"/>
       <c r="I948" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J948" t="inlineStr"/>
       <c r="K948" t="inlineStr"/>
       <c r="L948" t="inlineStr"/>
       <c r="M948" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N948" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O948" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P948" s="1" t="n">
-        <v>46228.34030092593</v>
+        <v>46249.74936342592</v>
       </c>
       <c r="Q948" s="1" t="n">
-        <v>46228.34030092593</v>
+        <v>46249.749375</v>
       </c>
       <c r="R948" t="n">
-        <v>4.8</v>
+        <v>11.9</v>
       </c>
       <c r="S948" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T948" t="inlineStr"/>
-      <c r="U948" t="inlineStr"/>
-      <c r="V948" t="inlineStr"/>
-      <c r="W948" t="inlineStr"/>
-      <c r="X948" t="inlineStr"/>
-      <c r="Y948" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T948" t="n">
+        <v>2</v>
+      </c>
+      <c r="U948" t="n">
+        <v>0</v>
+      </c>
+      <c r="V948" t="n">
+        <v>0</v>
+      </c>
+      <c r="W948" t="n">
+        <v>7</v>
+      </c>
+      <c r="X948" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="Y948" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>yamaalieujobe</t>
+          <t>yahwehshaven</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yamaalieujobe</t>
+          <t>https://www.tiktok.com/@yahwehshaven</t>
         </is>
       </c>
       <c r="C949" t="inlineStr"/>
@@ -56643,10 +56639,10 @@
         </is>
       </c>
       <c r="P949" s="1" t="n">
-        <v>46219.66237268518</v>
+        <v>46228.34030092593</v>
       </c>
       <c r="Q949" s="1" t="n">
-        <v>46219.66237268518</v>
+        <v>46228.34030092593</v>
       </c>
       <c r="R949" t="n">
         <v>4.8</v>
@@ -56666,12 +56662,12 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>yamania.2024</t>
+          <t>yamaalieujobe</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yamania.2024</t>
+          <t>https://www.tiktok.com/@yamaalieujobe</t>
         </is>
       </c>
       <c r="C950" t="inlineStr"/>
@@ -56682,7 +56678,7 @@
       <c r="H950" t="inlineStr"/>
       <c r="I950" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J950" t="inlineStr"/>
@@ -56702,10 +56698,10 @@
         </is>
       </c>
       <c r="P950" s="1" t="n">
-        <v>46209.50663194444</v>
+        <v>46219.66237268518</v>
       </c>
       <c r="Q950" s="1" t="n">
-        <v>46209.50663194444</v>
+        <v>46219.66237268518</v>
       </c>
       <c r="R950" t="n">
         <v>4.8</v>
@@ -56725,12 +56721,12 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>yasminsar_110</t>
+          <t>yamania.2024</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yasminsar_110</t>
+          <t>https://www.tiktok.com/@yamania.2024</t>
         </is>
       </c>
       <c r="C951" t="inlineStr"/>
@@ -56741,7 +56737,7 @@
       <c r="H951" t="inlineStr"/>
       <c r="I951" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J951" t="inlineStr"/>
@@ -56761,10 +56757,10 @@
         </is>
       </c>
       <c r="P951" s="1" t="n">
-        <v>46236.70356481482</v>
+        <v>46209.50663194444</v>
       </c>
       <c r="Q951" s="1" t="n">
-        <v>46236.70356481482</v>
+        <v>46209.50663194444</v>
       </c>
       <c r="R951" t="n">
         <v>4.8</v>
@@ -56784,12 +56780,12 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>yawa.kludje</t>
+          <t>yasminsar_110</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yawa.kludje</t>
+          <t>https://www.tiktok.com/@yasminsar_110</t>
         </is>
       </c>
       <c r="C952" t="inlineStr"/>
@@ -56798,7 +56794,11 @@
       <c r="F952" t="inlineStr"/>
       <c r="G952" t="inlineStr"/>
       <c r="H952" t="inlineStr"/>
-      <c r="I952" t="inlineStr"/>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J952" t="inlineStr"/>
       <c r="K952" t="inlineStr"/>
       <c r="L952" t="inlineStr"/>
@@ -56807,22 +56807,22 @@
       </c>
       <c r="N952" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O952" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P952" s="1" t="n">
-        <v>46253.09020833333</v>
+        <v>46236.70356481482</v>
       </c>
       <c r="Q952" s="1" t="n">
-        <v>46253.09020833333</v>
+        <v>46236.70356481482</v>
       </c>
       <c r="R952" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S952" t="inlineStr">
         <is>
@@ -56839,12 +56839,12 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>yemi0417</t>
+          <t>yawa.kludje</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemi0417</t>
+          <t>https://www.tiktok.com/@yawa.kludje</t>
         </is>
       </c>
       <c r="C953" t="inlineStr"/>
@@ -56853,11 +56853,7 @@
       <c r="F953" t="inlineStr"/>
       <c r="G953" t="inlineStr"/>
       <c r="H953" t="inlineStr"/>
-      <c r="I953" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
+      <c r="I953" t="inlineStr"/>
       <c r="J953" t="inlineStr"/>
       <c r="K953" t="inlineStr"/>
       <c r="L953" t="inlineStr"/>
@@ -56866,22 +56862,22 @@
       </c>
       <c r="N953" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O953" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P953" s="1" t="n">
-        <v>46208.78111111111</v>
+        <v>46253.09020833333</v>
       </c>
       <c r="Q953" s="1" t="n">
-        <v>46208.78111111111</v>
+        <v>46253.09020833333</v>
       </c>
       <c r="R953" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S953" t="inlineStr">
         <is>
@@ -56898,12 +56894,12 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>yemisi0906</t>
+          <t>yemi0417</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemisi0906</t>
+          <t>https://www.tiktok.com/@yemi0417</t>
         </is>
       </c>
       <c r="C954" t="inlineStr"/>
@@ -56934,10 +56930,10 @@
         </is>
       </c>
       <c r="P954" s="1" t="n">
-        <v>46213.52189814814</v>
+        <v>46208.78111111111</v>
       </c>
       <c r="Q954" s="1" t="n">
-        <v>46213.52189814814</v>
+        <v>46208.78111111111</v>
       </c>
       <c r="R954" t="n">
         <v>4.8</v>
@@ -56957,12 +56953,12 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>yemisi_81</t>
+          <t>yemisi0906</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemisi_81</t>
+          <t>https://www.tiktok.com/@yemisi0906</t>
         </is>
       </c>
       <c r="C955" t="inlineStr"/>
@@ -56993,10 +56989,10 @@
         </is>
       </c>
       <c r="P955" s="1" t="n">
-        <v>46238.41952546296</v>
+        <v>46213.52189814814</v>
       </c>
       <c r="Q955" s="1" t="n">
-        <v>46238.41952546296</v>
+        <v>46213.52189814814</v>
       </c>
       <c r="R955" t="n">
         <v>4.8</v>
@@ -57016,12 +57012,12 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>yimika24</t>
+          <t>yemisi_81</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yimika24</t>
+          <t>https://www.tiktok.com/@yemisi_81</t>
         </is>
       </c>
       <c r="C956" t="inlineStr"/>
@@ -57032,7 +57028,7 @@
       <c r="H956" t="inlineStr"/>
       <c r="I956" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J956" t="inlineStr"/>
@@ -57052,10 +57048,10 @@
         </is>
       </c>
       <c r="P956" s="1" t="n">
-        <v>46227.66070601852</v>
+        <v>46238.41952546296</v>
       </c>
       <c r="Q956" s="1" t="n">
-        <v>46227.66070601852</v>
+        <v>46238.41952546296</v>
       </c>
       <c r="R956" t="n">
         <v>4.8</v>
@@ -57075,12 +57071,12 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>yinkus520</t>
+          <t>yimika24</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yinkus520</t>
+          <t>https://www.tiktok.com/@yimika24</t>
         </is>
       </c>
       <c r="C957" t="inlineStr"/>
@@ -57091,7 +57087,7 @@
       <c r="H957" t="inlineStr"/>
       <c r="I957" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J957" t="inlineStr"/>
@@ -57111,10 +57107,10 @@
         </is>
       </c>
       <c r="P957" s="1" t="n">
-        <v>46223.694375</v>
+        <v>46227.66070601852</v>
       </c>
       <c r="Q957" s="1" t="n">
-        <v>46223.694375</v>
+        <v>46227.66070601852</v>
       </c>
       <c r="R957" t="n">
         <v>4.8</v>
@@ -57134,12 +57130,12 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>yvette.chance8</t>
+          <t>yinkus520</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yvette.chance8</t>
+          <t>https://www.tiktok.com/@yinkus520</t>
         </is>
       </c>
       <c r="C958" t="inlineStr"/>
@@ -57150,7 +57146,7 @@
       <c r="H958" t="inlineStr"/>
       <c r="I958" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J958" t="inlineStr"/>
@@ -57161,22 +57157,22 @@
       </c>
       <c r="N958" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O958" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P958" s="1" t="n">
-        <v>45990.94167824074</v>
+        <v>46223.694375</v>
       </c>
       <c r="Q958" s="1" t="n">
-        <v>45990.94167824074</v>
+        <v>46223.694375</v>
       </c>
       <c r="R958" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S958" t="inlineStr">
         <is>
@@ -57193,12 +57189,12 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>yxsna_98</t>
+          <t>yvette.chance8</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yxsna_98</t>
+          <t>https://www.tiktok.com/@yvette.chance8</t>
         </is>
       </c>
       <c r="C959" t="inlineStr"/>
@@ -57209,7 +57205,7 @@
       <c r="H959" t="inlineStr"/>
       <c r="I959" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J959" t="inlineStr"/>
@@ -57220,7 +57216,7 @@
       </c>
       <c r="N959" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O959" t="inlineStr">
@@ -57229,13 +57225,13 @@
         </is>
       </c>
       <c r="P959" s="1" t="n">
-        <v>46264.53219907408</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="Q959" s="1" t="n">
-        <v>46264.53219907408</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="R959" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="S959" t="inlineStr">
         <is>
@@ -57252,12 +57248,12 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>zabi.azmhh</t>
+          <t>yxsna_98</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zabi.azmhh</t>
+          <t>https://www.tiktok.com/@yxsna_98</t>
         </is>
       </c>
       <c r="C960" t="inlineStr"/>
@@ -57268,7 +57264,7 @@
       <c r="H960" t="inlineStr"/>
       <c r="I960" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J960" t="inlineStr"/>
@@ -57279,22 +57275,22 @@
       </c>
       <c r="N960" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O960" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P960" s="1" t="n">
-        <v>46208.71684027778</v>
+        <v>46264.53219907408</v>
       </c>
       <c r="Q960" s="1" t="n">
-        <v>46208.71684027778</v>
+        <v>46264.53219907408</v>
       </c>
       <c r="R960" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S960" t="inlineStr">
         <is>
@@ -57311,12 +57307,12 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>zachandmama2</t>
+          <t>zabi.azmhh</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zachandmama2</t>
+          <t>https://www.tiktok.com/@zabi.azmhh</t>
         </is>
       </c>
       <c r="C961" t="inlineStr"/>
@@ -57327,7 +57323,7 @@
       <c r="H961" t="inlineStr"/>
       <c r="I961" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="J961" t="inlineStr"/>
@@ -57338,22 +57334,22 @@
       </c>
       <c r="N961" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O961" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P961" s="1" t="n">
-        <v>46192.860625</v>
+        <v>46208.71684027778</v>
       </c>
       <c r="Q961" s="1" t="n">
-        <v>46192.860625</v>
+        <v>46208.71684027778</v>
       </c>
       <c r="R961" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S961" t="inlineStr">
         <is>
@@ -57370,12 +57366,12 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>zaheersheikh786</t>
+          <t>zachandmama2</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zaheersheikh786</t>
+          <t>https://www.tiktok.com/@zachandmama2</t>
         </is>
       </c>
       <c r="C962" t="inlineStr"/>
@@ -57386,7 +57382,7 @@
       <c r="H962" t="inlineStr"/>
       <c r="I962" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J962" t="inlineStr"/>
@@ -57406,10 +57402,10 @@
         </is>
       </c>
       <c r="P962" s="1" t="n">
-        <v>45913.74726851852</v>
+        <v>46192.860625</v>
       </c>
       <c r="Q962" s="1" t="n">
-        <v>45913.74726851852</v>
+        <v>46192.860625</v>
       </c>
       <c r="R962" t="n">
         <v>6</v>
@@ -57429,12 +57425,12 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>zainab36576</t>
+          <t>zaheersheikh786</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zainab36576</t>
+          <t>https://www.tiktok.com/@zaheersheikh786</t>
         </is>
       </c>
       <c r="C963" t="inlineStr"/>
@@ -57445,7 +57441,7 @@
       <c r="H963" t="inlineStr"/>
       <c r="I963" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J963" t="inlineStr"/>
@@ -57465,10 +57461,10 @@
         </is>
       </c>
       <c r="P963" s="1" t="n">
-        <v>46244.3722337963</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="Q963" s="1" t="n">
-        <v>46244.3722337963</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="R963" t="n">
         <v>6</v>
@@ -57488,12 +57484,12 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>zara.hussein2</t>
+          <t>zainab36576</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zara.hussein2</t>
+          <t>https://www.tiktok.com/@zainab36576</t>
         </is>
       </c>
       <c r="C964" t="inlineStr"/>
@@ -57504,7 +57500,7 @@
       <c r="H964" t="inlineStr"/>
       <c r="I964" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J964" t="inlineStr"/>
@@ -57515,22 +57511,22 @@
       </c>
       <c r="N964" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O964" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P964" s="1" t="n">
-        <v>46234.76921296296</v>
+        <v>46244.3722337963</v>
       </c>
       <c r="Q964" s="1" t="n">
-        <v>46234.76921296296</v>
+        <v>46244.3722337963</v>
       </c>
       <c r="R964" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S964" t="inlineStr">
         <is>
@@ -57547,12 +57543,12 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>zaynabee__flawless</t>
+          <t>zara.hussein2</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zaynabee__flawless</t>
+          <t>https://www.tiktok.com/@zara.hussein2</t>
         </is>
       </c>
       <c r="C965" t="inlineStr"/>
@@ -57561,7 +57557,11 @@
       <c r="F965" t="inlineStr"/>
       <c r="G965" t="inlineStr"/>
       <c r="H965" t="inlineStr"/>
-      <c r="I965" t="inlineStr"/>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J965" t="inlineStr"/>
       <c r="K965" t="inlineStr"/>
       <c r="L965" t="inlineStr"/>
@@ -57570,22 +57570,22 @@
       </c>
       <c r="N965" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O965" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P965" s="1" t="n">
-        <v>46253.10194444445</v>
+        <v>46234.76921296296</v>
       </c>
       <c r="Q965" s="1" t="n">
-        <v>46253.10194444445</v>
+        <v>46234.76921296296</v>
       </c>
       <c r="R965" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S965" t="inlineStr">
         <is>
@@ -57602,12 +57602,12 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>ze.b20</t>
+          <t>zaynabee__flawless</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ze.b20</t>
+          <t>https://www.tiktok.com/@zaynabee__flawless</t>
         </is>
       </c>
       <c r="C966" t="inlineStr"/>
@@ -57616,11 +57616,7 @@
       <c r="F966" t="inlineStr"/>
       <c r="G966" t="inlineStr"/>
       <c r="H966" t="inlineStr"/>
-      <c r="I966" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+      <c r="I966" t="inlineStr"/>
       <c r="J966" t="inlineStr"/>
       <c r="K966" t="inlineStr"/>
       <c r="L966" t="inlineStr"/>
@@ -57629,22 +57625,22 @@
       </c>
       <c r="N966" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O966" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P966" s="1" t="n">
-        <v>46208.82376157407</v>
+        <v>46253.10194444445</v>
       </c>
       <c r="Q966" s="1" t="n">
-        <v>46208.82376157407</v>
+        <v>46253.10194444445</v>
       </c>
       <c r="R966" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="S966" t="inlineStr">
         <is>
@@ -57661,12 +57657,12 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>zeesummer3</t>
+          <t>ze.b20</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zeesummer3</t>
+          <t>https://www.tiktok.com/@ze.b20</t>
         </is>
       </c>
       <c r="C967" t="inlineStr"/>
@@ -57697,10 +57693,10 @@
         </is>
       </c>
       <c r="P967" s="1" t="n">
-        <v>46234.76131944444</v>
+        <v>46208.82376157407</v>
       </c>
       <c r="Q967" s="1" t="n">
-        <v>46234.76131944444</v>
+        <v>46208.82376157407</v>
       </c>
       <c r="R967" t="n">
         <v>4.8</v>
@@ -57720,12 +57716,12 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>zembii</t>
+          <t>zeesummer3</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zembii</t>
+          <t>https://www.tiktok.com/@zeesummer3</t>
         </is>
       </c>
       <c r="C968" t="inlineStr"/>
@@ -57736,7 +57732,7 @@
       <c r="H968" t="inlineStr"/>
       <c r="I968" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J968" t="inlineStr"/>
@@ -57747,56 +57743,44 @@
       </c>
       <c r="N968" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O968" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P968" s="1" t="n">
-        <v>46221.60350694445</v>
+        <v>46234.76131944444</v>
       </c>
       <c r="Q968" s="1" t="n">
-        <v>46221.60350694445</v>
+        <v>46234.76131944444</v>
       </c>
       <c r="R968" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="S968" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T968" t="n">
-        <v>2</v>
-      </c>
-      <c r="U968" t="n">
-        <v>0</v>
-      </c>
-      <c r="V968" t="n">
-        <v>0</v>
-      </c>
-      <c r="W968" t="n">
-        <v>6</v>
-      </c>
-      <c r="X968" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="Y968" t="n">
-        <v>3</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T968" t="inlineStr"/>
+      <c r="U968" t="inlineStr"/>
+      <c r="V968" t="inlineStr"/>
+      <c r="W968" t="inlineStr"/>
+      <c r="X968" t="inlineStr"/>
+      <c r="Y968" t="inlineStr"/>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>zia.choudhury2</t>
+          <t>zembii</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zia.choudhury2</t>
+          <t>https://www.tiktok.com/@zembii</t>
         </is>
       </c>
       <c r="C969" t="inlineStr"/>
@@ -57807,7 +57791,7 @@
       <c r="H969" t="inlineStr"/>
       <c r="I969" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J969" t="inlineStr"/>
@@ -57818,44 +57802,56 @@
       </c>
       <c r="N969" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="O969" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="P969" s="1" t="n">
-        <v>46209.59967592593</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="Q969" s="1" t="n">
-        <v>46209.59967592593</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="R969" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="S969" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T969" t="inlineStr"/>
-      <c r="U969" t="inlineStr"/>
-      <c r="V969" t="inlineStr"/>
-      <c r="W969" t="inlineStr"/>
-      <c r="X969" t="inlineStr"/>
-      <c r="Y969" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T969" t="n">
+        <v>2</v>
+      </c>
+      <c r="U969" t="n">
+        <v>0</v>
+      </c>
+      <c r="V969" t="n">
+        <v>0</v>
+      </c>
+      <c r="W969" t="n">
+        <v>6</v>
+      </c>
+      <c r="X969" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="Y969" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>zndy239</t>
+          <t>zia.choudhury2</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zndy239</t>
+          <t>https://www.tiktok.com/@zia.choudhury2</t>
         </is>
       </c>
       <c r="C970" t="inlineStr"/>
@@ -57866,7 +57862,7 @@
       <c r="H970" t="inlineStr"/>
       <c r="I970" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="J970" t="inlineStr"/>
@@ -57886,10 +57882,10 @@
         </is>
       </c>
       <c r="P970" s="1" t="n">
-        <v>46233.66278935185</v>
+        <v>46209.59967592593</v>
       </c>
       <c r="Q970" s="1" t="n">
-        <v>46233.66278935185</v>
+        <v>46209.59967592593</v>
       </c>
       <c r="R970" t="n">
         <v>4.8</v>
@@ -57909,12 +57905,12 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>zommy45</t>
+          <t>zndy239</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zommy45</t>
+          <t>https://www.tiktok.com/@zndy239</t>
         </is>
       </c>
       <c r="C971" t="inlineStr"/>
@@ -57925,7 +57921,7 @@
       <c r="H971" t="inlineStr"/>
       <c r="I971" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="J971" t="inlineStr"/>
@@ -57945,10 +57941,10 @@
         </is>
       </c>
       <c r="P971" s="1" t="n">
-        <v>46209.55960648148</v>
+        <v>46233.66278935185</v>
       </c>
       <c r="Q971" s="1" t="n">
-        <v>46209.55960648148</v>
+        <v>46233.66278935185</v>
       </c>
       <c r="R971" t="n">
         <v>4.8</v>
@@ -57968,12 +57964,12 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>zoooweemamaa</t>
+          <t>zommy45</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zoooweemamaa</t>
+          <t>https://www.tiktok.com/@zommy45</t>
         </is>
       </c>
       <c r="C972" t="inlineStr"/>
@@ -57984,7 +57980,7 @@
       <c r="H972" t="inlineStr"/>
       <c r="I972" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J972" t="inlineStr"/>
@@ -58004,10 +58000,10 @@
         </is>
       </c>
       <c r="P972" s="1" t="n">
-        <v>46230.43392361111</v>
+        <v>46209.55960648148</v>
       </c>
       <c r="Q972" s="1" t="n">
-        <v>46230.43392361111</v>
+        <v>46209.55960648148</v>
       </c>
       <c r="R972" t="n">
         <v>4.8</v>
@@ -58027,12 +58023,12 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>zotouzotou</t>
+          <t>zoooweemamaa</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zotouzotou</t>
+          <t>https://www.tiktok.com/@zoooweemamaa</t>
         </is>
       </c>
       <c r="C973" t="inlineStr"/>
@@ -58043,7 +58039,7 @@
       <c r="H973" t="inlineStr"/>
       <c r="I973" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="J973" t="inlineStr"/>
@@ -58054,22 +58050,22 @@
       </c>
       <c r="N973" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="O973" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="P973" s="1" t="n">
-        <v>46256.54951388889</v>
+        <v>46230.43392361111</v>
       </c>
       <c r="Q973" s="1" t="n">
-        <v>46256.54951388889</v>
+        <v>46230.43392361111</v>
       </c>
       <c r="R973" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="S973" t="inlineStr">
         <is>
@@ -58086,12 +58082,12 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>zozadex</t>
+          <t>zotouzotou</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zozadex</t>
+          <t>https://www.tiktok.com/@zotouzotou</t>
         </is>
       </c>
       <c r="C974" t="inlineStr"/>
@@ -58100,7 +58096,11 @@
       <c r="F974" t="inlineStr"/>
       <c r="G974" t="inlineStr"/>
       <c r="H974" t="inlineStr"/>
-      <c r="I974" t="inlineStr"/>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J974" t="inlineStr"/>
       <c r="K974" t="inlineStr"/>
       <c r="L974" t="inlineStr"/>
@@ -58109,7 +58109,7 @@
       </c>
       <c r="N974" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="O974" t="inlineStr">
@@ -58118,13 +58118,13 @@
         </is>
       </c>
       <c r="P974" s="1" t="n">
-        <v>46254.53954861111</v>
+        <v>46256.54951388889</v>
       </c>
       <c r="Q974" s="1" t="n">
-        <v>46254.53954861111</v>
+        <v>46256.54951388889</v>
       </c>
       <c r="R974" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="S974" t="inlineStr">
         <is>
@@ -58138,6 +58138,61 @@
       <c r="X974" t="inlineStr"/>
       <c r="Y974" t="inlineStr"/>
     </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>zozadex</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@zozadex</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr"/>
+      <c r="D975" t="inlineStr"/>
+      <c r="E975" t="inlineStr"/>
+      <c r="F975" t="inlineStr"/>
+      <c r="G975" t="inlineStr"/>
+      <c r="H975" t="inlineStr"/>
+      <c r="I975" t="inlineStr"/>
+      <c r="J975" t="inlineStr"/>
+      <c r="K975" t="inlineStr"/>
+      <c r="L975" t="inlineStr"/>
+      <c r="M975" t="n">
+        <v>1</v>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="O975" t="inlineStr">
+        <is>
+          <t>TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="P975" s="1" t="n">
+        <v>46254.53954861111</v>
+      </c>
+      <c r="Q975" s="1" t="n">
+        <v>46254.53954861111</v>
+      </c>
+      <c r="R975" t="n">
+        <v>6</v>
+      </c>
+      <c r="S975" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T975" t="inlineStr"/>
+      <c r="U975" t="inlineStr"/>
+      <c r="V975" t="inlineStr"/>
+      <c r="W975" t="inlineStr"/>
+      <c r="X975" t="inlineStr"/>
+      <c r="Y975" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -30785,13 +30785,13 @@
         <v>0</v>
       </c>
       <c r="W518" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X518" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="Y518" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="519">
@@ -32302,7 +32302,7 @@
         </is>
       </c>
       <c r="T544" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U544" t="n">
         <v>0</v>
@@ -32311,7 +32311,7 @@
         <v>0</v>
       </c>
       <c r="W544" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X544" s="1" t="n">
         <v>46271</v>
@@ -45941,27 +45941,15 @@
       </c>
       <c r="S777" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T777" t="n">
-        <v>1</v>
-      </c>
-      <c r="U777" t="n">
-        <v>0</v>
-      </c>
-      <c r="V777" t="n">
-        <v>0</v>
-      </c>
-      <c r="W777" t="n">
-        <v>2</v>
-      </c>
-      <c r="X777" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="Y777" t="n">
-        <v>2</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T777" t="inlineStr"/>
+      <c r="U777" t="inlineStr"/>
+      <c r="V777" t="inlineStr"/>
+      <c r="W777" t="inlineStr"/>
+      <c r="X777" t="inlineStr"/>
+      <c r="Y777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
